--- a/data/ubicaciones.xlsx
+++ b/data/ubicaciones.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecnofastsa-my.sharepoint.com/personal/apinto_tecnopanel_cl/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LA CHACRA - copia\LA-CHACRA\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="618" documentId="8_{C99A5D9F-8668-4781-897B-E63D556314A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D54F2F5-7A4B-4B5A-9A62-D7264D343A4F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A188F45A-7FC4-4A22-8CFB-E9D8C126A403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" firstSheet="1" activeTab="1" xr2:uid="{93FECE06-38ED-44E5-9DFE-1A3DE9FBC240}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="18240" firstSheet="1" activeTab="1" xr2:uid="{93FECE06-38ED-44E5-9DFE-1A3DE9FBC240}"/>
   </bookViews>
   <sheets>
     <sheet name="UB.AFUERA CARPA CHICA" sheetId="9" state="hidden" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2858" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2856" uniqueCount="787">
   <si>
     <t>PONIENTE</t>
   </si>
@@ -3108,18 +3108,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3144,13 +3132,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3171,6 +3156,27 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3188,21 +3194,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3231,11 +3222,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3254,6 +3248,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3308,15 +3317,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4094,32 +4094,32 @@
     </row>
     <row r="2" spans="2:24" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="H3" s="92" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93"/>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="93"/>
-      <c r="R3" s="94"/>
+      <c r="H3" s="90" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="91"/>
+      <c r="N3" s="91"/>
+      <c r="O3" s="91"/>
+      <c r="P3" s="91"/>
+      <c r="Q3" s="91"/>
+      <c r="R3" s="92"/>
     </row>
     <row r="4" spans="2:24" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H4" s="95"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
-      <c r="M4" s="96"/>
-      <c r="N4" s="96"/>
-      <c r="O4" s="96"/>
-      <c r="P4" s="96"/>
-      <c r="Q4" s="96"/>
-      <c r="R4" s="97"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="94"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="95"/>
     </row>
     <row r="5" spans="2:24" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E5" s="3"/>
@@ -4127,299 +4127,306 @@
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="2:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="98" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="119"/>
-      <c r="F6" s="78"/>
-      <c r="H6" s="78"/>
-      <c r="J6" s="78"/>
-      <c r="L6" s="78" t="s">
+      <c r="F6" s="87"/>
+      <c r="H6" s="87"/>
+      <c r="J6" s="87"/>
+      <c r="L6" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="N6" s="78" t="s">
+      <c r="N6" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="P6" s="78" t="s">
+      <c r="P6" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="R6" s="78" t="s">
+      <c r="R6" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="V6" s="78"/>
-      <c r="X6" s="116" t="s">
+      <c r="T6" s="87"/>
+      <c r="V6" s="87"/>
+      <c r="X6" s="98" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="2:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="117"/>
+      <c r="B7" s="99"/>
       <c r="D7" s="120"/>
-      <c r="F7" s="90"/>
-      <c r="H7" s="90"/>
-      <c r="J7" s="90"/>
-      <c r="L7" s="90"/>
-      <c r="N7" s="90"/>
-      <c r="P7" s="90"/>
-      <c r="R7" s="90"/>
-      <c r="T7" s="90"/>
-      <c r="V7" s="90"/>
-      <c r="X7" s="117"/>
+      <c r="F7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="J7" s="96"/>
+      <c r="L7" s="96"/>
+      <c r="N7" s="96"/>
+      <c r="P7" s="96"/>
+      <c r="R7" s="96"/>
+      <c r="T7" s="96"/>
+      <c r="V7" s="96"/>
+      <c r="X7" s="99"/>
     </row>
     <row r="8" spans="2:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="117"/>
+      <c r="B8" s="99"/>
       <c r="D8" s="120"/>
-      <c r="F8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="J8" s="90"/>
-      <c r="L8" s="90"/>
-      <c r="N8" s="90"/>
-      <c r="P8" s="90"/>
-      <c r="R8" s="90"/>
-      <c r="T8" s="90"/>
-      <c r="V8" s="90"/>
-      <c r="X8" s="117"/>
+      <c r="F8" s="96"/>
+      <c r="H8" s="96"/>
+      <c r="J8" s="96"/>
+      <c r="L8" s="96"/>
+      <c r="N8" s="96"/>
+      <c r="P8" s="96"/>
+      <c r="R8" s="96"/>
+      <c r="T8" s="96"/>
+      <c r="V8" s="96"/>
+      <c r="X8" s="99"/>
     </row>
     <row r="9" spans="2:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="117"/>
+      <c r="B9" s="99"/>
       <c r="D9" s="120"/>
-      <c r="F9" s="90"/>
-      <c r="H9" s="90"/>
-      <c r="J9" s="90"/>
-      <c r="L9" s="90"/>
-      <c r="N9" s="90"/>
-      <c r="P9" s="90"/>
-      <c r="R9" s="90"/>
-      <c r="T9" s="90"/>
-      <c r="V9" s="90"/>
-      <c r="X9" s="117"/>
+      <c r="F9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="J9" s="96"/>
+      <c r="L9" s="96"/>
+      <c r="N9" s="96"/>
+      <c r="P9" s="96"/>
+      <c r="R9" s="96"/>
+      <c r="T9" s="96"/>
+      <c r="V9" s="96"/>
+      <c r="X9" s="99"/>
     </row>
     <row r="10" spans="2:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="117"/>
+      <c r="B10" s="99"/>
       <c r="D10" s="120"/>
-      <c r="F10" s="90"/>
-      <c r="H10" s="90"/>
-      <c r="J10" s="90"/>
-      <c r="L10" s="90"/>
-      <c r="N10" s="90"/>
-      <c r="P10" s="90"/>
-      <c r="R10" s="90"/>
-      <c r="T10" s="90"/>
-      <c r="V10" s="90"/>
-      <c r="X10" s="117"/>
+      <c r="F10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="J10" s="96"/>
+      <c r="L10" s="96"/>
+      <c r="N10" s="96"/>
+      <c r="P10" s="96"/>
+      <c r="R10" s="96"/>
+      <c r="T10" s="96"/>
+      <c r="V10" s="96"/>
+      <c r="X10" s="99"/>
     </row>
     <row r="11" spans="2:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="117"/>
+      <c r="B11" s="99"/>
       <c r="D11" s="120"/>
-      <c r="F11" s="90"/>
-      <c r="H11" s="90"/>
-      <c r="J11" s="90"/>
-      <c r="L11" s="90"/>
-      <c r="N11" s="90"/>
-      <c r="P11" s="90"/>
-      <c r="R11" s="90"/>
-      <c r="T11" s="90"/>
-      <c r="V11" s="90"/>
-      <c r="X11" s="117"/>
+      <c r="F11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="J11" s="96"/>
+      <c r="L11" s="96"/>
+      <c r="N11" s="96"/>
+      <c r="P11" s="96"/>
+      <c r="R11" s="96"/>
+      <c r="T11" s="96"/>
+      <c r="V11" s="96"/>
+      <c r="X11" s="99"/>
     </row>
     <row r="12" spans="2:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="117"/>
+      <c r="B12" s="99"/>
       <c r="D12" s="120"/>
-      <c r="F12" s="90"/>
-      <c r="H12" s="90"/>
-      <c r="J12" s="90"/>
-      <c r="L12" s="90"/>
-      <c r="N12" s="90"/>
-      <c r="P12" s="90"/>
-      <c r="R12" s="90"/>
-      <c r="T12" s="90"/>
-      <c r="V12" s="90"/>
-      <c r="X12" s="117"/>
+      <c r="F12" s="96"/>
+      <c r="H12" s="96"/>
+      <c r="J12" s="96"/>
+      <c r="L12" s="96"/>
+      <c r="N12" s="96"/>
+      <c r="P12" s="96"/>
+      <c r="R12" s="96"/>
+      <c r="T12" s="96"/>
+      <c r="V12" s="96"/>
+      <c r="X12" s="99"/>
     </row>
     <row r="13" spans="2:24" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="117"/>
+      <c r="B13" s="99"/>
       <c r="D13" s="121"/>
-      <c r="F13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="J13" s="91"/>
-      <c r="L13" s="91"/>
-      <c r="N13" s="91"/>
-      <c r="P13" s="91"/>
-      <c r="R13" s="91"/>
-      <c r="T13" s="91"/>
-      <c r="V13" s="91"/>
-      <c r="X13" s="117"/>
+      <c r="F13" s="97"/>
+      <c r="H13" s="97"/>
+      <c r="J13" s="97"/>
+      <c r="L13" s="97"/>
+      <c r="N13" s="97"/>
+      <c r="P13" s="97"/>
+      <c r="R13" s="97"/>
+      <c r="T13" s="97"/>
+      <c r="V13" s="97"/>
+      <c r="X13" s="99"/>
     </row>
     <row r="14" spans="2:24" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="117"/>
-      <c r="X14" s="117"/>
+      <c r="B14" s="99"/>
+      <c r="X14" s="99"/>
     </row>
     <row r="15" spans="2:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="117"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="100"/>
-      <c r="H15" s="98"/>
-      <c r="I15" s="99"/>
-      <c r="J15" s="100"/>
-      <c r="L15" s="107" t="s">
+      <c r="B15" s="99"/>
+      <c r="D15" s="101"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="103"/>
+      <c r="H15" s="101"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="103"/>
+      <c r="L15" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="108"/>
-      <c r="N15" s="109"/>
-      <c r="P15" s="107" t="s">
+      <c r="M15" s="111"/>
+      <c r="N15" s="112"/>
+      <c r="P15" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="Q15" s="108"/>
-      <c r="R15" s="109"/>
-      <c r="T15" s="78" t="s">
+      <c r="Q15" s="111"/>
+      <c r="R15" s="112"/>
+      <c r="T15" s="87" t="s">
         <v>10</v>
       </c>
       <c r="U15" s="6"/>
       <c r="V15" s="6"/>
-      <c r="X15" s="117"/>
+      <c r="X15" s="99"/>
     </row>
     <row r="16" spans="2:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="117"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="102"/>
-      <c r="F16" s="103"/>
-      <c r="H16" s="101"/>
-      <c r="I16" s="102"/>
-      <c r="J16" s="103"/>
-      <c r="L16" s="110"/>
-      <c r="M16" s="111"/>
-      <c r="N16" s="112"/>
-      <c r="P16" s="110"/>
-      <c r="Q16" s="111"/>
-      <c r="R16" s="112"/>
-      <c r="T16" s="90"/>
+      <c r="B16" s="99"/>
+      <c r="D16" s="104"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="106"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="105"/>
+      <c r="J16" s="106"/>
+      <c r="L16" s="113"/>
+      <c r="M16" s="114"/>
+      <c r="N16" s="115"/>
+      <c r="P16" s="113"/>
+      <c r="Q16" s="114"/>
+      <c r="R16" s="115"/>
+      <c r="T16" s="96"/>
       <c r="U16" s="6"/>
       <c r="V16" s="6"/>
-      <c r="X16" s="117"/>
+      <c r="X16" s="99"/>
     </row>
     <row r="17" spans="2:24" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="117"/>
-      <c r="D17" s="104"/>
-      <c r="E17" s="105"/>
-      <c r="F17" s="106"/>
-      <c r="H17" s="104"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="106"/>
-      <c r="L17" s="113"/>
-      <c r="M17" s="114"/>
-      <c r="N17" s="115"/>
-      <c r="P17" s="113"/>
-      <c r="Q17" s="114"/>
-      <c r="R17" s="115"/>
-      <c r="T17" s="90"/>
+      <c r="B17" s="99"/>
+      <c r="D17" s="107"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="109"/>
+      <c r="H17" s="107"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="109"/>
+      <c r="L17" s="116"/>
+      <c r="M17" s="117"/>
+      <c r="N17" s="118"/>
+      <c r="P17" s="116"/>
+      <c r="Q17" s="117"/>
+      <c r="R17" s="118"/>
+      <c r="T17" s="96"/>
       <c r="U17" s="6"/>
       <c r="V17" s="6"/>
-      <c r="X17" s="117"/>
+      <c r="X17" s="99"/>
     </row>
     <row r="18" spans="2:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="117"/>
-      <c r="T18" s="90"/>
-      <c r="X18" s="117"/>
+      <c r="B18" s="99"/>
+      <c r="T18" s="96"/>
+      <c r="X18" s="99"/>
     </row>
     <row r="19" spans="2:24" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="117"/>
-      <c r="T19" s="90"/>
+      <c r="B19" s="99"/>
+      <c r="T19" s="96"/>
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
-      <c r="X19" s="117"/>
+      <c r="X19" s="99"/>
     </row>
     <row r="20" spans="2:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="117"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="99"/>
-      <c r="F20" s="100"/>
-      <c r="H20" s="98"/>
-      <c r="I20" s="99"/>
-      <c r="J20" s="100"/>
-      <c r="L20" s="107" t="s">
+      <c r="B20" s="99"/>
+      <c r="D20" s="101"/>
+      <c r="E20" s="102"/>
+      <c r="F20" s="103"/>
+      <c r="H20" s="101"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="103"/>
+      <c r="L20" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="M20" s="108"/>
-      <c r="N20" s="109"/>
-      <c r="P20" s="107"/>
-      <c r="Q20" s="108"/>
-      <c r="R20" s="109"/>
-      <c r="T20" s="90"/>
+      <c r="M20" s="111"/>
+      <c r="N20" s="112"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="111"/>
+      <c r="R20" s="112"/>
+      <c r="T20" s="96"/>
       <c r="U20" s="6"/>
       <c r="V20" s="6"/>
-      <c r="X20" s="117"/>
+      <c r="X20" s="99"/>
     </row>
     <row r="21" spans="2:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="117"/>
-      <c r="D21" s="101"/>
-      <c r="E21" s="102"/>
-      <c r="F21" s="103"/>
-      <c r="H21" s="101"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="103"/>
-      <c r="L21" s="110"/>
-      <c r="M21" s="111"/>
-      <c r="N21" s="112"/>
-      <c r="P21" s="110"/>
-      <c r="Q21" s="111"/>
-      <c r="R21" s="112"/>
-      <c r="T21" s="90"/>
+      <c r="B21" s="99"/>
+      <c r="D21" s="104"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="106"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="106"/>
+      <c r="L21" s="113"/>
+      <c r="M21" s="114"/>
+      <c r="N21" s="115"/>
+      <c r="P21" s="113"/>
+      <c r="Q21" s="114"/>
+      <c r="R21" s="115"/>
+      <c r="T21" s="96"/>
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
-      <c r="X21" s="117"/>
+      <c r="X21" s="99"/>
     </row>
     <row r="22" spans="2:24" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="118"/>
-      <c r="D22" s="104"/>
-      <c r="E22" s="105"/>
-      <c r="F22" s="106"/>
-      <c r="H22" s="104"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="106"/>
-      <c r="L22" s="113"/>
-      <c r="M22" s="114"/>
-      <c r="N22" s="115"/>
-      <c r="P22" s="113"/>
-      <c r="Q22" s="114"/>
-      <c r="R22" s="115"/>
-      <c r="T22" s="91"/>
-      <c r="X22" s="118"/>
+      <c r="B22" s="100"/>
+      <c r="D22" s="107"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="109"/>
+      <c r="H22" s="107"/>
+      <c r="I22" s="108"/>
+      <c r="J22" s="109"/>
+      <c r="L22" s="116"/>
+      <c r="M22" s="117"/>
+      <c r="N22" s="118"/>
+      <c r="P22" s="116"/>
+      <c r="Q22" s="117"/>
+      <c r="R22" s="118"/>
+      <c r="T22" s="97"/>
+      <c r="X22" s="100"/>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.2">
       <c r="X23" s="10"/>
     </row>
     <row r="24" spans="2:24" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="H25" s="92" t="s">
+      <c r="H25" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="I25" s="93"/>
-      <c r="J25" s="93"/>
-      <c r="K25" s="93"/>
-      <c r="L25" s="93"/>
-      <c r="M25" s="93"/>
-      <c r="N25" s="93"/>
-      <c r="O25" s="93"/>
-      <c r="P25" s="93"/>
-      <c r="Q25" s="93"/>
-      <c r="R25" s="94"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="91"/>
+      <c r="K25" s="91"/>
+      <c r="L25" s="91"/>
+      <c r="M25" s="91"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="91"/>
+      <c r="P25" s="91"/>
+      <c r="Q25" s="91"/>
+      <c r="R25" s="92"/>
     </row>
     <row r="26" spans="2:24" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H26" s="95"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="96"/>
-      <c r="K26" s="96"/>
-      <c r="L26" s="96"/>
-      <c r="M26" s="96"/>
-      <c r="N26" s="96"/>
-      <c r="O26" s="96"/>
-      <c r="P26" s="96"/>
-      <c r="Q26" s="96"/>
-      <c r="R26" s="97"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="94"/>
+      <c r="J26" s="94"/>
+      <c r="K26" s="94"/>
+      <c r="L26" s="94"/>
+      <c r="M26" s="94"/>
+      <c r="N26" s="94"/>
+      <c r="O26" s="94"/>
+      <c r="P26" s="94"/>
+      <c r="Q26" s="94"/>
+      <c r="R26" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="P6:P13"/>
+    <mergeCell ref="R6:R13"/>
+    <mergeCell ref="H3:R4"/>
+    <mergeCell ref="D15:F17"/>
+    <mergeCell ref="H15:J17"/>
+    <mergeCell ref="L15:N17"/>
+    <mergeCell ref="P15:R17"/>
     <mergeCell ref="H25:R26"/>
     <mergeCell ref="T15:T22"/>
     <mergeCell ref="B6:B22"/>
@@ -4436,13 +4443,6 @@
     <mergeCell ref="J6:J13"/>
     <mergeCell ref="L6:L13"/>
     <mergeCell ref="N6:N13"/>
-    <mergeCell ref="P6:P13"/>
-    <mergeCell ref="R6:R13"/>
-    <mergeCell ref="H3:R4"/>
-    <mergeCell ref="D15:F17"/>
-    <mergeCell ref="H15:J17"/>
-    <mergeCell ref="L15:N17"/>
-    <mergeCell ref="P15:R17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4567,117 +4567,117 @@
     <row r="8" spans="27:71" x14ac:dyDescent="0.2">
       <c r="AM8"/>
       <c r="AN8"/>
-      <c r="BA8" s="61"/>
+      <c r="BA8" s="67"/>
       <c r="BB8"/>
-      <c r="BC8" s="61"/>
+      <c r="BC8" s="67"/>
       <c r="BD8"/>
-      <c r="BE8" s="61"/>
+      <c r="BE8" s="67"/>
       <c r="BF8"/>
-      <c r="BG8" s="61"/>
+      <c r="BG8" s="67"/>
       <c r="BH8"/>
-      <c r="BI8" s="61"/>
+      <c r="BI8" s="67"/>
       <c r="BJ8"/>
-      <c r="BK8" s="61"/>
+      <c r="BK8" s="67"/>
       <c r="BL8"/>
-      <c r="BM8" s="61"/>
+      <c r="BM8" s="67"/>
       <c r="BN8"/>
-      <c r="BO8" s="61"/>
+      <c r="BO8" s="67"/>
       <c r="BP8"/>
-      <c r="BQ8" s="61"/>
+      <c r="BQ8" s="67"/>
       <c r="BR8"/>
-      <c r="BS8" s="61"/>
+      <c r="BS8" s="67"/>
     </row>
     <row r="9" spans="27:71" x14ac:dyDescent="0.2">
       <c r="AM9"/>
       <c r="AN9"/>
-      <c r="BA9" s="51"/>
+      <c r="BA9" s="68"/>
       <c r="BB9"/>
-      <c r="BC9" s="51"/>
+      <c r="BC9" s="68"/>
       <c r="BD9"/>
-      <c r="BE9" s="51"/>
+      <c r="BE9" s="68"/>
       <c r="BF9"/>
-      <c r="BG9" s="51"/>
+      <c r="BG9" s="68"/>
       <c r="BH9"/>
-      <c r="BI9" s="51"/>
+      <c r="BI9" s="68"/>
       <c r="BJ9"/>
-      <c r="BK9" s="51"/>
+      <c r="BK9" s="68"/>
       <c r="BL9"/>
-      <c r="BM9" s="51"/>
+      <c r="BM9" s="68"/>
       <c r="BN9"/>
-      <c r="BO9" s="51"/>
+      <c r="BO9" s="68"/>
       <c r="BP9"/>
-      <c r="BQ9" s="51"/>
+      <c r="BQ9" s="68"/>
       <c r="BR9"/>
-      <c r="BS9" s="51"/>
+      <c r="BS9" s="68"/>
     </row>
     <row r="10" spans="27:71" x14ac:dyDescent="0.2">
       <c r="AM10"/>
       <c r="AN10"/>
-      <c r="BA10" s="51"/>
+      <c r="BA10" s="68"/>
       <c r="BB10"/>
-      <c r="BC10" s="51"/>
+      <c r="BC10" s="68"/>
       <c r="BD10"/>
-      <c r="BE10" s="51"/>
+      <c r="BE10" s="68"/>
       <c r="BF10"/>
-      <c r="BG10" s="51"/>
+      <c r="BG10" s="68"/>
       <c r="BH10"/>
-      <c r="BI10" s="51"/>
+      <c r="BI10" s="68"/>
       <c r="BJ10"/>
-      <c r="BK10" s="51"/>
+      <c r="BK10" s="68"/>
       <c r="BL10"/>
-      <c r="BM10" s="51"/>
+      <c r="BM10" s="68"/>
       <c r="BN10"/>
-      <c r="BO10" s="51"/>
+      <c r="BO10" s="68"/>
       <c r="BP10"/>
-      <c r="BQ10" s="51"/>
+      <c r="BQ10" s="68"/>
       <c r="BR10"/>
-      <c r="BS10" s="51"/>
+      <c r="BS10" s="68"/>
     </row>
     <row r="11" spans="27:71" x14ac:dyDescent="0.2">
       <c r="AM11"/>
       <c r="AN11"/>
-      <c r="BA11" s="51"/>
+      <c r="BA11" s="68"/>
       <c r="BB11"/>
-      <c r="BC11" s="51"/>
+      <c r="BC11" s="68"/>
       <c r="BD11"/>
-      <c r="BE11" s="51"/>
+      <c r="BE11" s="68"/>
       <c r="BF11"/>
-      <c r="BG11" s="51"/>
+      <c r="BG11" s="68"/>
       <c r="BH11"/>
-      <c r="BI11" s="51"/>
+      <c r="BI11" s="68"/>
       <c r="BJ11"/>
-      <c r="BK11" s="51"/>
+      <c r="BK11" s="68"/>
       <c r="BL11"/>
-      <c r="BM11" s="51"/>
+      <c r="BM11" s="68"/>
       <c r="BN11"/>
-      <c r="BO11" s="51"/>
+      <c r="BO11" s="68"/>
       <c r="BP11"/>
-      <c r="BQ11" s="51"/>
+      <c r="BQ11" s="68"/>
       <c r="BR11"/>
-      <c r="BS11" s="51"/>
+      <c r="BS11" s="68"/>
     </row>
     <row r="12" spans="27:71" x14ac:dyDescent="0.2">
       <c r="AM12"/>
       <c r="AN12"/>
-      <c r="BA12" s="51"/>
+      <c r="BA12" s="68"/>
       <c r="BB12"/>
-      <c r="BC12" s="51"/>
+      <c r="BC12" s="68"/>
       <c r="BD12"/>
-      <c r="BE12" s="51"/>
+      <c r="BE12" s="68"/>
       <c r="BF12"/>
-      <c r="BG12" s="51"/>
+      <c r="BG12" s="68"/>
       <c r="BH12"/>
-      <c r="BI12" s="51"/>
+      <c r="BI12" s="68"/>
       <c r="BJ12"/>
-      <c r="BK12" s="51"/>
+      <c r="BK12" s="68"/>
       <c r="BL12"/>
-      <c r="BM12" s="51"/>
+      <c r="BM12" s="68"/>
       <c r="BN12"/>
-      <c r="BO12" s="51"/>
+      <c r="BO12" s="68"/>
       <c r="BP12"/>
-      <c r="BQ12" s="51"/>
+      <c r="BQ12" s="68"/>
       <c r="BR12"/>
-      <c r="BS12" s="51"/>
+      <c r="BS12" s="68"/>
     </row>
     <row r="13" spans="27:71" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="AM13"/>
@@ -4733,146 +4733,142 @@
       </c>
     </row>
     <row r="14" spans="27:71" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AA14" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="AB14" s="54"/>
-      <c r="AC14" s="41">
+      <c r="AA14" s="49"/>
+      <c r="AB14" s="50"/>
+      <c r="AC14" s="41" t="str">
         <f>+_xlfn.XLOOKUP(AA14,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
-        <v>0.96999999999999986</v>
-      </c>
-      <c r="AG14" s="53" t="s">
+        <v/>
+      </c>
+      <c r="AG14" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="AH14" s="54"/>
+      <c r="AH14" s="50"/>
       <c r="AI14" s="41">
         <f>+_xlfn.XLOOKUP(AG14,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.86499999999999999</v>
       </c>
-      <c r="AM14" s="53" t="s">
+      <c r="AM14" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="AN14" s="54"/>
+      <c r="AN14" s="50"/>
       <c r="AO14" s="41">
         <f>+_xlfn.XLOOKUP(AM14,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.75</v>
       </c>
-      <c r="AS14" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT14" s="54"/>
-      <c r="AU14" s="41">
+      <c r="AS14" s="49"/>
+      <c r="AT14" s="50"/>
+      <c r="AU14" s="41" t="str">
         <f>+_xlfn.XLOOKUP(AS14,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
-        <v>0.99999999999999978</v>
-      </c>
-      <c r="BA14" s="51" t="str">
+        <v/>
+      </c>
+      <c r="BA14" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BA8,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BB14"/>
-      <c r="BC14" s="51" t="str">
+      <c r="BC14" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BC8,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BD14"/>
-      <c r="BE14" s="51" t="str">
+      <c r="BE14" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BE8,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BF14"/>
-      <c r="BG14" s="51" t="str">
+      <c r="BG14" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BG8,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BH14"/>
-      <c r="BI14" s="51" t="str">
+      <c r="BI14" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BI8,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BJ14"/>
-      <c r="BK14" s="51" t="str">
+      <c r="BK14" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BK8,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BL14"/>
-      <c r="BM14" s="51" t="str">
+      <c r="BM14" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BM8,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BN14"/>
-      <c r="BO14" s="51" t="str">
+      <c r="BO14" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BO8,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BP14"/>
-      <c r="BQ14" s="51" t="str">
+      <c r="BQ14" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BQ8,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BR14"/>
-      <c r="BS14" s="51" t="str">
+      <c r="BS14" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BS8,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
     </row>
     <row r="15" spans="27:71" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="AA15" s="55"/>
-      <c r="AB15" s="56"/>
-      <c r="AC15" s="59" t="str">
+      <c r="AA15" s="51"/>
+      <c r="AB15" s="52"/>
+      <c r="AC15" s="55" t="str">
         <f>+_xlfn.XLOOKUP(AA14,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
-        <v>HUMEDO</v>
-      </c>
-      <c r="AG15" s="55"/>
-      <c r="AH15" s="56"/>
-      <c r="AI15" s="59" t="str">
+        <v/>
+      </c>
+      <c r="AG15" s="51"/>
+      <c r="AH15" s="52"/>
+      <c r="AI15" s="55" t="str">
         <f>+_xlfn.XLOOKUP(AG14,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
-      <c r="AM15" s="55"/>
-      <c r="AN15" s="56"/>
-      <c r="AO15" s="59" t="str">
+      <c r="AM15" s="51"/>
+      <c r="AN15" s="52"/>
+      <c r="AO15" s="55" t="str">
         <f>+_xlfn.XLOOKUP(AM14,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
-      <c r="AS15" s="55"/>
-      <c r="AT15" s="56"/>
-      <c r="AU15" s="59" t="str">
+      <c r="AS15" s="51"/>
+      <c r="AT15" s="52"/>
+      <c r="AU15" s="55" t="str">
         <f>+_xlfn.XLOOKUP(AS14,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
-        <v>HUMEDO</v>
-      </c>
-      <c r="BA15" s="52"/>
+        <v/>
+      </c>
+      <c r="BA15" s="69"/>
       <c r="BB15"/>
-      <c r="BC15" s="52"/>
+      <c r="BC15" s="69"/>
       <c r="BD15"/>
-      <c r="BE15" s="52"/>
+      <c r="BE15" s="69"/>
       <c r="BF15"/>
-      <c r="BG15" s="52"/>
+      <c r="BG15" s="69"/>
       <c r="BH15"/>
-      <c r="BI15" s="52"/>
+      <c r="BI15" s="69"/>
       <c r="BJ15"/>
-      <c r="BK15" s="52"/>
+      <c r="BK15" s="69"/>
       <c r="BL15"/>
-      <c r="BM15" s="52"/>
+      <c r="BM15" s="69"/>
       <c r="BN15"/>
-      <c r="BO15" s="52"/>
+      <c r="BO15" s="69"/>
       <c r="BP15"/>
-      <c r="BQ15" s="52"/>
+      <c r="BQ15" s="69"/>
       <c r="BR15"/>
-      <c r="BS15" s="52"/>
+      <c r="BS15" s="69"/>
     </row>
     <row r="16" spans="27:71" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="AA16" s="57"/>
-      <c r="AB16" s="58"/>
-      <c r="AC16" s="60"/>
-      <c r="AG16" s="57"/>
-      <c r="AH16" s="58"/>
-      <c r="AI16" s="60"/>
-      <c r="AM16" s="57"/>
-      <c r="AN16" s="58"/>
-      <c r="AO16" s="60"/>
-      <c r="AS16" s="57"/>
-      <c r="AT16" s="58"/>
-      <c r="AU16" s="60"/>
+      <c r="AA16" s="53"/>
+      <c r="AB16" s="54"/>
+      <c r="AC16" s="56"/>
+      <c r="AG16" s="53"/>
+      <c r="AH16" s="54"/>
+      <c r="AI16" s="56"/>
+      <c r="AM16" s="53"/>
+      <c r="AN16" s="54"/>
+      <c r="AO16" s="56"/>
+      <c r="AS16" s="53"/>
+      <c r="AT16" s="54"/>
+      <c r="AU16" s="56"/>
       <c r="BA16"/>
       <c r="BB16"/>
       <c r="BC16"/>
@@ -4896,37 +4892,37 @@
     <row r="17" spans="39:71" ht="18" x14ac:dyDescent="0.2">
       <c r="AM17"/>
       <c r="AN17"/>
-      <c r="BA17" s="53" t="s">
+      <c r="BA17" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="BB17" s="54"/>
+      <c r="BB17" s="50"/>
       <c r="BC17" s="41">
         <f>+_xlfn.XLOOKUP(BA17,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.79999999999999993</v>
       </c>
       <c r="BD17"/>
-      <c r="BE17" s="53"/>
-      <c r="BF17" s="54"/>
+      <c r="BE17" s="49"/>
+      <c r="BF17" s="50"/>
       <c r="BG17" s="41" t="str">
         <f>+_xlfn.XLOOKUP(BE17,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
       </c>
       <c r="BH17"/>
-      <c r="BI17" s="53"/>
-      <c r="BJ17" s="54"/>
+      <c r="BI17" s="49"/>
+      <c r="BJ17" s="50"/>
       <c r="BK17" s="41" t="str">
         <f>+_xlfn.XLOOKUP(BI17,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
       </c>
       <c r="BL17"/>
-      <c r="BM17" s="53"/>
-      <c r="BN17" s="54"/>
+      <c r="BM17" s="49"/>
+      <c r="BN17" s="50"/>
       <c r="BO17" s="41" t="str">
         <f>+_xlfn.XLOOKUP(BM17,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
       </c>
       <c r="BP17"/>
-      <c r="BQ17" s="61" t="s">
+      <c r="BQ17" s="67" t="s">
         <v>128</v>
       </c>
       <c r="BR17" s="6"/>
@@ -4935,58 +4931,58 @@
     <row r="18" spans="39:71" ht="18" x14ac:dyDescent="0.2">
       <c r="AM18"/>
       <c r="AN18"/>
-      <c r="BA18" s="55"/>
-      <c r="BB18" s="56"/>
-      <c r="BC18" s="59" t="str">
+      <c r="BA18" s="51"/>
+      <c r="BB18" s="52"/>
+      <c r="BC18" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BA17,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="BD18"/>
-      <c r="BE18" s="55"/>
-      <c r="BF18" s="56"/>
-      <c r="BG18" s="59" t="str">
+      <c r="BE18" s="51"/>
+      <c r="BF18" s="52"/>
+      <c r="BG18" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BE17,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BH18"/>
-      <c r="BI18" s="55"/>
-      <c r="BJ18" s="56"/>
-      <c r="BK18" s="59" t="str">
+      <c r="BI18" s="51"/>
+      <c r="BJ18" s="52"/>
+      <c r="BK18" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BI17,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BL18"/>
-      <c r="BM18" s="55"/>
-      <c r="BN18" s="56"/>
-      <c r="BO18" s="59" t="str">
+      <c r="BM18" s="51"/>
+      <c r="BN18" s="52"/>
+      <c r="BO18" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BM17,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BP18"/>
-      <c r="BQ18" s="51"/>
+      <c r="BQ18" s="68"/>
       <c r="BR18" s="6"/>
       <c r="BS18" s="6"/>
     </row>
     <row r="19" spans="39:71" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="AM19"/>
       <c r="AN19"/>
-      <c r="BA19" s="57"/>
-      <c r="BB19" s="58"/>
-      <c r="BC19" s="60"/>
+      <c r="BA19" s="53"/>
+      <c r="BB19" s="54"/>
+      <c r="BC19" s="56"/>
       <c r="BD19"/>
-      <c r="BE19" s="57"/>
-      <c r="BF19" s="58"/>
-      <c r="BG19" s="60"/>
+      <c r="BE19" s="53"/>
+      <c r="BF19" s="54"/>
+      <c r="BG19" s="56"/>
       <c r="BH19"/>
-      <c r="BI19" s="57"/>
-      <c r="BJ19" s="58"/>
-      <c r="BK19" s="60"/>
+      <c r="BI19" s="53"/>
+      <c r="BJ19" s="54"/>
+      <c r="BK19" s="56"/>
       <c r="BL19"/>
-      <c r="BM19" s="57"/>
-      <c r="BN19" s="58"/>
-      <c r="BO19" s="60"/>
+      <c r="BM19" s="53"/>
+      <c r="BN19" s="54"/>
+      <c r="BO19" s="56"/>
       <c r="BP19"/>
-      <c r="BQ19" s="51"/>
+      <c r="BQ19" s="68"/>
       <c r="BR19" s="6"/>
       <c r="BS19" s="6"/>
     </row>
@@ -5009,7 +5005,7 @@
       <c r="BN20"/>
       <c r="BO20"/>
       <c r="BP20"/>
-      <c r="BQ20" s="51"/>
+      <c r="BQ20" s="68"/>
       <c r="BR20"/>
       <c r="BS20"/>
     </row>
@@ -5032,40 +5028,40 @@
       <c r="BN21"/>
       <c r="BO21"/>
       <c r="BP21"/>
-      <c r="BQ21" s="51"/>
+      <c r="BQ21" s="68"/>
       <c r="BR21" s="6"/>
       <c r="BS21" s="6"/>
     </row>
     <row r="22" spans="39:71" ht="18" x14ac:dyDescent="0.2">
       <c r="AM22"/>
       <c r="AN22"/>
-      <c r="BA22" s="53"/>
-      <c r="BB22" s="54"/>
+      <c r="BA22" s="49"/>
+      <c r="BB22" s="50"/>
       <c r="BC22" s="41" t="str">
         <f>+_xlfn.XLOOKUP(BA22,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
       </c>
       <c r="BD22"/>
-      <c r="BE22" s="53" t="s">
+      <c r="BE22" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="BF22" s="54"/>
+      <c r="BF22" s="50"/>
       <c r="BG22" s="41">
         <f>+_xlfn.XLOOKUP(BE22,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.95999999999999985</v>
       </c>
       <c r="BH22"/>
-      <c r="BI22" s="53" t="s">
+      <c r="BI22" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="BJ22" s="54"/>
+      <c r="BJ22" s="50"/>
       <c r="BK22" s="41">
         <f>+_xlfn.XLOOKUP(BI22,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.97999999999999976</v>
       </c>
       <c r="BL22"/>
-      <c r="BM22" s="53"/>
-      <c r="BN22" s="54"/>
+      <c r="BM22" s="49"/>
+      <c r="BN22" s="50"/>
       <c r="BO22" s="41" t="str">
         <f>+_xlfn.XLOOKUP(BM22,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
@@ -5093,35 +5089,35 @@
       <c r="AX23"/>
       <c r="AY23"/>
       <c r="AZ23"/>
-      <c r="BA23" s="55"/>
-      <c r="BB23" s="56"/>
-      <c r="BC23" s="59" t="str">
+      <c r="BA23" s="51"/>
+      <c r="BB23" s="52"/>
+      <c r="BC23" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BA22,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BD23"/>
-      <c r="BE23" s="55"/>
-      <c r="BF23" s="56"/>
-      <c r="BG23" s="59" t="str">
+      <c r="BE23" s="51"/>
+      <c r="BF23" s="52"/>
+      <c r="BG23" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BE22,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="BH23"/>
-      <c r="BI23" s="55"/>
-      <c r="BJ23" s="56"/>
-      <c r="BK23" s="59" t="str">
+      <c r="BI23" s="51"/>
+      <c r="BJ23" s="52"/>
+      <c r="BK23" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BI22,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="BL23"/>
-      <c r="BM23" s="55"/>
-      <c r="BN23" s="56"/>
-      <c r="BO23" s="59" t="str">
+      <c r="BM23" s="51"/>
+      <c r="BN23" s="52"/>
+      <c r="BO23" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BM22,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BP23"/>
-      <c r="BQ23" s="51" t="str">
+      <c r="BQ23" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BQ17,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
@@ -5143,23 +5139,23 @@
       <c r="AX24"/>
       <c r="AY24"/>
       <c r="AZ24"/>
-      <c r="BA24" s="57"/>
-      <c r="BB24" s="58"/>
-      <c r="BC24" s="60"/>
+      <c r="BA24" s="53"/>
+      <c r="BB24" s="54"/>
+      <c r="BC24" s="56"/>
       <c r="BD24"/>
-      <c r="BE24" s="57"/>
-      <c r="BF24" s="58"/>
-      <c r="BG24" s="60"/>
+      <c r="BE24" s="53"/>
+      <c r="BF24" s="54"/>
+      <c r="BG24" s="56"/>
       <c r="BH24"/>
-      <c r="BI24" s="57"/>
-      <c r="BJ24" s="58"/>
-      <c r="BK24" s="60"/>
+      <c r="BI24" s="53"/>
+      <c r="BJ24" s="54"/>
+      <c r="BK24" s="56"/>
       <c r="BL24"/>
-      <c r="BM24" s="57"/>
-      <c r="BN24" s="58"/>
-      <c r="BO24" s="60"/>
+      <c r="BM24" s="53"/>
+      <c r="BN24" s="54"/>
+      <c r="BO24" s="56"/>
       <c r="BP24"/>
-      <c r="BQ24" s="52"/>
+      <c r="BQ24" s="69"/>
       <c r="BR24"/>
       <c r="BS24"/>
     </row>
@@ -5229,13 +5225,13 @@
       <c r="AS40" s="8"/>
     </row>
     <row r="41" spans="19:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="S41" s="81" t="s">
+      <c r="S41" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="T41" s="82"/>
-      <c r="U41" s="82"/>
-      <c r="V41" s="82"/>
-      <c r="W41" s="83"/>
+      <c r="T41" s="79"/>
+      <c r="U41" s="79"/>
+      <c r="V41" s="79"/>
+      <c r="W41" s="80"/>
       <c r="Y41" s="14"/>
       <c r="Z41" s="15"/>
       <c r="AA41" s="15"/>
@@ -5259,11 +5255,11 @@
       <c r="AS41" s="12"/>
     </row>
     <row r="42" spans="19:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="S42" s="84"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
-      <c r="V42" s="85"/>
-      <c r="W42" s="86"/>
+      <c r="S42" s="81"/>
+      <c r="T42" s="82"/>
+      <c r="U42" s="82"/>
+      <c r="V42" s="82"/>
+      <c r="W42" s="83"/>
       <c r="Y42" s="17"/>
       <c r="AB42" s="2"/>
       <c r="AC42" s="2"/>
@@ -5271,11 +5267,11 @@
       <c r="AS42" s="25"/>
     </row>
     <row r="43" spans="19:50" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S43" s="84"/>
-      <c r="T43" s="85"/>
-      <c r="U43" s="85"/>
-      <c r="V43" s="85"/>
-      <c r="W43" s="86"/>
+      <c r="S43" s="81"/>
+      <c r="T43" s="82"/>
+      <c r="U43" s="82"/>
+      <c r="V43" s="82"/>
+      <c r="W43" s="83"/>
       <c r="Y43" s="17"/>
       <c r="AB43" s="2"/>
       <c r="AC43" s="2"/>
@@ -5285,152 +5281,152 @@
       <c r="AS43" s="25"/>
     </row>
     <row r="44" spans="19:50" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="S44" s="84"/>
-      <c r="T44" s="85"/>
-      <c r="U44" s="85"/>
-      <c r="V44" s="85"/>
-      <c r="W44" s="86"/>
+      <c r="S44" s="81"/>
+      <c r="T44" s="82"/>
+      <c r="U44" s="82"/>
+      <c r="V44" s="82"/>
+      <c r="W44" s="83"/>
       <c r="Y44" s="17"/>
-      <c r="AA44" s="62" t="s">
+      <c r="AA44" s="70" t="s">
         <v>130</v>
       </c>
-      <c r="AC44" s="64" t="s">
+      <c r="AC44" s="59" t="s">
         <v>144</v>
       </c>
-      <c r="AD44" s="65"/>
+      <c r="AD44" s="60"/>
       <c r="AE44" s="44">
         <f>+_xlfn.XLOOKUP(AC44,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.94</v>
       </c>
       <c r="AF44" s="5"/>
-      <c r="AG44" s="62" t="s">
+      <c r="AG44" s="70" t="s">
         <v>168</v>
       </c>
-      <c r="AK44" s="62" t="s">
+      <c r="AK44" s="70" t="s">
         <v>126</v>
       </c>
-      <c r="AM44" s="64" t="s">
+      <c r="AM44" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="AN44" s="65"/>
+      <c r="AN44" s="60"/>
       <c r="AO44" s="41">
         <f>+_xlfn.XLOOKUP(AM44,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.74</v>
       </c>
       <c r="AP44" s="5"/>
-      <c r="AQ44" s="62" t="s">
+      <c r="AQ44" s="70" t="s">
         <v>125</v>
       </c>
       <c r="AS44" s="25"/>
     </row>
     <row r="45" spans="19:50" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="S45" s="84"/>
-      <c r="T45" s="85"/>
-      <c r="U45" s="85"/>
-      <c r="V45" s="85"/>
-      <c r="W45" s="86"/>
+      <c r="S45" s="81"/>
+      <c r="T45" s="82"/>
+      <c r="U45" s="82"/>
+      <c r="V45" s="82"/>
+      <c r="W45" s="83"/>
       <c r="Y45" s="17"/>
-      <c r="AA45" s="63"/>
-      <c r="AC45" s="66"/>
-      <c r="AD45" s="67"/>
-      <c r="AE45" s="76" t="str">
+      <c r="AA45" s="71"/>
+      <c r="AC45" s="61"/>
+      <c r="AD45" s="62"/>
+      <c r="AE45" s="57" t="str">
         <f>+_xlfn.XLOOKUP(AC44,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AF45" s="5"/>
-      <c r="AG45" s="63"/>
-      <c r="AK45" s="63"/>
-      <c r="AM45" s="66"/>
-      <c r="AN45" s="67"/>
-      <c r="AO45" s="59" t="str">
+      <c r="AG45" s="71"/>
+      <c r="AK45" s="71"/>
+      <c r="AM45" s="61"/>
+      <c r="AN45" s="62"/>
+      <c r="AO45" s="55" t="str">
         <f>+_xlfn.XLOOKUP(AM44,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="AP45" s="5"/>
-      <c r="AQ45" s="63"/>
+      <c r="AQ45" s="71"/>
       <c r="AS45" s="25"/>
     </row>
     <row r="46" spans="19:50" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S46" s="84"/>
-      <c r="T46" s="85"/>
-      <c r="U46" s="85"/>
-      <c r="V46" s="85"/>
-      <c r="W46" s="86"/>
+      <c r="S46" s="81"/>
+      <c r="T46" s="82"/>
+      <c r="U46" s="82"/>
+      <c r="V46" s="82"/>
+      <c r="W46" s="83"/>
       <c r="Y46" s="17"/>
-      <c r="AA46" s="63"/>
-      <c r="AC46" s="68"/>
-      <c r="AD46" s="69"/>
-      <c r="AE46" s="77"/>
+      <c r="AA46" s="71"/>
+      <c r="AC46" s="63"/>
+      <c r="AD46" s="64"/>
+      <c r="AE46" s="58"/>
       <c r="AF46" s="5"/>
-      <c r="AG46" s="63"/>
+      <c r="AG46" s="71"/>
       <c r="AH46" s="5"/>
       <c r="AI46" s="5"/>
       <c r="AJ46" s="5"/>
-      <c r="AK46" s="63"/>
-      <c r="AM46" s="68"/>
-      <c r="AN46" s="69"/>
-      <c r="AO46" s="60"/>
+      <c r="AK46" s="71"/>
+      <c r="AM46" s="63"/>
+      <c r="AN46" s="64"/>
+      <c r="AO46" s="56"/>
       <c r="AP46" s="5"/>
-      <c r="AQ46" s="63"/>
+      <c r="AQ46" s="71"/>
       <c r="AS46" s="25"/>
     </row>
     <row r="47" spans="19:50" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="S47" s="84"/>
-      <c r="T47" s="85"/>
-      <c r="U47" s="85"/>
-      <c r="V47" s="85"/>
-      <c r="W47" s="86"/>
+      <c r="S47" s="81"/>
+      <c r="T47" s="82"/>
+      <c r="U47" s="82"/>
+      <c r="V47" s="82"/>
+      <c r="W47" s="83"/>
       <c r="Y47" s="17"/>
-      <c r="AA47" s="63"/>
+      <c r="AA47" s="71"/>
       <c r="AC47" s="5"/>
       <c r="AD47" s="5"/>
       <c r="AE47" s="5"/>
       <c r="AF47" s="5"/>
-      <c r="AG47" s="63"/>
+      <c r="AG47" s="71"/>
       <c r="AH47" s="5"/>
       <c r="AI47" s="5"/>
       <c r="AJ47" s="5"/>
-      <c r="AK47" s="63"/>
+      <c r="AK47" s="71"/>
       <c r="AM47" s="5"/>
       <c r="AN47" s="5"/>
       <c r="AO47" s="5"/>
       <c r="AP47" s="5"/>
-      <c r="AQ47" s="63"/>
+      <c r="AQ47" s="71"/>
       <c r="AS47" s="25"/>
     </row>
     <row r="48" spans="19:50" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S48" s="84"/>
-      <c r="T48" s="85"/>
-      <c r="U48" s="85"/>
-      <c r="V48" s="85"/>
-      <c r="W48" s="86"/>
+      <c r="S48" s="81"/>
+      <c r="T48" s="82"/>
+      <c r="U48" s="82"/>
+      <c r="V48" s="82"/>
+      <c r="W48" s="83"/>
       <c r="Y48" s="17"/>
-      <c r="AA48" s="63"/>
+      <c r="AA48" s="71"/>
       <c r="AF48" s="5"/>
-      <c r="AG48" s="63"/>
+      <c r="AG48" s="71"/>
       <c r="AH48" s="5"/>
       <c r="AI48" s="5"/>
       <c r="AJ48" s="5"/>
-      <c r="AK48" s="63"/>
+      <c r="AK48" s="71"/>
       <c r="AP48" s="5"/>
-      <c r="AQ48" s="63"/>
+      <c r="AQ48" s="71"/>
       <c r="AS48" s="25"/>
     </row>
     <row r="49" spans="19:74" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="S49" s="84"/>
-      <c r="T49" s="85"/>
-      <c r="U49" s="85"/>
-      <c r="V49" s="85"/>
-      <c r="W49" s="86"/>
+      <c r="S49" s="81"/>
+      <c r="T49" s="82"/>
+      <c r="U49" s="82"/>
+      <c r="V49" s="82"/>
+      <c r="W49" s="83"/>
       <c r="Y49" s="17"/>
       <c r="AA49" s="43">
         <f>+_xlfn.XLOOKUP(AA44,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.80499999999999994</v>
       </c>
-      <c r="AC49" s="64" t="s">
+      <c r="AC49" s="59" t="s">
         <v>147</v>
       </c>
-      <c r="AD49" s="65"/>
+      <c r="AD49" s="60"/>
       <c r="AE49" s="44">
         <f>+_xlfn.XLOOKUP(AC49,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.63</v>
@@ -5447,10 +5443,10 @@
         <f>+_xlfn.XLOOKUP(AK44,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.83499999999999996</v>
       </c>
-      <c r="AM49" s="64" t="s">
+      <c r="AM49" s="59" t="s">
         <v>132</v>
       </c>
-      <c r="AN49" s="65"/>
+      <c r="AN49" s="60"/>
       <c r="AO49" s="41">
         <f>+_xlfn.XLOOKUP(AM49,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.95499999999999985</v>
@@ -5463,67 +5459,67 @@
       <c r="AS49" s="25"/>
     </row>
     <row r="50" spans="19:74" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="S50" s="84"/>
-      <c r="T50" s="85"/>
-      <c r="U50" s="85"/>
-      <c r="V50" s="85"/>
-      <c r="W50" s="86"/>
+      <c r="S50" s="81"/>
+      <c r="T50" s="82"/>
+      <c r="U50" s="82"/>
+      <c r="V50" s="82"/>
+      <c r="W50" s="83"/>
       <c r="Y50" s="17"/>
-      <c r="AA50" s="49" t="str">
+      <c r="AA50" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AA44,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
-      <c r="AC50" s="66"/>
-      <c r="AD50" s="67"/>
-      <c r="AE50" s="76" t="str">
+      <c r="AC50" s="61"/>
+      <c r="AD50" s="62"/>
+      <c r="AE50" s="57" t="str">
         <f>+_xlfn.XLOOKUP(AC49,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="AF50" s="5"/>
-      <c r="AG50" s="49" t="str">
+      <c r="AG50" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AG44,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AH50" s="5"/>
       <c r="AI50" s="5"/>
       <c r="AJ50" s="5"/>
-      <c r="AK50" s="49" t="str">
+      <c r="AK50" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AK44,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
-      <c r="AM50" s="66"/>
-      <c r="AN50" s="67"/>
-      <c r="AO50" s="59" t="str">
+      <c r="AM50" s="61"/>
+      <c r="AN50" s="62"/>
+      <c r="AO50" s="55" t="str">
         <f>+_xlfn.XLOOKUP(AM49,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AP50" s="5"/>
-      <c r="AQ50" s="49" t="str">
+      <c r="AQ50" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AQ44,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AS50" s="25"/>
     </row>
     <row r="51" spans="19:74" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S51" s="84"/>
-      <c r="T51" s="85"/>
-      <c r="U51" s="85"/>
-      <c r="V51" s="85"/>
-      <c r="W51" s="86"/>
+      <c r="S51" s="81"/>
+      <c r="T51" s="82"/>
+      <c r="U51" s="82"/>
+      <c r="V51" s="82"/>
+      <c r="W51" s="83"/>
       <c r="Y51" s="17"/>
-      <c r="AA51" s="50"/>
-      <c r="AC51" s="68"/>
-      <c r="AD51" s="69"/>
-      <c r="AE51" s="77"/>
+      <c r="AA51" s="66"/>
+      <c r="AC51" s="63"/>
+      <c r="AD51" s="64"/>
+      <c r="AE51" s="58"/>
       <c r="AF51" s="5"/>
-      <c r="AG51" s="50"/>
+      <c r="AG51" s="66"/>
       <c r="AH51" s="5"/>
-      <c r="AK51" s="50"/>
-      <c r="AM51" s="68"/>
-      <c r="AN51" s="69"/>
-      <c r="AO51" s="60"/>
+      <c r="AK51" s="66"/>
+      <c r="AM51" s="63"/>
+      <c r="AN51" s="64"/>
+      <c r="AO51" s="56"/>
       <c r="AP51" s="5"/>
-      <c r="AQ51" s="50"/>
+      <c r="AQ51" s="66"/>
       <c r="AS51" s="25"/>
       <c r="AX51"/>
       <c r="AY51"/>
@@ -5540,11 +5536,11 @@
       <c r="BV51"/>
     </row>
     <row r="52" spans="19:74" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S52" s="84"/>
-      <c r="T52" s="85"/>
-      <c r="U52" s="85"/>
-      <c r="V52" s="85"/>
-      <c r="W52" s="86"/>
+      <c r="S52" s="81"/>
+      <c r="T52" s="82"/>
+      <c r="U52" s="82"/>
+      <c r="V52" s="82"/>
+      <c r="W52" s="83"/>
       <c r="Y52" s="17"/>
       <c r="AH52" s="5"/>
       <c r="AS52" s="25"/>
@@ -5563,39 +5559,39 @@
       <c r="BV52"/>
     </row>
     <row r="53" spans="19:74" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="S53" s="84"/>
-      <c r="T53" s="85"/>
-      <c r="U53" s="85"/>
-      <c r="V53" s="85"/>
-      <c r="W53" s="86"/>
+      <c r="S53" s="81"/>
+      <c r="T53" s="82"/>
+      <c r="U53" s="82"/>
+      <c r="V53" s="82"/>
+      <c r="W53" s="83"/>
       <c r="Y53" s="17"/>
-      <c r="AA53" s="62" t="s">
+      <c r="AA53" s="70" t="s">
         <v>133</v>
       </c>
-      <c r="AC53" s="64"/>
-      <c r="AD53" s="65"/>
+      <c r="AC53" s="59"/>
+      <c r="AD53" s="60"/>
       <c r="AE53" s="44" t="str">
         <f>+_xlfn.XLOOKUP(AC53,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
       </c>
       <c r="AF53" s="5"/>
-      <c r="AG53" s="62" t="s">
+      <c r="AG53" s="70" t="s">
         <v>159</v>
       </c>
       <c r="AH53" s="5"/>
-      <c r="AK53" s="62" t="s">
+      <c r="AK53" s="70" t="s">
         <v>121</v>
       </c>
-      <c r="AM53" s="64" t="s">
+      <c r="AM53" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="AN53" s="65"/>
+      <c r="AN53" s="60"/>
       <c r="AO53" s="41">
         <f>+_xlfn.XLOOKUP(AM53,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.97499999999999987</v>
       </c>
       <c r="AP53" s="5"/>
-      <c r="AQ53" s="62" t="s">
+      <c r="AQ53" s="70" t="s">
         <v>124</v>
       </c>
       <c r="AS53" s="25"/>
@@ -5626,30 +5622,30 @@
       <c r="BV53"/>
     </row>
     <row r="54" spans="19:74" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="S54" s="84"/>
-      <c r="T54" s="85"/>
-      <c r="U54" s="85"/>
-      <c r="V54" s="85"/>
-      <c r="W54" s="86"/>
+      <c r="S54" s="81"/>
+      <c r="T54" s="82"/>
+      <c r="U54" s="82"/>
+      <c r="V54" s="82"/>
+      <c r="W54" s="83"/>
       <c r="Y54" s="17"/>
-      <c r="AA54" s="63"/>
-      <c r="AC54" s="66"/>
-      <c r="AD54" s="67"/>
-      <c r="AE54" s="76" t="str">
+      <c r="AA54" s="71"/>
+      <c r="AC54" s="61"/>
+      <c r="AD54" s="62"/>
+      <c r="AE54" s="57" t="str">
         <f>+_xlfn.XLOOKUP(AC53,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="AF54" s="5"/>
-      <c r="AG54" s="63"/>
-      <c r="AK54" s="63"/>
-      <c r="AM54" s="66"/>
-      <c r="AN54" s="67"/>
-      <c r="AO54" s="59" t="str">
+      <c r="AG54" s="71"/>
+      <c r="AK54" s="71"/>
+      <c r="AM54" s="61"/>
+      <c r="AN54" s="62"/>
+      <c r="AO54" s="55" t="str">
         <f>+_xlfn.XLOOKUP(AM53,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AP54" s="5"/>
-      <c r="AQ54" s="63"/>
+      <c r="AQ54" s="71"/>
       <c r="AS54" s="25"/>
       <c r="AX54"/>
       <c r="AY54"/>
@@ -5666,24 +5662,24 @@
       <c r="BV54"/>
     </row>
     <row r="55" spans="19:74" ht="24" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S55" s="84"/>
-      <c r="T55" s="85"/>
-      <c r="U55" s="85"/>
-      <c r="V55" s="85"/>
-      <c r="W55" s="86"/>
+      <c r="S55" s="81"/>
+      <c r="T55" s="82"/>
+      <c r="U55" s="82"/>
+      <c r="V55" s="82"/>
+      <c r="W55" s="83"/>
       <c r="Y55" s="17"/>
-      <c r="AA55" s="63"/>
-      <c r="AC55" s="68"/>
-      <c r="AD55" s="69"/>
-      <c r="AE55" s="77"/>
+      <c r="AA55" s="71"/>
+      <c r="AC55" s="63"/>
+      <c r="AD55" s="64"/>
+      <c r="AE55" s="58"/>
       <c r="AF55" s="5"/>
-      <c r="AG55" s="63"/>
-      <c r="AK55" s="63"/>
-      <c r="AM55" s="68"/>
-      <c r="AN55" s="69"/>
-      <c r="AO55" s="60"/>
+      <c r="AG55" s="71"/>
+      <c r="AK55" s="71"/>
+      <c r="AM55" s="63"/>
+      <c r="AN55" s="64"/>
+      <c r="AO55" s="56"/>
       <c r="AP55" s="5"/>
-      <c r="AQ55" s="63"/>
+      <c r="AQ55" s="71"/>
       <c r="AS55" s="25"/>
       <c r="AX55"/>
       <c r="AY55"/>
@@ -5712,68 +5708,68 @@
       <c r="BV55"/>
     </row>
     <row r="56" spans="19:74" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="S56" s="84"/>
-      <c r="T56" s="85"/>
-      <c r="U56" s="85"/>
-      <c r="V56" s="85"/>
-      <c r="W56" s="86"/>
+      <c r="S56" s="81"/>
+      <c r="T56" s="82"/>
+      <c r="U56" s="82"/>
+      <c r="V56" s="82"/>
+      <c r="W56" s="83"/>
       <c r="Y56" s="17"/>
-      <c r="AA56" s="63"/>
+      <c r="AA56" s="71"/>
       <c r="AC56" s="5"/>
       <c r="AD56" s="5"/>
       <c r="AE56" s="5"/>
       <c r="AF56" s="5"/>
-      <c r="AG56" s="63"/>
-      <c r="AK56" s="63"/>
+      <c r="AG56" s="71"/>
+      <c r="AK56" s="71"/>
       <c r="AM56" s="5"/>
       <c r="AN56" s="5"/>
       <c r="AO56" s="5"/>
       <c r="AP56" s="5"/>
-      <c r="AQ56" s="63"/>
+      <c r="AQ56" s="71"/>
       <c r="AS56" s="25"/>
       <c r="AX56"/>
       <c r="AY56"/>
       <c r="AZ56" s="29"/>
-      <c r="BA56" s="53" t="s">
+      <c r="BA56" s="49" t="s">
         <v>158</v>
       </c>
-      <c r="BB56" s="54"/>
+      <c r="BB56" s="50"/>
       <c r="BC56" s="41">
         <f>+_xlfn.XLOOKUP(BA56,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.56999999999999995</v>
       </c>
       <c r="BD56"/>
-      <c r="BE56" s="53" t="s">
+      <c r="BE56" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="BF56" s="54"/>
+      <c r="BF56" s="50"/>
       <c r="BG56" s="41">
         <f>+_xlfn.XLOOKUP(BE56,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.57999999999999996</v>
       </c>
       <c r="BH56"/>
-      <c r="BI56" s="70" t="s">
+      <c r="BI56" s="72" t="s">
         <v>142</v>
       </c>
-      <c r="BJ56" s="71"/>
+      <c r="BJ56" s="73"/>
       <c r="BK56" s="41">
         <f>+_xlfn.XLOOKUP(BI56,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.59</v>
       </c>
       <c r="BL56"/>
-      <c r="BM56" s="70" t="s">
+      <c r="BM56" s="72" t="s">
         <v>119</v>
       </c>
-      <c r="BN56" s="71"/>
+      <c r="BN56" s="73"/>
       <c r="BO56" s="41">
         <f>+_xlfn.XLOOKUP(BM56,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.86499999999999999</v>
       </c>
       <c r="BP56"/>
-      <c r="BQ56" s="70" t="s">
+      <c r="BQ56" s="72" t="s">
         <v>114</v>
       </c>
-      <c r="BR56" s="71"/>
+      <c r="BR56" s="73"/>
       <c r="BS56" s="41">
         <f>+_xlfn.XLOOKUP(BQ56,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.98499999999999988</v>
@@ -5783,56 +5779,56 @@
       <c r="BV56"/>
     </row>
     <row r="57" spans="19:74" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S57" s="84"/>
-      <c r="T57" s="85"/>
-      <c r="U57" s="85"/>
-      <c r="V57" s="85"/>
-      <c r="W57" s="86"/>
+      <c r="S57" s="81"/>
+      <c r="T57" s="82"/>
+      <c r="U57" s="82"/>
+      <c r="V57" s="82"/>
+      <c r="W57" s="83"/>
       <c r="Y57" s="17"/>
-      <c r="AA57" s="63"/>
+      <c r="AA57" s="71"/>
       <c r="AF57" s="5"/>
-      <c r="AG57" s="63"/>
+      <c r="AG57" s="71"/>
       <c r="AH57" s="5"/>
       <c r="AI57" s="5"/>
       <c r="AJ57" s="5"/>
-      <c r="AK57" s="63"/>
+      <c r="AK57" s="71"/>
       <c r="AP57" s="5"/>
-      <c r="AQ57" s="63"/>
+      <c r="AQ57" s="71"/>
       <c r="AS57" s="25"/>
       <c r="AX57"/>
       <c r="AY57"/>
       <c r="AZ57" s="29"/>
-      <c r="BA57" s="55"/>
-      <c r="BB57" s="56"/>
-      <c r="BC57" s="59" t="str">
+      <c r="BA57" s="51"/>
+      <c r="BB57" s="52"/>
+      <c r="BC57" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BA56,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="BD57"/>
-      <c r="BE57" s="55"/>
-      <c r="BF57" s="56"/>
-      <c r="BG57" s="59" t="str">
+      <c r="BE57" s="51"/>
+      <c r="BF57" s="52"/>
+      <c r="BG57" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BE56,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="BH57"/>
-      <c r="BI57" s="72"/>
-      <c r="BJ57" s="73"/>
-      <c r="BK57" s="59" t="str">
+      <c r="BI57" s="74"/>
+      <c r="BJ57" s="75"/>
+      <c r="BK57" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BI56,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="BL57"/>
-      <c r="BM57" s="72"/>
-      <c r="BN57" s="73"/>
-      <c r="BO57" s="59" t="str">
+      <c r="BM57" s="74"/>
+      <c r="BN57" s="75"/>
+      <c r="BO57" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BM56,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="BP57"/>
-      <c r="BQ57" s="72"/>
-      <c r="BR57" s="73"/>
-      <c r="BS57" s="59" t="str">
+      <c r="BQ57" s="74"/>
+      <c r="BR57" s="75"/>
+      <c r="BS57" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BQ56,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
@@ -5841,20 +5837,20 @@
       <c r="BV57"/>
     </row>
     <row r="58" spans="19:74" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S58" s="84"/>
-      <c r="T58" s="85"/>
-      <c r="U58" s="85"/>
-      <c r="V58" s="85"/>
-      <c r="W58" s="86"/>
+      <c r="S58" s="81"/>
+      <c r="T58" s="82"/>
+      <c r="U58" s="82"/>
+      <c r="V58" s="82"/>
+      <c r="W58" s="83"/>
       <c r="Y58" s="17"/>
       <c r="AA58" s="43">
         <f>+_xlfn.XLOOKUP(AA53,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.94999999999999984</v>
       </c>
-      <c r="AC58" s="64" t="s">
+      <c r="AC58" s="59" t="s">
         <v>143</v>
       </c>
-      <c r="AD58" s="65"/>
+      <c r="AD58" s="60"/>
       <c r="AE58" s="44">
         <f>+_xlfn.XLOOKUP(AC58,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.7</v>
@@ -5869,10 +5865,10 @@
         <f>+_xlfn.XLOOKUP(AK53,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.97499999999999987</v>
       </c>
-      <c r="AM58" s="64" t="s">
+      <c r="AM58" s="59" t="s">
         <v>146</v>
       </c>
-      <c r="AN58" s="65"/>
+      <c r="AN58" s="60"/>
       <c r="AO58" s="41">
         <f>+_xlfn.XLOOKUP(AM58,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.69</v>
@@ -5883,73 +5879,73 @@
         <v>0.96999999999999975</v>
       </c>
       <c r="AS58" s="25"/>
-      <c r="AU58" s="62"/>
+      <c r="AU58" s="70"/>
       <c r="AX58"/>
       <c r="AY58"/>
       <c r="AZ58" s="29"/>
-      <c r="BA58" s="57"/>
-      <c r="BB58" s="58"/>
-      <c r="BC58" s="60"/>
+      <c r="BA58" s="53"/>
+      <c r="BB58" s="54"/>
+      <c r="BC58" s="56"/>
       <c r="BD58"/>
-      <c r="BE58" s="57"/>
-      <c r="BF58" s="58"/>
-      <c r="BG58" s="60"/>
+      <c r="BE58" s="53"/>
+      <c r="BF58" s="54"/>
+      <c r="BG58" s="56"/>
       <c r="BH58"/>
-      <c r="BI58" s="74"/>
-      <c r="BJ58" s="75"/>
-      <c r="BK58" s="60"/>
+      <c r="BI58" s="76"/>
+      <c r="BJ58" s="77"/>
+      <c r="BK58" s="56"/>
       <c r="BL58"/>
-      <c r="BM58" s="74"/>
-      <c r="BN58" s="75"/>
-      <c r="BO58" s="60"/>
+      <c r="BM58" s="76"/>
+      <c r="BN58" s="77"/>
+      <c r="BO58" s="56"/>
       <c r="BP58"/>
-      <c r="BQ58" s="74"/>
-      <c r="BR58" s="75"/>
-      <c r="BS58" s="60"/>
+      <c r="BQ58" s="76"/>
+      <c r="BR58" s="77"/>
+      <c r="BS58" s="56"/>
       <c r="BT58" s="22"/>
       <c r="BU58"/>
       <c r="BV58"/>
     </row>
     <row r="59" spans="19:74" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S59" s="84"/>
-      <c r="T59" s="85"/>
-      <c r="U59" s="85"/>
-      <c r="V59" s="85"/>
-      <c r="W59" s="86"/>
+      <c r="S59" s="81"/>
+      <c r="T59" s="82"/>
+      <c r="U59" s="82"/>
+      <c r="V59" s="82"/>
+      <c r="W59" s="83"/>
       <c r="Y59" s="17"/>
-      <c r="AA59" s="49" t="str">
+      <c r="AA59" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AA53,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
-      <c r="AC59" s="66"/>
-      <c r="AD59" s="67"/>
-      <c r="AE59" s="76" t="str">
+      <c r="AC59" s="61"/>
+      <c r="AD59" s="62"/>
+      <c r="AE59" s="57" t="str">
         <f>+_xlfn.XLOOKUP(AC58,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="AF59" s="5"/>
-      <c r="AG59" s="49" t="str">
+      <c r="AG59" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AG53,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="AJ59" s="5"/>
-      <c r="AK59" s="49" t="str">
+      <c r="AK59" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AK53,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
-      <c r="AM59" s="66"/>
-      <c r="AN59" s="67"/>
-      <c r="AO59" s="59" t="str">
+      <c r="AM59" s="61"/>
+      <c r="AN59" s="62"/>
+      <c r="AO59" s="55" t="str">
         <f>+_xlfn.XLOOKUP(AM58,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="AP59" s="5"/>
-      <c r="AQ59" s="49" t="str">
+      <c r="AQ59" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AQ53,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AS59" s="25"/>
-      <c r="AU59" s="63"/>
+      <c r="AU59" s="71"/>
       <c r="AX59"/>
       <c r="AY59"/>
       <c r="AZ59" s="29"/>
@@ -5977,54 +5973,54 @@
       <c r="BV59"/>
     </row>
     <row r="60" spans="19:74" ht="24" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S60" s="84"/>
-      <c r="T60" s="85"/>
-      <c r="U60" s="85"/>
-      <c r="V60" s="85"/>
-      <c r="W60" s="86"/>
+      <c r="S60" s="81"/>
+      <c r="T60" s="82"/>
+      <c r="U60" s="82"/>
+      <c r="V60" s="82"/>
+      <c r="W60" s="83"/>
       <c r="Y60" s="17"/>
-      <c r="AA60" s="50"/>
-      <c r="AC60" s="68"/>
-      <c r="AD60" s="69"/>
-      <c r="AE60" s="77"/>
+      <c r="AA60" s="66"/>
+      <c r="AC60" s="63"/>
+      <c r="AD60" s="64"/>
+      <c r="AE60" s="58"/>
       <c r="AF60" s="5"/>
-      <c r="AG60" s="50"/>
-      <c r="AK60" s="50"/>
-      <c r="AM60" s="68"/>
-      <c r="AN60" s="69"/>
-      <c r="AO60" s="60"/>
+      <c r="AG60" s="66"/>
+      <c r="AK60" s="66"/>
+      <c r="AM60" s="63"/>
+      <c r="AN60" s="64"/>
+      <c r="AO60" s="56"/>
       <c r="AP60" s="5"/>
-      <c r="AQ60" s="50"/>
+      <c r="AQ60" s="66"/>
       <c r="AS60" s="25"/>
-      <c r="AU60" s="63"/>
+      <c r="AU60" s="71"/>
       <c r="AX60"/>
       <c r="AY60"/>
       <c r="AZ60" s="29"/>
-      <c r="BA60" s="61"/>
+      <c r="BA60" s="67"/>
       <c r="BB60"/>
-      <c r="BC60" s="61"/>
+      <c r="BC60" s="67"/>
       <c r="BD60"/>
-      <c r="BE60" s="61"/>
+      <c r="BE60" s="67"/>
       <c r="BF60"/>
-      <c r="BG60" s="61"/>
+      <c r="BG60" s="67"/>
       <c r="BH60"/>
-      <c r="BI60" s="61"/>
+      <c r="BI60" s="67"/>
       <c r="BJ60"/>
-      <c r="BK60" s="61"/>
+      <c r="BK60" s="67"/>
       <c r="BL60"/>
-      <c r="BM60" s="61" t="s">
+      <c r="BM60" s="67" t="s">
         <v>129</v>
       </c>
       <c r="BN60"/>
-      <c r="BO60" s="61" t="s">
+      <c r="BO60" s="67" t="s">
         <v>127</v>
       </c>
       <c r="BP60"/>
-      <c r="BQ60" s="61" t="s">
+      <c r="BQ60" s="67" t="s">
         <v>123</v>
       </c>
       <c r="BR60"/>
-      <c r="BS60" s="61" t="s">
+      <c r="BS60" s="67" t="s">
         <v>118</v>
       </c>
       <c r="BT60" s="22"/>
@@ -6032,130 +6028,130 @@
       <c r="BV60"/>
     </row>
     <row r="61" spans="19:74" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S61" s="84"/>
-      <c r="T61" s="85"/>
-      <c r="U61" s="85"/>
-      <c r="V61" s="85"/>
-      <c r="W61" s="86"/>
+      <c r="S61" s="81"/>
+      <c r="T61" s="82"/>
+      <c r="U61" s="82"/>
+      <c r="V61" s="82"/>
+      <c r="W61" s="83"/>
       <c r="Y61" s="17"/>
       <c r="AS61" s="25"/>
-      <c r="AU61" s="63"/>
+      <c r="AU61" s="71"/>
       <c r="AX61"/>
       <c r="AY61"/>
       <c r="AZ61" s="29"/>
-      <c r="BA61" s="51"/>
+      <c r="BA61" s="68"/>
       <c r="BB61"/>
-      <c r="BC61" s="51"/>
+      <c r="BC61" s="68"/>
       <c r="BD61"/>
-      <c r="BE61" s="51"/>
+      <c r="BE61" s="68"/>
       <c r="BF61"/>
-      <c r="BG61" s="51"/>
+      <c r="BG61" s="68"/>
       <c r="BH61"/>
-      <c r="BI61" s="51"/>
+      <c r="BI61" s="68"/>
       <c r="BJ61"/>
-      <c r="BK61" s="51"/>
+      <c r="BK61" s="68"/>
       <c r="BL61"/>
-      <c r="BM61" s="51"/>
+      <c r="BM61" s="68"/>
       <c r="BN61"/>
-      <c r="BO61" s="51"/>
+      <c r="BO61" s="68"/>
       <c r="BP61"/>
-      <c r="BQ61" s="51"/>
+      <c r="BQ61" s="68"/>
       <c r="BR61"/>
-      <c r="BS61" s="51"/>
+      <c r="BS61" s="68"/>
       <c r="BT61" s="22"/>
       <c r="BU61"/>
       <c r="BV61"/>
     </row>
     <row r="62" spans="19:74" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="S62" s="84"/>
-      <c r="T62" s="85"/>
-      <c r="U62" s="85"/>
-      <c r="V62" s="85"/>
-      <c r="W62" s="86"/>
+      <c r="S62" s="81"/>
+      <c r="T62" s="82"/>
+      <c r="U62" s="82"/>
+      <c r="V62" s="82"/>
+      <c r="W62" s="83"/>
       <c r="Y62" s="17"/>
-      <c r="AA62" s="62" t="s">
+      <c r="AA62" s="70" t="s">
         <v>137</v>
       </c>
-      <c r="AC62" s="64" t="s">
+      <c r="AC62" s="59" t="s">
         <v>153</v>
       </c>
-      <c r="AD62" s="65"/>
+      <c r="AD62" s="60"/>
       <c r="AE62" s="44">
         <f>+_xlfn.XLOOKUP(AC62,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.78499999999999992</v>
       </c>
       <c r="AF62" s="5"/>
-      <c r="AG62" s="62" t="s">
+      <c r="AG62" s="70" t="s">
         <v>134</v>
       </c>
-      <c r="AK62" s="62" t="s">
+      <c r="AK62" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AM62" s="64" t="s">
+      <c r="AM62" s="59" t="s">
         <v>151</v>
       </c>
-      <c r="AN62" s="65"/>
+      <c r="AN62" s="60"/>
       <c r="AO62" s="44">
         <f>+_xlfn.XLOOKUP(AM62,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.66999999999999993</v>
       </c>
       <c r="AP62" s="5"/>
-      <c r="AQ62" s="62" t="s">
+      <c r="AQ62" s="70" t="s">
         <v>140</v>
       </c>
       <c r="AS62" s="25"/>
-      <c r="AU62" s="63"/>
+      <c r="AU62" s="71"/>
       <c r="AX62"/>
       <c r="AY62"/>
       <c r="AZ62" s="29"/>
-      <c r="BA62" s="51"/>
+      <c r="BA62" s="68"/>
       <c r="BB62"/>
-      <c r="BC62" s="51"/>
+      <c r="BC62" s="68"/>
       <c r="BD62"/>
-      <c r="BE62" s="51"/>
+      <c r="BE62" s="68"/>
       <c r="BF62"/>
-      <c r="BG62" s="51"/>
+      <c r="BG62" s="68"/>
       <c r="BH62"/>
-      <c r="BI62" s="51"/>
+      <c r="BI62" s="68"/>
       <c r="BJ62"/>
-      <c r="BK62" s="51"/>
+      <c r="BK62" s="68"/>
       <c r="BL62"/>
-      <c r="BM62" s="51"/>
+      <c r="BM62" s="68"/>
       <c r="BN62"/>
-      <c r="BO62" s="51"/>
+      <c r="BO62" s="68"/>
       <c r="BP62"/>
-      <c r="BQ62" s="51"/>
+      <c r="BQ62" s="68"/>
       <c r="BR62"/>
-      <c r="BS62" s="51"/>
+      <c r="BS62" s="68"/>
       <c r="BT62" s="22"/>
       <c r="BU62"/>
       <c r="BV62"/>
     </row>
     <row r="63" spans="19:74" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="S63" s="84"/>
-      <c r="T63" s="85"/>
-      <c r="U63" s="85"/>
-      <c r="V63" s="85"/>
-      <c r="W63" s="86"/>
+      <c r="S63" s="81"/>
+      <c r="T63" s="82"/>
+      <c r="U63" s="82"/>
+      <c r="V63" s="82"/>
+      <c r="W63" s="83"/>
       <c r="Y63" s="17"/>
-      <c r="AA63" s="63"/>
-      <c r="AC63" s="66"/>
-      <c r="AD63" s="67"/>
-      <c r="AE63" s="76" t="str">
+      <c r="AA63" s="71"/>
+      <c r="AC63" s="61"/>
+      <c r="AD63" s="62"/>
+      <c r="AE63" s="57" t="str">
         <f>+_xlfn.XLOOKUP(AC62,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AF63" s="5"/>
-      <c r="AG63" s="63"/>
-      <c r="AK63" s="63"/>
-      <c r="AM63" s="66"/>
-      <c r="AN63" s="67"/>
-      <c r="AO63" s="76" t="str">
+      <c r="AG63" s="71"/>
+      <c r="AK63" s="71"/>
+      <c r="AM63" s="61"/>
+      <c r="AN63" s="62"/>
+      <c r="AO63" s="57" t="str">
         <f>+_xlfn.XLOOKUP(AM62,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="AP63" s="5"/>
-      <c r="AQ63" s="63"/>
+      <c r="AQ63" s="71"/>
       <c r="AS63" s="25"/>
       <c r="AU63" s="43" t="str">
         <f>+_xlfn.XLOOKUP(AU58,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
@@ -6164,100 +6160,100 @@
       <c r="AX63"/>
       <c r="AY63"/>
       <c r="AZ63" s="29"/>
-      <c r="BA63" s="51"/>
+      <c r="BA63" s="68"/>
       <c r="BB63"/>
-      <c r="BC63" s="51"/>
+      <c r="BC63" s="68"/>
       <c r="BD63"/>
-      <c r="BE63" s="51"/>
+      <c r="BE63" s="68"/>
       <c r="BF63"/>
-      <c r="BG63" s="51"/>
+      <c r="BG63" s="68"/>
       <c r="BH63"/>
-      <c r="BI63" s="51"/>
+      <c r="BI63" s="68"/>
       <c r="BJ63"/>
-      <c r="BK63" s="51"/>
+      <c r="BK63" s="68"/>
       <c r="BL63"/>
-      <c r="BM63" s="51"/>
+      <c r="BM63" s="68"/>
       <c r="BN63"/>
-      <c r="BO63" s="51"/>
+      <c r="BO63" s="68"/>
       <c r="BP63"/>
-      <c r="BQ63" s="51"/>
+      <c r="BQ63" s="68"/>
       <c r="BR63"/>
-      <c r="BS63" s="51"/>
+      <c r="BS63" s="68"/>
       <c r="BT63" s="22"/>
       <c r="BU63"/>
       <c r="BV63"/>
     </row>
     <row r="64" spans="19:74" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S64" s="84"/>
-      <c r="T64" s="85"/>
-      <c r="U64" s="85"/>
-      <c r="V64" s="85"/>
-      <c r="W64" s="86"/>
+      <c r="S64" s="81"/>
+      <c r="T64" s="82"/>
+      <c r="U64" s="82"/>
+      <c r="V64" s="82"/>
+      <c r="W64" s="83"/>
       <c r="Y64" s="17"/>
-      <c r="AA64" s="63"/>
-      <c r="AC64" s="68"/>
-      <c r="AD64" s="69"/>
-      <c r="AE64" s="77"/>
+      <c r="AA64" s="71"/>
+      <c r="AC64" s="63"/>
+      <c r="AD64" s="64"/>
+      <c r="AE64" s="58"/>
       <c r="AF64" s="5"/>
-      <c r="AG64" s="63"/>
-      <c r="AK64" s="63"/>
-      <c r="AM64" s="68"/>
-      <c r="AN64" s="69"/>
-      <c r="AO64" s="77"/>
+      <c r="AG64" s="71"/>
+      <c r="AK64" s="71"/>
+      <c r="AM64" s="63"/>
+      <c r="AN64" s="64"/>
+      <c r="AO64" s="58"/>
       <c r="AP64" s="5"/>
-      <c r="AQ64" s="63"/>
+      <c r="AQ64" s="71"/>
       <c r="AS64" s="25"/>
-      <c r="AU64" s="49" t="str">
+      <c r="AU64" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AU58,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="AX64"/>
       <c r="AY64"/>
       <c r="AZ64" s="29"/>
-      <c r="BA64" s="51"/>
+      <c r="BA64" s="68"/>
       <c r="BB64"/>
-      <c r="BC64" s="51"/>
+      <c r="BC64" s="68"/>
       <c r="BD64"/>
-      <c r="BE64" s="51"/>
+      <c r="BE64" s="68"/>
       <c r="BF64"/>
-      <c r="BG64" s="51"/>
+      <c r="BG64" s="68"/>
       <c r="BH64"/>
-      <c r="BI64" s="51"/>
+      <c r="BI64" s="68"/>
       <c r="BJ64"/>
-      <c r="BK64" s="51"/>
+      <c r="BK64" s="68"/>
       <c r="BL64"/>
-      <c r="BM64" s="51"/>
+      <c r="BM64" s="68"/>
       <c r="BN64"/>
-      <c r="BO64" s="51"/>
+      <c r="BO64" s="68"/>
       <c r="BP64"/>
-      <c r="BQ64" s="51"/>
+      <c r="BQ64" s="68"/>
       <c r="BR64"/>
-      <c r="BS64" s="51"/>
+      <c r="BS64" s="68"/>
       <c r="BT64" s="22"/>
       <c r="BU64"/>
       <c r="BV64"/>
     </row>
     <row r="65" spans="19:74" ht="24" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S65" s="84"/>
-      <c r="T65" s="85"/>
-      <c r="U65" s="85"/>
-      <c r="V65" s="85"/>
-      <c r="W65" s="86"/>
+      <c r="S65" s="81"/>
+      <c r="T65" s="82"/>
+      <c r="U65" s="82"/>
+      <c r="V65" s="82"/>
+      <c r="W65" s="83"/>
       <c r="Y65" s="17"/>
-      <c r="AA65" s="63"/>
+      <c r="AA65" s="71"/>
       <c r="AC65" s="5"/>
       <c r="AD65" s="5"/>
       <c r="AE65" s="5"/>
       <c r="AF65" s="5"/>
-      <c r="AG65" s="63"/>
-      <c r="AK65" s="63"/>
+      <c r="AG65" s="71"/>
+      <c r="AK65" s="71"/>
       <c r="AM65" s="5"/>
       <c r="AN65" s="5"/>
       <c r="AO65" s="5"/>
       <c r="AP65" s="5"/>
-      <c r="AQ65" s="63"/>
+      <c r="AQ65" s="71"/>
       <c r="AS65" s="25"/>
-      <c r="AU65" s="50"/>
+      <c r="AU65" s="66"/>
       <c r="AX65"/>
       <c r="AY65"/>
       <c r="AZ65" s="29"/>
@@ -6315,68 +6311,68 @@
       <c r="BV65"/>
     </row>
     <row r="66" spans="19:74" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S66" s="84"/>
-      <c r="T66" s="85"/>
-      <c r="U66" s="85"/>
-      <c r="V66" s="85"/>
-      <c r="W66" s="86"/>
+      <c r="S66" s="81"/>
+      <c r="T66" s="82"/>
+      <c r="U66" s="82"/>
+      <c r="V66" s="82"/>
+      <c r="W66" s="83"/>
       <c r="Y66" s="17"/>
-      <c r="AA66" s="63"/>
+      <c r="AA66" s="71"/>
       <c r="AF66" s="5"/>
-      <c r="AG66" s="63"/>
-      <c r="AK66" s="63"/>
+      <c r="AG66" s="71"/>
+      <c r="AK66" s="71"/>
       <c r="AP66" s="5"/>
-      <c r="AQ66" s="63"/>
+      <c r="AQ66" s="71"/>
       <c r="AS66" s="25"/>
       <c r="AX66"/>
       <c r="AY66"/>
       <c r="AZ66" s="29"/>
-      <c r="BA66" s="51" t="str">
+      <c r="BA66" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BA60,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BB66"/>
-      <c r="BC66" s="51" t="str">
+      <c r="BC66" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BC60,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BD66"/>
-      <c r="BE66" s="51" t="str">
+      <c r="BE66" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BE60,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BF66"/>
-      <c r="BG66" s="51" t="str">
+      <c r="BG66" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BG60,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BH66"/>
-      <c r="BI66" s="51" t="str">
+      <c r="BI66" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BI60,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BJ66"/>
-      <c r="BK66" s="51" t="str">
+      <c r="BK66" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BK60,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="BL66"/>
-      <c r="BM66" s="51" t="str">
+      <c r="BM66" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BM60,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="BN66"/>
-      <c r="BO66" s="51" t="str">
+      <c r="BO66" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BO60,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="BP66"/>
-      <c r="BQ66" s="51" t="str">
+      <c r="BQ66" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BQ60,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="BR66"/>
-      <c r="BS66" s="51" t="str">
+      <c r="BS66" s="68" t="str">
         <f>+_xlfn.XLOOKUP(BS60,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
@@ -6385,20 +6381,20 @@
       <c r="BV66"/>
     </row>
     <row r="67" spans="19:74" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S67" s="84"/>
-      <c r="T67" s="85"/>
-      <c r="U67" s="85"/>
-      <c r="V67" s="85"/>
-      <c r="W67" s="86"/>
+      <c r="S67" s="81"/>
+      <c r="T67" s="82"/>
+      <c r="U67" s="82"/>
+      <c r="V67" s="82"/>
+      <c r="W67" s="83"/>
       <c r="Y67" s="17"/>
       <c r="AA67" s="43">
         <f>+_xlfn.XLOOKUP(AA62,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.94</v>
       </c>
-      <c r="AC67" s="64" t="s">
+      <c r="AC67" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="AD67" s="65"/>
+      <c r="AD67" s="60"/>
       <c r="AE67" s="44">
         <f>+_xlfn.XLOOKUP(AC67,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.80499999999999994</v>
@@ -6412,10 +6408,10 @@
         <f>+_xlfn.XLOOKUP(AK62,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.91999999999999993</v>
       </c>
-      <c r="AM67" s="64" t="s">
+      <c r="AM67" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="AN67" s="65"/>
+      <c r="AN67" s="60"/>
       <c r="AO67" s="44">
         <f>+_xlfn.XLOOKUP(AM67,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.8899999999999999</v>
@@ -6429,63 +6425,63 @@
       <c r="AX67"/>
       <c r="AY67"/>
       <c r="AZ67" s="29"/>
-      <c r="BA67" s="52"/>
+      <c r="BA67" s="69"/>
       <c r="BB67"/>
-      <c r="BC67" s="52"/>
+      <c r="BC67" s="69"/>
       <c r="BD67"/>
-      <c r="BE67" s="52"/>
+      <c r="BE67" s="69"/>
       <c r="BF67"/>
-      <c r="BG67" s="52"/>
+      <c r="BG67" s="69"/>
       <c r="BH67"/>
-      <c r="BI67" s="52"/>
+      <c r="BI67" s="69"/>
       <c r="BJ67"/>
-      <c r="BK67" s="52"/>
+      <c r="BK67" s="69"/>
       <c r="BL67"/>
-      <c r="BM67" s="52"/>
+      <c r="BM67" s="69"/>
       <c r="BN67"/>
-      <c r="BO67" s="52"/>
+      <c r="BO67" s="69"/>
       <c r="BP67"/>
-      <c r="BQ67" s="52"/>
+      <c r="BQ67" s="69"/>
       <c r="BR67"/>
-      <c r="BS67" s="52"/>
+      <c r="BS67" s="69"/>
       <c r="BT67" s="22"/>
       <c r="BU67"/>
       <c r="BV67"/>
     </row>
     <row r="68" spans="19:74" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S68" s="84"/>
-      <c r="T68" s="85"/>
-      <c r="U68" s="85"/>
-      <c r="V68" s="85"/>
-      <c r="W68" s="86"/>
+      <c r="S68" s="81"/>
+      <c r="T68" s="82"/>
+      <c r="U68" s="82"/>
+      <c r="V68" s="82"/>
+      <c r="W68" s="83"/>
       <c r="Y68" s="17"/>
-      <c r="AA68" s="49" t="str">
+      <c r="AA68" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AA62,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
-      <c r="AC68" s="66"/>
-      <c r="AD68" s="67"/>
-      <c r="AE68" s="76" t="str">
+      <c r="AC68" s="61"/>
+      <c r="AD68" s="62"/>
+      <c r="AE68" s="57" t="str">
         <f>+_xlfn.XLOOKUP(AC67,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AF68" s="5"/>
-      <c r="AG68" s="49" t="str">
+      <c r="AG68" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AG62,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
-      <c r="AK68" s="49" t="str">
+      <c r="AK68" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AK62,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
-      <c r="AM68" s="66"/>
-      <c r="AN68" s="67"/>
-      <c r="AO68" s="76" t="str">
+      <c r="AM68" s="61"/>
+      <c r="AN68" s="62"/>
+      <c r="AO68" s="57" t="str">
         <f>+_xlfn.XLOOKUP(AM67,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AP68" s="5"/>
-      <c r="AQ68" s="49" t="str">
+      <c r="AQ68" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AQ62,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
@@ -6517,68 +6513,68 @@
       <c r="BV68"/>
     </row>
     <row r="69" spans="19:74" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S69" s="84"/>
-      <c r="T69" s="85"/>
-      <c r="U69" s="85"/>
-      <c r="V69" s="85"/>
-      <c r="W69" s="86"/>
+      <c r="S69" s="81"/>
+      <c r="T69" s="82"/>
+      <c r="U69" s="82"/>
+      <c r="V69" s="82"/>
+      <c r="W69" s="83"/>
       <c r="Y69" s="17"/>
-      <c r="AA69" s="50"/>
-      <c r="AC69" s="68"/>
-      <c r="AD69" s="69"/>
-      <c r="AE69" s="77"/>
+      <c r="AA69" s="66"/>
+      <c r="AC69" s="63"/>
+      <c r="AD69" s="64"/>
+      <c r="AE69" s="58"/>
       <c r="AF69" s="5"/>
-      <c r="AG69" s="50"/>
-      <c r="AK69" s="50"/>
-      <c r="AM69" s="68"/>
-      <c r="AN69" s="69"/>
-      <c r="AO69" s="77"/>
+      <c r="AG69" s="66"/>
+      <c r="AK69" s="66"/>
+      <c r="AM69" s="63"/>
+      <c r="AN69" s="64"/>
+      <c r="AO69" s="58"/>
       <c r="AP69" s="5"/>
-      <c r="AQ69" s="50"/>
+      <c r="AQ69" s="66"/>
       <c r="AS69" s="25"/>
       <c r="AX69"/>
       <c r="AY69"/>
       <c r="AZ69" s="29"/>
-      <c r="BA69" s="53" t="s">
+      <c r="BA69" s="49" t="s">
         <v>154</v>
       </c>
-      <c r="BB69" s="54"/>
+      <c r="BB69" s="50"/>
       <c r="BC69" s="41">
         <f>+_xlfn.XLOOKUP(BA69,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.59</v>
       </c>
       <c r="BD69"/>
-      <c r="BE69" s="53" t="s">
+      <c r="BE69" s="49" t="s">
         <v>150</v>
       </c>
-      <c r="BF69" s="54"/>
+      <c r="BF69" s="50"/>
       <c r="BG69" s="41">
         <f>+_xlfn.XLOOKUP(BE69,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.59</v>
       </c>
       <c r="BH69"/>
-      <c r="BI69" s="70" t="s">
+      <c r="BI69" s="72" t="s">
         <v>116</v>
       </c>
-      <c r="BJ69" s="71"/>
+      <c r="BJ69" s="73"/>
       <c r="BK69" s="41">
         <f>+_xlfn.XLOOKUP(BI69,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.98499999999999988</v>
       </c>
       <c r="BL69"/>
-      <c r="BM69" s="70" t="s">
+      <c r="BM69" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="BN69" s="71"/>
+      <c r="BN69" s="73"/>
       <c r="BO69" s="41">
         <f>+_xlfn.XLOOKUP(BM69,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.98499999999999988</v>
       </c>
       <c r="BP69"/>
-      <c r="BQ69" s="70" t="s">
+      <c r="BQ69" s="72" t="s">
         <v>120</v>
       </c>
-      <c r="BR69" s="71"/>
+      <c r="BR69" s="73"/>
       <c r="BS69" s="41">
         <f>+_xlfn.XLOOKUP(BQ69,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.97499999999999987</v>
@@ -6588,47 +6584,47 @@
       <c r="BV69"/>
     </row>
     <row r="70" spans="19:74" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S70" s="84"/>
-      <c r="T70" s="85"/>
-      <c r="U70" s="85"/>
-      <c r="V70" s="85"/>
-      <c r="W70" s="86"/>
+      <c r="S70" s="81"/>
+      <c r="T70" s="82"/>
+      <c r="U70" s="82"/>
+      <c r="V70" s="82"/>
+      <c r="W70" s="83"/>
       <c r="Y70" s="17"/>
       <c r="AS70" s="25"/>
       <c r="AX70"/>
       <c r="AY70"/>
       <c r="AZ70" s="29"/>
-      <c r="BA70" s="55"/>
-      <c r="BB70" s="56"/>
-      <c r="BC70" s="59" t="str">
+      <c r="BA70" s="51"/>
+      <c r="BB70" s="52"/>
+      <c r="BC70" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BA69,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="BD70"/>
-      <c r="BE70" s="55"/>
-      <c r="BF70" s="56"/>
-      <c r="BG70" s="59" t="str">
+      <c r="BE70" s="51"/>
+      <c r="BF70" s="52"/>
+      <c r="BG70" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BE69,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="BH70"/>
-      <c r="BI70" s="72"/>
-      <c r="BJ70" s="73"/>
-      <c r="BK70" s="59" t="str">
+      <c r="BI70" s="74"/>
+      <c r="BJ70" s="75"/>
+      <c r="BK70" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BI69,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="BL70"/>
-      <c r="BM70" s="72"/>
-      <c r="BN70" s="73"/>
-      <c r="BO70" s="59" t="str">
+      <c r="BM70" s="74"/>
+      <c r="BN70" s="75"/>
+      <c r="BO70" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BM69,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="BP70"/>
-      <c r="BQ70" s="72"/>
-      <c r="BR70" s="73"/>
-      <c r="BS70" s="59" t="str">
+      <c r="BQ70" s="74"/>
+      <c r="BR70" s="75"/>
+      <c r="BS70" s="55" t="str">
         <f>+_xlfn.XLOOKUP(BQ69,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
@@ -6637,94 +6633,94 @@
       <c r="BV70"/>
     </row>
     <row r="71" spans="19:74" ht="24" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S71" s="84"/>
-      <c r="T71" s="85"/>
-      <c r="U71" s="85"/>
-      <c r="V71" s="85"/>
-      <c r="W71" s="86"/>
+      <c r="S71" s="81"/>
+      <c r="T71" s="82"/>
+      <c r="U71" s="82"/>
+      <c r="V71" s="82"/>
+      <c r="W71" s="83"/>
       <c r="Y71" s="17"/>
-      <c r="AA71" s="62" t="s">
+      <c r="AA71" s="70" t="s">
         <v>138</v>
       </c>
-      <c r="AC71" s="64" t="s">
+      <c r="AC71" s="59" t="s">
         <v>157</v>
       </c>
-      <c r="AD71" s="65"/>
+      <c r="AD71" s="60"/>
       <c r="AE71" s="44">
         <f>+_xlfn.XLOOKUP(AC71,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.7649999999999999</v>
       </c>
       <c r="AF71" s="5"/>
-      <c r="AG71" s="62" t="s">
+      <c r="AG71" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AK71" s="62" t="s">
+      <c r="AK71" s="70" t="s">
         <v>152</v>
       </c>
-      <c r="AM71" s="53" t="s">
+      <c r="AM71" s="49" t="s">
         <v>167</v>
       </c>
-      <c r="AN71" s="54"/>
+      <c r="AN71" s="50"/>
       <c r="AO71" s="44">
         <f>+_xlfn.XLOOKUP(AM71,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.42999999999999994</v>
       </c>
       <c r="AP71" s="5"/>
-      <c r="AQ71" s="62" t="s">
+      <c r="AQ71" s="70" t="s">
         <v>149</v>
       </c>
       <c r="AS71" s="25"/>
       <c r="AX71"/>
       <c r="AY71"/>
       <c r="AZ71" s="29"/>
-      <c r="BA71" s="57"/>
-      <c r="BB71" s="58"/>
-      <c r="BC71" s="60"/>
+      <c r="BA71" s="53"/>
+      <c r="BB71" s="54"/>
+      <c r="BC71" s="56"/>
       <c r="BD71"/>
-      <c r="BE71" s="57"/>
-      <c r="BF71" s="58"/>
-      <c r="BG71" s="60"/>
+      <c r="BE71" s="53"/>
+      <c r="BF71" s="54"/>
+      <c r="BG71" s="56"/>
       <c r="BH71"/>
-      <c r="BI71" s="74"/>
-      <c r="BJ71" s="75"/>
-      <c r="BK71" s="60"/>
+      <c r="BI71" s="76"/>
+      <c r="BJ71" s="77"/>
+      <c r="BK71" s="56"/>
       <c r="BL71"/>
-      <c r="BM71" s="74"/>
-      <c r="BN71" s="75"/>
-      <c r="BO71" s="60"/>
+      <c r="BM71" s="76"/>
+      <c r="BN71" s="77"/>
+      <c r="BO71" s="56"/>
       <c r="BP71"/>
-      <c r="BQ71" s="74"/>
-      <c r="BR71" s="75"/>
-      <c r="BS71" s="60"/>
+      <c r="BQ71" s="76"/>
+      <c r="BR71" s="77"/>
+      <c r="BS71" s="56"/>
       <c r="BT71" s="22"/>
       <c r="BU71"/>
       <c r="BV71"/>
     </row>
     <row r="72" spans="19:74" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="S72" s="84"/>
-      <c r="T72" s="85"/>
-      <c r="U72" s="85"/>
-      <c r="V72" s="85"/>
-      <c r="W72" s="86"/>
+      <c r="S72" s="81"/>
+      <c r="T72" s="82"/>
+      <c r="U72" s="82"/>
+      <c r="V72" s="82"/>
+      <c r="W72" s="83"/>
       <c r="Y72" s="17"/>
-      <c r="AA72" s="63"/>
-      <c r="AC72" s="66"/>
-      <c r="AD72" s="67"/>
-      <c r="AE72" s="76" t="str">
+      <c r="AA72" s="71"/>
+      <c r="AC72" s="61"/>
+      <c r="AD72" s="62"/>
+      <c r="AE72" s="57" t="str">
         <f>+_xlfn.XLOOKUP(AC71,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AF72" s="5"/>
-      <c r="AG72" s="63"/>
-      <c r="AK72" s="63"/>
-      <c r="AM72" s="55"/>
-      <c r="AN72" s="56"/>
-      <c r="AO72" s="76" t="str">
+      <c r="AG72" s="71"/>
+      <c r="AK72" s="71"/>
+      <c r="AM72" s="51"/>
+      <c r="AN72" s="52"/>
+      <c r="AO72" s="57" t="str">
         <f>+_xlfn.XLOOKUP(AM71,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="AP72" s="5"/>
-      <c r="AQ72" s="63"/>
+      <c r="AQ72" s="71"/>
       <c r="AS72" s="25"/>
       <c r="AX72"/>
       <c r="AY72"/>
@@ -6753,24 +6749,24 @@
       <c r="BV72"/>
     </row>
     <row r="73" spans="19:74" ht="24" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S73" s="84"/>
-      <c r="T73" s="85"/>
-      <c r="U73" s="85"/>
-      <c r="V73" s="85"/>
-      <c r="W73" s="86"/>
+      <c r="S73" s="81"/>
+      <c r="T73" s="82"/>
+      <c r="U73" s="82"/>
+      <c r="V73" s="82"/>
+      <c r="W73" s="83"/>
       <c r="Y73" s="17"/>
-      <c r="AA73" s="63"/>
-      <c r="AC73" s="68"/>
-      <c r="AD73" s="69"/>
-      <c r="AE73" s="77"/>
+      <c r="AA73" s="71"/>
+      <c r="AC73" s="63"/>
+      <c r="AD73" s="64"/>
+      <c r="AE73" s="58"/>
       <c r="AF73" s="5"/>
-      <c r="AG73" s="63"/>
-      <c r="AK73" s="63"/>
-      <c r="AM73" s="57"/>
-      <c r="AN73" s="58"/>
-      <c r="AO73" s="77"/>
+      <c r="AG73" s="71"/>
+      <c r="AK73" s="71"/>
+      <c r="AM73" s="53"/>
+      <c r="AN73" s="54"/>
+      <c r="AO73" s="58"/>
       <c r="AP73" s="5"/>
-      <c r="AQ73" s="63"/>
+      <c r="AQ73" s="71"/>
       <c r="AS73" s="25"/>
       <c r="AX73"/>
       <c r="AY73"/>
@@ -6799,24 +6795,24 @@
       <c r="BV73"/>
     </row>
     <row r="74" spans="19:74" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="S74" s="84"/>
-      <c r="T74" s="85"/>
-      <c r="U74" s="85"/>
-      <c r="V74" s="85"/>
-      <c r="W74" s="86"/>
+      <c r="S74" s="81"/>
+      <c r="T74" s="82"/>
+      <c r="U74" s="82"/>
+      <c r="V74" s="82"/>
+      <c r="W74" s="83"/>
       <c r="Y74" s="17"/>
-      <c r="AA74" s="63"/>
+      <c r="AA74" s="71"/>
       <c r="AC74" s="5"/>
       <c r="AD74" s="5"/>
       <c r="AE74" s="5"/>
       <c r="AF74" s="5"/>
-      <c r="AG74" s="63"/>
-      <c r="AK74" s="63"/>
+      <c r="AG74" s="71"/>
+      <c r="AK74" s="71"/>
       <c r="AM74" s="5"/>
       <c r="AN74" s="5"/>
       <c r="AO74" s="5"/>
       <c r="AP74" s="5"/>
-      <c r="AQ74" s="63"/>
+      <c r="AQ74" s="71"/>
       <c r="AS74" s="25"/>
       <c r="AX74"/>
       <c r="AY74"/>
@@ -6845,18 +6841,18 @@
       <c r="BV74"/>
     </row>
     <row r="75" spans="19:74" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S75" s="84"/>
-      <c r="T75" s="85"/>
-      <c r="U75" s="85"/>
-      <c r="V75" s="85"/>
-      <c r="W75" s="86"/>
+      <c r="S75" s="81"/>
+      <c r="T75" s="82"/>
+      <c r="U75" s="82"/>
+      <c r="V75" s="82"/>
+      <c r="W75" s="83"/>
       <c r="Y75" s="17"/>
-      <c r="AA75" s="63"/>
+      <c r="AA75" s="71"/>
       <c r="AF75" s="5"/>
-      <c r="AG75" s="63"/>
-      <c r="AK75" s="63"/>
+      <c r="AG75" s="71"/>
+      <c r="AK75" s="71"/>
       <c r="AP75" s="5"/>
-      <c r="AQ75" s="63"/>
+      <c r="AQ75" s="71"/>
       <c r="AS75" s="25"/>
       <c r="AX75"/>
       <c r="AY75"/>
@@ -6885,20 +6881,20 @@
       <c r="BV75"/>
     </row>
     <row r="76" spans="19:74" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="S76" s="84"/>
-      <c r="T76" s="85"/>
-      <c r="U76" s="85"/>
-      <c r="V76" s="85"/>
-      <c r="W76" s="86"/>
+      <c r="S76" s="81"/>
+      <c r="T76" s="82"/>
+      <c r="U76" s="82"/>
+      <c r="V76" s="82"/>
+      <c r="W76" s="83"/>
       <c r="Y76" s="17"/>
       <c r="AA76" s="43">
         <f>+_xlfn.XLOOKUP(AA71,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.65999999999999992</v>
       </c>
-      <c r="AC76" s="53" t="s">
+      <c r="AC76" s="49" t="s">
         <v>156</v>
       </c>
-      <c r="AD76" s="54"/>
+      <c r="AD76" s="50"/>
       <c r="AE76" s="44">
         <f>+_xlfn.XLOOKUP(AC76,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.6</v>
@@ -6912,8 +6908,8 @@
         <f>+_xlfn.XLOOKUP(AK71,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v>0.8949999999999998</v>
       </c>
-      <c r="AM76" s="53"/>
-      <c r="AN76" s="54"/>
+      <c r="AM76" s="49"/>
+      <c r="AN76" s="50"/>
       <c r="AO76" s="41" t="str">
         <f>+_xlfn.XLOOKUP(AM76,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
@@ -6951,39 +6947,39 @@
       <c r="BV76"/>
     </row>
     <row r="77" spans="19:74" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="S77" s="84"/>
-      <c r="T77" s="85"/>
-      <c r="U77" s="85"/>
-      <c r="V77" s="85"/>
-      <c r="W77" s="86"/>
+      <c r="S77" s="81"/>
+      <c r="T77" s="82"/>
+      <c r="U77" s="82"/>
+      <c r="V77" s="82"/>
+      <c r="W77" s="83"/>
       <c r="Y77" s="17"/>
-      <c r="AA77" s="49" t="str">
+      <c r="AA77" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AA71,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
-      <c r="AC77" s="55"/>
-      <c r="AD77" s="56"/>
-      <c r="AE77" s="76" t="str">
+      <c r="AC77" s="51"/>
+      <c r="AD77" s="52"/>
+      <c r="AE77" s="57" t="str">
         <f>+_xlfn.XLOOKUP(AC76,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AF77" s="5"/>
-      <c r="AG77" s="49" t="str">
+      <c r="AG77" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AG71,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
-      <c r="AK77" s="49" t="str">
+      <c r="AK77" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AK71,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
-      <c r="AM77" s="55"/>
-      <c r="AN77" s="56"/>
-      <c r="AO77" s="59" t="str">
+      <c r="AM77" s="51"/>
+      <c r="AN77" s="52"/>
+      <c r="AO77" s="55" t="str">
         <f>+_xlfn.XLOOKUP(AM76,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="AP77" s="5"/>
-      <c r="AQ77" s="49" t="str">
+      <c r="AQ77" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AQ71,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
@@ -7015,24 +7011,24 @@
       <c r="BV77"/>
     </row>
     <row r="78" spans="19:74" ht="24" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S78" s="84"/>
-      <c r="T78" s="85"/>
-      <c r="U78" s="85"/>
-      <c r="V78" s="85"/>
-      <c r="W78" s="86"/>
+      <c r="S78" s="81"/>
+      <c r="T78" s="82"/>
+      <c r="U78" s="82"/>
+      <c r="V78" s="82"/>
+      <c r="W78" s="83"/>
       <c r="Y78" s="17"/>
-      <c r="AA78" s="50"/>
-      <c r="AC78" s="57"/>
-      <c r="AD78" s="58"/>
-      <c r="AE78" s="77"/>
+      <c r="AA78" s="66"/>
+      <c r="AC78" s="53"/>
+      <c r="AD78" s="54"/>
+      <c r="AE78" s="58"/>
       <c r="AF78" s="5"/>
-      <c r="AG78" s="50"/>
-      <c r="AK78" s="50"/>
-      <c r="AM78" s="57"/>
-      <c r="AN78" s="58"/>
-      <c r="AO78" s="60"/>
+      <c r="AG78" s="66"/>
+      <c r="AK78" s="66"/>
+      <c r="AM78" s="53"/>
+      <c r="AN78" s="54"/>
+      <c r="AO78" s="56"/>
       <c r="AP78" s="5"/>
-      <c r="AQ78" s="50"/>
+      <c r="AQ78" s="66"/>
       <c r="AS78" s="25"/>
       <c r="AX78"/>
       <c r="AY78"/>
@@ -7061,11 +7057,11 @@
       <c r="BV78"/>
     </row>
     <row r="79" spans="19:74" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="S79" s="84"/>
-      <c r="T79" s="85"/>
-      <c r="U79" s="85"/>
-      <c r="V79" s="85"/>
-      <c r="W79" s="86"/>
+      <c r="S79" s="81"/>
+      <c r="T79" s="82"/>
+      <c r="U79" s="82"/>
+      <c r="V79" s="82"/>
+      <c r="W79" s="83"/>
       <c r="Y79" s="17"/>
       <c r="AS79" s="25"/>
       <c r="AY79"/>
@@ -7085,11 +7081,11 @@
       <c r="BU79"/>
     </row>
     <row r="80" spans="19:74" ht="24" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S80" s="87"/>
-      <c r="T80" s="88"/>
-      <c r="U80" s="88"/>
-      <c r="V80" s="88"/>
-      <c r="W80" s="89"/>
+      <c r="S80" s="84"/>
+      <c r="T80" s="85"/>
+      <c r="U80" s="85"/>
+      <c r="V80" s="85"/>
+      <c r="W80" s="86"/>
       <c r="Y80" s="19"/>
       <c r="Z80" s="20"/>
       <c r="AA80" s="20"/>
@@ -7210,76 +7206,76 @@
       <c r="AQ106" s="18"/>
     </row>
     <row r="107" spans="15:43" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="O107" s="53"/>
-      <c r="P107" s="54"/>
+      <c r="O107" s="49"/>
+      <c r="P107" s="50"/>
       <c r="Q107" s="41" t="str">
         <f>+_xlfn.XLOOKUP(O107,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
       </c>
-      <c r="S107" s="61"/>
+      <c r="S107" s="67"/>
       <c r="Y107" s="17"/>
-      <c r="AA107" s="61"/>
+      <c r="AA107" s="67"/>
       <c r="AB107"/>
-      <c r="AC107" s="61"/>
+      <c r="AC107" s="67"/>
       <c r="AD107"/>
-      <c r="AE107" s="61"/>
+      <c r="AE107" s="67"/>
       <c r="AQ107" s="18"/>
     </row>
     <row r="108" spans="15:43" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="O108" s="55"/>
-      <c r="P108" s="56"/>
-      <c r="Q108" s="59" t="str">
+      <c r="O108" s="51"/>
+      <c r="P108" s="52"/>
+      <c r="Q108" s="55" t="str">
         <f>+_xlfn.XLOOKUP(O107,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
-      <c r="S108" s="51"/>
+      <c r="S108" s="68"/>
       <c r="Y108" s="17"/>
-      <c r="AA108" s="51"/>
+      <c r="AA108" s="68"/>
       <c r="AB108"/>
-      <c r="AC108" s="51"/>
+      <c r="AC108" s="68"/>
       <c r="AD108"/>
-      <c r="AE108" s="51"/>
+      <c r="AE108" s="68"/>
       <c r="AQ108" s="18"/>
     </row>
     <row r="109" spans="15:43" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O109" s="57"/>
-      <c r="P109" s="58"/>
-      <c r="Q109" s="60"/>
-      <c r="S109" s="51"/>
+      <c r="O109" s="53"/>
+      <c r="P109" s="54"/>
+      <c r="Q109" s="56"/>
+      <c r="S109" s="68"/>
       <c r="Y109" s="17"/>
-      <c r="AA109" s="51"/>
+      <c r="AA109" s="68"/>
       <c r="AB109"/>
-      <c r="AC109" s="51"/>
+      <c r="AC109" s="68"/>
       <c r="AD109"/>
-      <c r="AE109" s="51"/>
+      <c r="AE109" s="68"/>
       <c r="AQ109" s="18"/>
     </row>
     <row r="110" spans="15:43" ht="18" x14ac:dyDescent="0.2">
       <c r="O110" s="5"/>
       <c r="P110" s="5"/>
       <c r="Q110" s="5"/>
-      <c r="S110" s="51"/>
+      <c r="S110" s="68"/>
       <c r="Y110" s="17"/>
-      <c r="AA110" s="51"/>
+      <c r="AA110" s="68"/>
       <c r="AB110"/>
-      <c r="AC110" s="51"/>
+      <c r="AC110" s="68"/>
       <c r="AD110"/>
-      <c r="AE110" s="51"/>
+      <c r="AE110" s="68"/>
       <c r="AQ110" s="18"/>
     </row>
     <row r="111" spans="15:43" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S111" s="51"/>
+      <c r="S111" s="68"/>
       <c r="Y111" s="17"/>
-      <c r="AA111" s="51"/>
+      <c r="AA111" s="68"/>
       <c r="AB111"/>
-      <c r="AC111" s="51"/>
+      <c r="AC111" s="68"/>
       <c r="AD111"/>
-      <c r="AE111" s="51"/>
+      <c r="AE111" s="68"/>
       <c r="AQ111" s="18"/>
     </row>
     <row r="112" spans="15:43" ht="18" x14ac:dyDescent="0.2">
-      <c r="O112" s="53"/>
-      <c r="P112" s="54"/>
+      <c r="O112" s="49"/>
+      <c r="P112" s="50"/>
       <c r="Q112" s="41" t="str">
         <f>+_xlfn.XLOOKUP(O112,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
@@ -7306,44 +7302,44 @@
       <c r="AQ112" s="18"/>
     </row>
     <row r="113" spans="15:43" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="O113" s="55"/>
-      <c r="P113" s="56"/>
-      <c r="Q113" s="59" t="str">
+      <c r="O113" s="51"/>
+      <c r="P113" s="52"/>
+      <c r="Q113" s="55" t="str">
         <f>+_xlfn.XLOOKUP(O112,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
-      <c r="S113" s="49" t="str">
+      <c r="S113" s="65" t="str">
         <f>+_xlfn.XLOOKUP(S107,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="Y113" s="17"/>
-      <c r="AA113" s="49" t="str">
+      <c r="AA113" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AA107,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="AB113"/>
-      <c r="AC113" s="49" t="str">
+      <c r="AC113" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AC107,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="AD113"/>
-      <c r="AE113" s="49" t="str">
+      <c r="AE113" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AE107,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="AQ113" s="18"/>
     </row>
     <row r="114" spans="15:43" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O114" s="57"/>
-      <c r="P114" s="58"/>
-      <c r="Q114" s="60"/>
-      <c r="S114" s="50"/>
+      <c r="O114" s="53"/>
+      <c r="P114" s="54"/>
+      <c r="Q114" s="56"/>
+      <c r="S114" s="66"/>
       <c r="Y114" s="17"/>
-      <c r="AA114" s="50"/>
+      <c r="AA114" s="66"/>
       <c r="AB114"/>
-      <c r="AC114" s="50"/>
+      <c r="AC114" s="66"/>
       <c r="AD114"/>
-      <c r="AE114" s="50"/>
+      <c r="AE114" s="66"/>
       <c r="AQ114" s="18"/>
     </row>
     <row r="115" spans="15:43" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7352,79 +7348,79 @@
     </row>
     <row r="116" spans="15:43" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="Y116" s="17"/>
-      <c r="AA116" s="61" t="s">
+      <c r="AA116" s="67" t="s">
         <v>161</v>
       </c>
       <c r="AB116"/>
-      <c r="AC116" s="61" t="s">
+      <c r="AC116" s="67" t="s">
         <v>162</v>
       </c>
       <c r="AD116"/>
-      <c r="AE116" s="61" t="s">
+      <c r="AE116" s="67" t="s">
         <v>163</v>
       </c>
       <c r="AQ116" s="18"/>
     </row>
     <row r="117" spans="15:43" x14ac:dyDescent="0.2">
-      <c r="O117" s="53"/>
-      <c r="P117" s="54"/>
+      <c r="O117" s="49"/>
+      <c r="P117" s="50"/>
       <c r="Q117" s="41" t="str">
         <f>+_xlfn.XLOOKUP(O117,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
       </c>
-      <c r="S117" s="61"/>
+      <c r="S117" s="67"/>
       <c r="Y117" s="17"/>
-      <c r="AA117" s="51"/>
+      <c r="AA117" s="68"/>
       <c r="AB117"/>
-      <c r="AC117" s="51"/>
+      <c r="AC117" s="68"/>
       <c r="AD117"/>
-      <c r="AE117" s="51"/>
+      <c r="AE117" s="68"/>
       <c r="AQ117" s="18"/>
     </row>
     <row r="118" spans="15:43" x14ac:dyDescent="0.2">
-      <c r="O118" s="55"/>
-      <c r="P118" s="56"/>
-      <c r="Q118" s="59" t="str">
+      <c r="O118" s="51"/>
+      <c r="P118" s="52"/>
+      <c r="Q118" s="55" t="str">
         <f>+_xlfn.XLOOKUP(O117,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
-      <c r="S118" s="51"/>
+      <c r="S118" s="68"/>
       <c r="Y118" s="17"/>
-      <c r="AA118" s="51"/>
+      <c r="AA118" s="68"/>
       <c r="AB118"/>
-      <c r="AC118" s="51"/>
+      <c r="AC118" s="68"/>
       <c r="AD118"/>
-      <c r="AE118" s="51"/>
+      <c r="AE118" s="68"/>
       <c r="AQ118" s="18"/>
     </row>
     <row r="119" spans="15:43" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O119" s="57"/>
-      <c r="P119" s="58"/>
-      <c r="Q119" s="60"/>
-      <c r="S119" s="51"/>
+      <c r="O119" s="53"/>
+      <c r="P119" s="54"/>
+      <c r="Q119" s="56"/>
+      <c r="S119" s="68"/>
       <c r="Y119" s="17"/>
-      <c r="AA119" s="51"/>
+      <c r="AA119" s="68"/>
       <c r="AB119"/>
-      <c r="AC119" s="51"/>
+      <c r="AC119" s="68"/>
       <c r="AD119"/>
-      <c r="AE119" s="51"/>
+      <c r="AE119" s="68"/>
       <c r="AQ119" s="18"/>
     </row>
     <row r="120" spans="15:43" ht="18" x14ac:dyDescent="0.2">
       <c r="O120" s="5"/>
       <c r="P120" s="5"/>
       <c r="Q120" s="5"/>
-      <c r="S120" s="51"/>
+      <c r="S120" s="68"/>
       <c r="Y120" s="17"/>
-      <c r="AA120" s="51"/>
+      <c r="AA120" s="68"/>
       <c r="AB120"/>
-      <c r="AC120" s="51"/>
+      <c r="AC120" s="68"/>
       <c r="AD120"/>
-      <c r="AE120" s="51"/>
+      <c r="AE120" s="68"/>
       <c r="AQ120" s="18"/>
     </row>
     <row r="121" spans="15:43" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S121" s="51"/>
+      <c r="S121" s="68"/>
       <c r="Y121" s="17"/>
       <c r="AA121" s="42">
         <f>+_xlfn.XLOOKUP(AA116,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
@@ -7443,8 +7439,8 @@
       <c r="AQ121" s="18"/>
     </row>
     <row r="122" spans="15:43" ht="18" x14ac:dyDescent="0.2">
-      <c r="O122" s="53"/>
-      <c r="P122" s="54"/>
+      <c r="O122" s="49"/>
+      <c r="P122" s="50"/>
       <c r="Q122" s="41" t="str">
         <f>+_xlfn.XLOOKUP(O122,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
@@ -7454,46 +7450,46 @@
         <v/>
       </c>
       <c r="Y122" s="17"/>
-      <c r="AA122" s="49" t="str">
+      <c r="AA122" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AA116,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AB122"/>
-      <c r="AC122" s="49" t="str">
+      <c r="AC122" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AC116,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="AD122"/>
-      <c r="AE122" s="49" t="str">
+      <c r="AE122" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AE116,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="AQ122" s="18"/>
     </row>
     <row r="123" spans="15:43" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O123" s="55"/>
-      <c r="P123" s="56"/>
-      <c r="Q123" s="59" t="str">
+      <c r="O123" s="51"/>
+      <c r="P123" s="52"/>
+      <c r="Q123" s="55" t="str">
         <f>+_xlfn.XLOOKUP(O122,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
-      <c r="S123" s="51" t="str">
+      <c r="S123" s="68" t="str">
         <f>+_xlfn.XLOOKUP(S117,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="Y123" s="17"/>
-      <c r="AA123" s="50"/>
+      <c r="AA123" s="66"/>
       <c r="AB123"/>
-      <c r="AC123" s="50"/>
+      <c r="AC123" s="66"/>
       <c r="AD123"/>
-      <c r="AE123" s="50"/>
+      <c r="AE123" s="66"/>
       <c r="AQ123" s="18"/>
     </row>
     <row r="124" spans="15:43" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O124" s="57"/>
-      <c r="P124" s="58"/>
-      <c r="Q124" s="60"/>
-      <c r="S124" s="52"/>
+      <c r="O124" s="53"/>
+      <c r="P124" s="54"/>
+      <c r="Q124" s="56"/>
+      <c r="S124" s="69"/>
       <c r="Y124" s="17"/>
       <c r="AQ124" s="18"/>
     </row>
@@ -7503,72 +7499,72 @@
     </row>
     <row r="126" spans="15:43" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="Y126" s="17"/>
-      <c r="AA126" s="61" t="s">
+      <c r="AA126" s="67" t="s">
         <v>164</v>
       </c>
       <c r="AB126"/>
-      <c r="AC126" s="61" t="s">
+      <c r="AC126" s="67" t="s">
         <v>165</v>
       </c>
       <c r="AD126"/>
-      <c r="AE126" s="61" t="s">
+      <c r="AE126" s="67" t="s">
         <v>176</v>
       </c>
       <c r="AQ126" s="18"/>
     </row>
     <row r="127" spans="15:43" x14ac:dyDescent="0.2">
-      <c r="O127" s="53"/>
-      <c r="P127" s="54"/>
+      <c r="O127" s="49"/>
+      <c r="P127" s="50"/>
       <c r="Q127" s="41" t="str">
         <f>+_xlfn.XLOOKUP(O127,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
       </c>
-      <c r="S127" s="61"/>
+      <c r="S127" s="67"/>
       <c r="Y127" s="17"/>
-      <c r="AA127" s="51"/>
+      <c r="AA127" s="68"/>
       <c r="AB127"/>
-      <c r="AC127" s="51"/>
+      <c r="AC127" s="68"/>
       <c r="AD127"/>
-      <c r="AE127" s="51"/>
+      <c r="AE127" s="68"/>
       <c r="AQ127" s="18"/>
     </row>
     <row r="128" spans="15:43" x14ac:dyDescent="0.2">
-      <c r="O128" s="55"/>
-      <c r="P128" s="56"/>
-      <c r="Q128" s="59" t="str">
+      <c r="O128" s="51"/>
+      <c r="P128" s="52"/>
+      <c r="Q128" s="55" t="str">
         <f>+_xlfn.XLOOKUP(O127,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
-      <c r="S128" s="51"/>
+      <c r="S128" s="68"/>
       <c r="Y128" s="17"/>
-      <c r="AA128" s="51"/>
+      <c r="AA128" s="68"/>
       <c r="AB128"/>
-      <c r="AC128" s="51"/>
+      <c r="AC128" s="68"/>
       <c r="AD128"/>
-      <c r="AE128" s="51"/>
+      <c r="AE128" s="68"/>
       <c r="AQ128" s="18"/>
     </row>
     <row r="129" spans="15:61" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O129" s="57"/>
-      <c r="P129" s="58"/>
-      <c r="Q129" s="60"/>
-      <c r="S129" s="51"/>
+      <c r="O129" s="53"/>
+      <c r="P129" s="54"/>
+      <c r="Q129" s="56"/>
+      <c r="S129" s="68"/>
       <c r="Y129" s="17"/>
-      <c r="AA129" s="51"/>
+      <c r="AA129" s="68"/>
       <c r="AB129"/>
-      <c r="AC129" s="51"/>
+      <c r="AC129" s="68"/>
       <c r="AD129"/>
-      <c r="AE129" s="51"/>
+      <c r="AE129" s="68"/>
       <c r="AQ129" s="18"/>
     </row>
     <row r="130" spans="15:61" x14ac:dyDescent="0.2">
-      <c r="S130" s="51"/>
+      <c r="S130" s="68"/>
       <c r="Y130" s="17"/>
-      <c r="AA130" s="51"/>
+      <c r="AA130" s="68"/>
       <c r="AB130"/>
-      <c r="AC130" s="51"/>
+      <c r="AC130" s="68"/>
       <c r="AD130"/>
-      <c r="AE130" s="51"/>
+      <c r="AE130" s="68"/>
       <c r="AI130"/>
       <c r="AJ130"/>
       <c r="AP130"/>
@@ -7593,7 +7589,7 @@
       <c r="BI130"/>
     </row>
     <row r="131" spans="15:61" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S131" s="51"/>
+      <c r="S131" s="68"/>
       <c r="Y131" s="17"/>
       <c r="AA131" s="42">
         <f>+_xlfn.XLOOKUP(AA126,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
@@ -7612,8 +7608,8 @@
       <c r="AQ131" s="18"/>
     </row>
     <row r="132" spans="15:61" ht="18" x14ac:dyDescent="0.2">
-      <c r="O132" s="53"/>
-      <c r="P132" s="54"/>
+      <c r="O132" s="49"/>
+      <c r="P132" s="50"/>
       <c r="Q132" s="41" t="str">
         <f>+_xlfn.XLOOKUP(O132,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
@@ -7623,46 +7619,46 @@
         <v/>
       </c>
       <c r="Y132" s="17"/>
-      <c r="AA132" s="49" t="str">
+      <c r="AA132" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AA126,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AB132"/>
-      <c r="AC132" s="49" t="str">
+      <c r="AC132" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AC126,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AD132"/>
-      <c r="AE132" s="49" t="str">
+      <c r="AE132" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AE126,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AQ132" s="18"/>
     </row>
     <row r="133" spans="15:61" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O133" s="55"/>
-      <c r="P133" s="56"/>
-      <c r="Q133" s="59" t="str">
+      <c r="O133" s="51"/>
+      <c r="P133" s="52"/>
+      <c r="Q133" s="55" t="str">
         <f>+_xlfn.XLOOKUP(O132,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
-      <c r="S133" s="51" t="str">
+      <c r="S133" s="68" t="str">
         <f>+_xlfn.XLOOKUP(S127,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="Y133" s="17"/>
-      <c r="AA133" s="50"/>
+      <c r="AA133" s="66"/>
       <c r="AB133"/>
-      <c r="AC133" s="50"/>
+      <c r="AC133" s="66"/>
       <c r="AD133"/>
-      <c r="AE133" s="50"/>
+      <c r="AE133" s="66"/>
       <c r="AQ133" s="18"/>
     </row>
     <row r="134" spans="15:61" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O134" s="57"/>
-      <c r="P134" s="58"/>
-      <c r="Q134" s="60"/>
-      <c r="S134" s="52"/>
+      <c r="O134" s="53"/>
+      <c r="P134" s="54"/>
+      <c r="Q134" s="56"/>
+      <c r="S134" s="69"/>
       <c r="Y134" s="17"/>
       <c r="AQ134" s="18"/>
     </row>
@@ -7672,76 +7668,76 @@
     </row>
     <row r="136" spans="15:61" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="Y136" s="17"/>
-      <c r="AA136" s="61" t="s">
+      <c r="AA136" s="67" t="s">
         <v>166</v>
       </c>
       <c r="AB136"/>
-      <c r="AC136" s="61" t="s">
+      <c r="AC136" s="67" t="s">
         <v>175</v>
       </c>
       <c r="AD136"/>
-      <c r="AE136" s="61" t="s">
+      <c r="AE136" s="67" t="s">
         <v>176</v>
       </c>
       <c r="AQ136" s="18"/>
     </row>
     <row r="137" spans="15:61" x14ac:dyDescent="0.2">
-      <c r="O137" s="53"/>
-      <c r="P137" s="54"/>
+      <c r="O137" s="49"/>
+      <c r="P137" s="50"/>
       <c r="Q137" s="41" t="str">
         <f>+_xlfn.XLOOKUP(O137,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
       </c>
-      <c r="S137" s="61"/>
+      <c r="S137" s="67"/>
       <c r="Y137" s="17"/>
-      <c r="AA137" s="51"/>
+      <c r="AA137" s="68"/>
       <c r="AB137"/>
-      <c r="AC137" s="51"/>
+      <c r="AC137" s="68"/>
       <c r="AD137"/>
-      <c r="AE137" s="51"/>
+      <c r="AE137" s="68"/>
       <c r="AQ137" s="18"/>
     </row>
     <row r="138" spans="15:61" x14ac:dyDescent="0.2">
-      <c r="O138" s="55"/>
-      <c r="P138" s="56"/>
-      <c r="Q138" s="59" t="str">
+      <c r="O138" s="51"/>
+      <c r="P138" s="52"/>
+      <c r="Q138" s="55" t="str">
         <f>+_xlfn.XLOOKUP(O137,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
-      <c r="S138" s="51"/>
+      <c r="S138" s="68"/>
       <c r="Y138" s="17"/>
-      <c r="AA138" s="51"/>
+      <c r="AA138" s="68"/>
       <c r="AB138"/>
-      <c r="AC138" s="51"/>
+      <c r="AC138" s="68"/>
       <c r="AD138"/>
-      <c r="AE138" s="51"/>
+      <c r="AE138" s="68"/>
       <c r="AQ138" s="18"/>
     </row>
     <row r="139" spans="15:61" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O139" s="57"/>
-      <c r="P139" s="58"/>
-      <c r="Q139" s="60"/>
-      <c r="S139" s="51"/>
+      <c r="O139" s="53"/>
+      <c r="P139" s="54"/>
+      <c r="Q139" s="56"/>
+      <c r="S139" s="68"/>
       <c r="Y139" s="17"/>
-      <c r="AA139" s="51"/>
+      <c r="AA139" s="68"/>
       <c r="AB139"/>
-      <c r="AC139" s="51"/>
+      <c r="AC139" s="68"/>
       <c r="AD139"/>
-      <c r="AE139" s="51"/>
+      <c r="AE139" s="68"/>
       <c r="AQ139" s="18"/>
     </row>
     <row r="140" spans="15:61" x14ac:dyDescent="0.2">
-      <c r="S140" s="51"/>
+      <c r="S140" s="68"/>
       <c r="Y140" s="17"/>
-      <c r="AA140" s="51"/>
+      <c r="AA140" s="68"/>
       <c r="AB140"/>
-      <c r="AC140" s="51"/>
+      <c r="AC140" s="68"/>
       <c r="AD140"/>
-      <c r="AE140" s="51"/>
+      <c r="AE140" s="68"/>
       <c r="AQ140" s="18"/>
     </row>
     <row r="141" spans="15:61" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S141" s="51"/>
+      <c r="S141" s="68"/>
       <c r="Y141" s="17"/>
       <c r="AA141" s="42">
         <f>+_xlfn.XLOOKUP(AA136,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
@@ -7760,8 +7756,8 @@
       <c r="AQ141" s="18"/>
     </row>
     <row r="142" spans="15:61" ht="18" x14ac:dyDescent="0.2">
-      <c r="O142" s="53"/>
-      <c r="P142" s="54"/>
+      <c r="O142" s="49"/>
+      <c r="P142" s="50"/>
       <c r="Q142" s="41" t="str">
         <f>+_xlfn.XLOOKUP(O142,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
@@ -7771,46 +7767,46 @@
         <v/>
       </c>
       <c r="Y142" s="17"/>
-      <c r="AA142" s="49" t="str">
+      <c r="AA142" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AA136,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="AB142"/>
-      <c r="AC142" s="49" t="str">
+      <c r="AC142" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AC136,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="AD142"/>
-      <c r="AE142" s="51" t="str">
+      <c r="AE142" s="68" t="str">
         <f>+_xlfn.XLOOKUP(AE136,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AQ142" s="18"/>
     </row>
     <row r="143" spans="15:61" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O143" s="55"/>
-      <c r="P143" s="56"/>
-      <c r="Q143" s="59" t="str">
+      <c r="O143" s="51"/>
+      <c r="P143" s="52"/>
+      <c r="Q143" s="55" t="str">
         <f>+_xlfn.XLOOKUP(O142,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
-      <c r="S143" s="51" t="str">
+      <c r="S143" s="68" t="str">
         <f>+_xlfn.XLOOKUP(S137,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="Y143" s="17"/>
-      <c r="AA143" s="50"/>
+      <c r="AA143" s="66"/>
       <c r="AB143"/>
-      <c r="AC143" s="50"/>
+      <c r="AC143" s="66"/>
       <c r="AD143"/>
-      <c r="AE143" s="52"/>
+      <c r="AE143" s="69"/>
       <c r="AQ143" s="18"/>
     </row>
     <row r="144" spans="15:61" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O144" s="57"/>
-      <c r="P144" s="58"/>
-      <c r="Q144" s="60"/>
-      <c r="S144" s="52"/>
+      <c r="O144" s="53"/>
+      <c r="P144" s="54"/>
+      <c r="Q144" s="56"/>
+      <c r="S144" s="69"/>
       <c r="Y144" s="17"/>
       <c r="AQ144" s="18"/>
     </row>
@@ -7820,76 +7816,76 @@
     </row>
     <row r="146" spans="15:43" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="Y146" s="17"/>
-      <c r="AA146" s="61" t="s">
+      <c r="AA146" s="67" t="s">
         <v>170</v>
       </c>
       <c r="AB146"/>
-      <c r="AC146" s="61" t="s">
+      <c r="AC146" s="67" t="s">
         <v>171</v>
       </c>
       <c r="AD146"/>
-      <c r="AE146" s="61" t="s">
+      <c r="AE146" s="67" t="s">
         <v>169</v>
       </c>
       <c r="AQ146" s="18"/>
     </row>
     <row r="147" spans="15:43" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="O147" s="53"/>
-      <c r="P147" s="54"/>
+      <c r="O147" s="49"/>
+      <c r="P147" s="50"/>
       <c r="Q147" s="41" t="str">
         <f>+_xlfn.XLOOKUP(O147,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
         <v/>
       </c>
-      <c r="S147" s="61"/>
+      <c r="S147" s="67"/>
       <c r="Y147" s="17"/>
-      <c r="AA147" s="51"/>
+      <c r="AA147" s="68"/>
       <c r="AB147"/>
-      <c r="AC147" s="51"/>
+      <c r="AC147" s="68"/>
       <c r="AD147"/>
-      <c r="AE147" s="51"/>
+      <c r="AE147" s="68"/>
       <c r="AQ147" s="18"/>
     </row>
     <row r="148" spans="15:43" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="O148" s="55"/>
-      <c r="P148" s="56"/>
-      <c r="Q148" s="59" t="str">
+      <c r="O148" s="51"/>
+      <c r="P148" s="52"/>
+      <c r="Q148" s="55" t="str">
         <f>+_xlfn.XLOOKUP(O147,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
-      <c r="S148" s="51"/>
+      <c r="S148" s="68"/>
       <c r="Y148" s="17"/>
-      <c r="AA148" s="51"/>
+      <c r="AA148" s="68"/>
       <c r="AB148"/>
-      <c r="AC148" s="51"/>
+      <c r="AC148" s="68"/>
       <c r="AD148"/>
-      <c r="AE148" s="51"/>
+      <c r="AE148" s="68"/>
       <c r="AQ148" s="18"/>
     </row>
     <row r="149" spans="15:43" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="O149" s="57"/>
-      <c r="P149" s="58"/>
-      <c r="Q149" s="60"/>
-      <c r="S149" s="51"/>
+      <c r="O149" s="53"/>
+      <c r="P149" s="54"/>
+      <c r="Q149" s="56"/>
+      <c r="S149" s="68"/>
       <c r="Y149" s="17"/>
-      <c r="AA149" s="51"/>
+      <c r="AA149" s="68"/>
       <c r="AB149"/>
-      <c r="AC149" s="51"/>
+      <c r="AC149" s="68"/>
       <c r="AD149"/>
-      <c r="AE149" s="51"/>
+      <c r="AE149" s="68"/>
       <c r="AQ149" s="18"/>
     </row>
     <row r="150" spans="15:43" x14ac:dyDescent="0.2">
-      <c r="S150" s="51"/>
+      <c r="S150" s="68"/>
       <c r="Y150" s="17"/>
-      <c r="AA150" s="51"/>
+      <c r="AA150" s="68"/>
       <c r="AB150"/>
-      <c r="AC150" s="51"/>
+      <c r="AC150" s="68"/>
       <c r="AD150"/>
-      <c r="AE150" s="51"/>
+      <c r="AE150" s="68"/>
       <c r="AQ150" s="18"/>
     </row>
     <row r="151" spans="15:43" ht="18" x14ac:dyDescent="0.2">
-      <c r="S151" s="51"/>
+      <c r="S151" s="68"/>
       <c r="Y151" s="17"/>
       <c r="AA151" s="42">
         <f>+_xlfn.XLOOKUP(AA146,BASE[N° MÓDULO],BASE[% AVANCE],"",0)</f>
@@ -7913,87 +7909,87 @@
         <v/>
       </c>
       <c r="Y152" s="17"/>
-      <c r="AA152" s="49" t="str">
+      <c r="AA152" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AA146,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="AB152"/>
-      <c r="AC152" s="49" t="str">
+      <c r="AC152" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AC146,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="AD152"/>
-      <c r="AE152" s="51" t="str">
+      <c r="AE152" s="68" t="str">
         <f>+_xlfn.XLOOKUP(AE146,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AQ152" s="18"/>
     </row>
     <row r="153" spans="15:43" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S153" s="51" t="str">
+      <c r="S153" s="68" t="str">
         <f>+_xlfn.XLOOKUP(S147,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
       <c r="Y153" s="17"/>
-      <c r="AA153" s="50"/>
+      <c r="AA153" s="66"/>
       <c r="AB153"/>
-      <c r="AC153" s="50"/>
+      <c r="AC153" s="66"/>
       <c r="AD153"/>
-      <c r="AE153" s="52"/>
+      <c r="AE153" s="69"/>
       <c r="AQ153" s="18"/>
     </row>
     <row r="154" spans="15:43" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="S154" s="52"/>
+      <c r="S154" s="69"/>
       <c r="Y154" s="17"/>
       <c r="AQ154" s="18"/>
     </row>
     <row r="155" spans="15:43" x14ac:dyDescent="0.2">
       <c r="Y155" s="17"/>
-      <c r="AA155" s="61" t="s">
+      <c r="AA155" s="67" t="s">
         <v>174</v>
       </c>
       <c r="AB155"/>
-      <c r="AC155" s="61" t="s">
+      <c r="AC155" s="67" t="s">
         <v>172</v>
       </c>
       <c r="AD155"/>
-      <c r="AE155" s="61"/>
+      <c r="AE155" s="67"/>
       <c r="AQ155" s="18"/>
     </row>
     <row r="156" spans="15:43" x14ac:dyDescent="0.2">
       <c r="Y156" s="17"/>
-      <c r="AA156" s="51"/>
+      <c r="AA156" s="68"/>
       <c r="AB156"/>
-      <c r="AC156" s="51"/>
+      <c r="AC156" s="68"/>
       <c r="AD156"/>
-      <c r="AE156" s="51"/>
+      <c r="AE156" s="68"/>
       <c r="AQ156" s="18"/>
     </row>
     <row r="157" spans="15:43" x14ac:dyDescent="0.2">
       <c r="Y157" s="17"/>
-      <c r="AA157" s="51"/>
+      <c r="AA157" s="68"/>
       <c r="AB157"/>
-      <c r="AC157" s="51"/>
+      <c r="AC157" s="68"/>
       <c r="AD157"/>
-      <c r="AE157" s="51"/>
+      <c r="AE157" s="68"/>
       <c r="AQ157" s="18"/>
     </row>
     <row r="158" spans="15:43" x14ac:dyDescent="0.2">
       <c r="Y158" s="17"/>
-      <c r="AA158" s="51"/>
+      <c r="AA158" s="68"/>
       <c r="AB158"/>
-      <c r="AC158" s="51"/>
+      <c r="AC158" s="68"/>
       <c r="AD158"/>
-      <c r="AE158" s="51"/>
+      <c r="AE158" s="68"/>
       <c r="AQ158" s="18"/>
     </row>
     <row r="159" spans="15:43" x14ac:dyDescent="0.2">
       <c r="Y159" s="17"/>
-      <c r="AA159" s="51"/>
+      <c r="AA159" s="68"/>
       <c r="AB159"/>
-      <c r="AC159" s="51"/>
+      <c r="AC159" s="68"/>
       <c r="AD159"/>
-      <c r="AE159" s="51"/>
+      <c r="AE159" s="68"/>
       <c r="AQ159" s="18"/>
     </row>
     <row r="160" spans="15:43" ht="18" x14ac:dyDescent="0.2">
@@ -8016,17 +8012,17 @@
     </row>
     <row r="161" spans="25:43" x14ac:dyDescent="0.2">
       <c r="Y161" s="17"/>
-      <c r="AA161" s="49" t="str">
+      <c r="AA161" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AA155,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>HUMEDO</v>
       </c>
       <c r="AB161"/>
-      <c r="AC161" s="49" t="str">
+      <c r="AC161" s="65" t="str">
         <f>+_xlfn.XLOOKUP(AC155,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v>SECO</v>
       </c>
       <c r="AD161"/>
-      <c r="AE161" s="51" t="str">
+      <c r="AE161" s="68" t="str">
         <f>+_xlfn.XLOOKUP(AE155,BASE[N° MÓDULO],BASE[TIPO],"",0)</f>
         <v/>
       </c>
@@ -8034,11 +8030,11 @@
     </row>
     <row r="162" spans="25:43" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="Y162" s="17"/>
-      <c r="AA162" s="50"/>
+      <c r="AA162" s="66"/>
       <c r="AB162"/>
-      <c r="AC162" s="50"/>
+      <c r="AC162" s="66"/>
       <c r="AD162"/>
-      <c r="AE162" s="52"/>
+      <c r="AE162" s="69"/>
       <c r="AQ162" s="18"/>
     </row>
     <row r="163" spans="25:43" x14ac:dyDescent="0.2">
@@ -8055,64 +8051,64 @@
     </row>
     <row r="166" spans="25:43" x14ac:dyDescent="0.2">
       <c r="Y166" s="17"/>
-      <c r="AA166" s="78" t="s">
+      <c r="AA166" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="AC166" s="78" t="s">
+      <c r="AC166" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="AE166" s="78" t="s">
+      <c r="AE166" s="87" t="s">
         <v>51</v>
       </c>
       <c r="AQ166" s="18"/>
     </row>
     <row r="167" spans="25:43" x14ac:dyDescent="0.2">
       <c r="Y167" s="17"/>
-      <c r="AA167" s="79"/>
-      <c r="AC167" s="79"/>
-      <c r="AE167" s="79"/>
+      <c r="AA167" s="88"/>
+      <c r="AC167" s="88"/>
+      <c r="AE167" s="88"/>
       <c r="AQ167" s="18"/>
     </row>
     <row r="168" spans="25:43" x14ac:dyDescent="0.2">
       <c r="Y168" s="17"/>
-      <c r="AA168" s="79"/>
-      <c r="AC168" s="79"/>
-      <c r="AE168" s="79"/>
+      <c r="AA168" s="88"/>
+      <c r="AC168" s="88"/>
+      <c r="AE168" s="88"/>
       <c r="AQ168" s="18"/>
     </row>
     <row r="169" spans="25:43" x14ac:dyDescent="0.2">
       <c r="Y169" s="17"/>
-      <c r="AA169" s="79"/>
-      <c r="AC169" s="79"/>
-      <c r="AE169" s="79"/>
+      <c r="AA169" s="88"/>
+      <c r="AC169" s="88"/>
+      <c r="AE169" s="88"/>
       <c r="AQ169" s="18"/>
     </row>
     <row r="170" spans="25:43" x14ac:dyDescent="0.2">
       <c r="Y170" s="17"/>
-      <c r="AA170" s="79"/>
-      <c r="AC170" s="79"/>
-      <c r="AE170" s="79"/>
+      <c r="AA170" s="88"/>
+      <c r="AC170" s="88"/>
+      <c r="AE170" s="88"/>
       <c r="AQ170" s="18"/>
     </row>
     <row r="171" spans="25:43" x14ac:dyDescent="0.2">
       <c r="Y171" s="17"/>
-      <c r="AA171" s="79"/>
-      <c r="AC171" s="79"/>
-      <c r="AE171" s="79"/>
+      <c r="AA171" s="88"/>
+      <c r="AC171" s="88"/>
+      <c r="AE171" s="88"/>
       <c r="AQ171" s="18"/>
     </row>
     <row r="172" spans="25:43" x14ac:dyDescent="0.2">
       <c r="Y172" s="17"/>
-      <c r="AA172" s="79"/>
-      <c r="AC172" s="79"/>
-      <c r="AE172" s="79"/>
+      <c r="AA172" s="88"/>
+      <c r="AC172" s="88"/>
+      <c r="AE172" s="88"/>
       <c r="AQ172" s="18"/>
     </row>
     <row r="173" spans="25:43" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="Y173" s="17"/>
-      <c r="AA173" s="80"/>
-      <c r="AC173" s="80"/>
-      <c r="AE173" s="80"/>
+      <c r="AA173" s="89"/>
+      <c r="AC173" s="89"/>
+      <c r="AE173" s="89"/>
       <c r="AQ173" s="18"/>
     </row>
     <row r="174" spans="25:43" x14ac:dyDescent="0.2">
@@ -8146,28 +8142,178 @@
     </row>
   </sheetData>
   <mergeCells count="220">
-    <mergeCell ref="O147:P149"/>
-    <mergeCell ref="Q148:Q149"/>
-    <mergeCell ref="AC76:AD78"/>
-    <mergeCell ref="AE77:AE78"/>
-    <mergeCell ref="AC71:AD73"/>
-    <mergeCell ref="AE72:AE73"/>
-    <mergeCell ref="AC67:AD69"/>
-    <mergeCell ref="AE68:AE69"/>
-    <mergeCell ref="O127:P129"/>
-    <mergeCell ref="Q128:Q129"/>
-    <mergeCell ref="O132:P134"/>
-    <mergeCell ref="Q133:Q134"/>
-    <mergeCell ref="O137:P139"/>
-    <mergeCell ref="Q138:Q139"/>
-    <mergeCell ref="O112:P114"/>
-    <mergeCell ref="Q113:Q114"/>
-    <mergeCell ref="O107:P109"/>
-    <mergeCell ref="Q108:Q109"/>
-    <mergeCell ref="O117:P119"/>
-    <mergeCell ref="Q118:Q119"/>
-    <mergeCell ref="O122:P124"/>
-    <mergeCell ref="Q123:Q124"/>
+    <mergeCell ref="AA161:AA162"/>
+    <mergeCell ref="AC161:AC162"/>
+    <mergeCell ref="AE161:AE162"/>
+    <mergeCell ref="AA14:AB16"/>
+    <mergeCell ref="AC15:AC16"/>
+    <mergeCell ref="AG14:AH16"/>
+    <mergeCell ref="AC107:AC111"/>
+    <mergeCell ref="AC113:AC114"/>
+    <mergeCell ref="AE122:AE123"/>
+    <mergeCell ref="AA50:AA51"/>
+    <mergeCell ref="AA77:AA78"/>
+    <mergeCell ref="AA62:AA66"/>
+    <mergeCell ref="AA68:AA69"/>
+    <mergeCell ref="AA53:AA57"/>
+    <mergeCell ref="AA59:AA60"/>
+    <mergeCell ref="AA107:AA111"/>
+    <mergeCell ref="AA71:AA75"/>
+    <mergeCell ref="AE152:AE153"/>
+    <mergeCell ref="AE146:AE150"/>
+    <mergeCell ref="AA44:AA48"/>
+    <mergeCell ref="AC44:AD46"/>
+    <mergeCell ref="AE54:AE55"/>
+    <mergeCell ref="AK50:AK51"/>
+    <mergeCell ref="BA17:BB19"/>
+    <mergeCell ref="BC18:BC19"/>
+    <mergeCell ref="BA22:BB24"/>
+    <mergeCell ref="BC23:BC24"/>
+    <mergeCell ref="BE69:BF71"/>
+    <mergeCell ref="AA155:AA159"/>
+    <mergeCell ref="AC155:AC159"/>
+    <mergeCell ref="AE155:AE159"/>
+    <mergeCell ref="AK62:AK66"/>
+    <mergeCell ref="AK68:AK69"/>
+    <mergeCell ref="AE142:AE143"/>
+    <mergeCell ref="AA146:AA150"/>
+    <mergeCell ref="AA126:AA130"/>
+    <mergeCell ref="AA132:AA133"/>
+    <mergeCell ref="AC126:AC130"/>
+    <mergeCell ref="AC132:AC133"/>
+    <mergeCell ref="AA116:AA120"/>
+    <mergeCell ref="AA122:AA123"/>
+    <mergeCell ref="AC116:AC120"/>
+    <mergeCell ref="BE22:BF24"/>
+    <mergeCell ref="AK44:AK48"/>
+    <mergeCell ref="AK53:AK57"/>
+    <mergeCell ref="AC53:AD55"/>
+    <mergeCell ref="AI15:AI16"/>
+    <mergeCell ref="AM14:AN16"/>
+    <mergeCell ref="AO15:AO16"/>
+    <mergeCell ref="BI8:BI12"/>
+    <mergeCell ref="BI14:BI15"/>
+    <mergeCell ref="BG8:BG12"/>
+    <mergeCell ref="BG14:BG15"/>
+    <mergeCell ref="BE8:BE12"/>
+    <mergeCell ref="BE14:BE15"/>
+    <mergeCell ref="BC8:BC12"/>
+    <mergeCell ref="BC14:BC15"/>
+    <mergeCell ref="BA8:BA12"/>
+    <mergeCell ref="BA14:BA15"/>
+    <mergeCell ref="AS14:AT16"/>
+    <mergeCell ref="AU15:AU16"/>
+    <mergeCell ref="AE136:AE140"/>
+    <mergeCell ref="AQ59:AQ60"/>
+    <mergeCell ref="AK59:AK60"/>
+    <mergeCell ref="AO77:AO78"/>
+    <mergeCell ref="AG59:AG60"/>
+    <mergeCell ref="AG62:AG66"/>
+    <mergeCell ref="AG68:AG69"/>
+    <mergeCell ref="BG57:BG58"/>
+    <mergeCell ref="BI69:BJ71"/>
+    <mergeCell ref="BI60:BI64"/>
+    <mergeCell ref="BI66:BI67"/>
+    <mergeCell ref="BG60:BG64"/>
+    <mergeCell ref="BG66:BG67"/>
+    <mergeCell ref="BG70:BG71"/>
+    <mergeCell ref="AM71:AN73"/>
+    <mergeCell ref="AO72:AO73"/>
+    <mergeCell ref="AO68:AO69"/>
+    <mergeCell ref="AE166:AE173"/>
+    <mergeCell ref="AC166:AC173"/>
+    <mergeCell ref="AA166:AA173"/>
+    <mergeCell ref="BE56:BF58"/>
+    <mergeCell ref="BE60:BE64"/>
+    <mergeCell ref="BE66:BE67"/>
+    <mergeCell ref="BC60:BC64"/>
+    <mergeCell ref="BC66:BC67"/>
+    <mergeCell ref="BA60:BA64"/>
+    <mergeCell ref="BA66:BA67"/>
+    <mergeCell ref="AQ71:AQ75"/>
+    <mergeCell ref="AQ77:AQ78"/>
+    <mergeCell ref="BA56:BB58"/>
+    <mergeCell ref="BC57:BC58"/>
+    <mergeCell ref="AK71:AK75"/>
+    <mergeCell ref="AA152:AA153"/>
+    <mergeCell ref="AC146:AC150"/>
+    <mergeCell ref="AC152:AC153"/>
+    <mergeCell ref="AC122:AC123"/>
+    <mergeCell ref="AE116:AE120"/>
+    <mergeCell ref="AQ62:AQ66"/>
+    <mergeCell ref="AK77:AK78"/>
+    <mergeCell ref="AC136:AC140"/>
+    <mergeCell ref="AC142:AC143"/>
+    <mergeCell ref="S113:S114"/>
+    <mergeCell ref="S117:S121"/>
+    <mergeCell ref="S147:S151"/>
+    <mergeCell ref="S153:S154"/>
+    <mergeCell ref="AA136:AA140"/>
+    <mergeCell ref="AA142:AA143"/>
+    <mergeCell ref="AA113:AA114"/>
+    <mergeCell ref="S123:S124"/>
+    <mergeCell ref="S127:S131"/>
+    <mergeCell ref="S133:S134"/>
+    <mergeCell ref="S137:S141"/>
+    <mergeCell ref="S143:S144"/>
+    <mergeCell ref="BQ56:BR58"/>
+    <mergeCell ref="BS57:BS58"/>
+    <mergeCell ref="BM56:BN58"/>
+    <mergeCell ref="BO57:BO58"/>
+    <mergeCell ref="BI56:BJ58"/>
+    <mergeCell ref="BK57:BK58"/>
+    <mergeCell ref="BQ69:BR71"/>
+    <mergeCell ref="BS70:BS71"/>
+    <mergeCell ref="BK60:BK64"/>
+    <mergeCell ref="BK66:BK67"/>
+    <mergeCell ref="BM60:BM64"/>
+    <mergeCell ref="BM66:BM67"/>
+    <mergeCell ref="BO60:BO64"/>
+    <mergeCell ref="BO66:BO67"/>
+    <mergeCell ref="BQ60:BQ64"/>
+    <mergeCell ref="BQ66:BQ67"/>
+    <mergeCell ref="BS60:BS64"/>
+    <mergeCell ref="BS66:BS67"/>
+    <mergeCell ref="BK70:BK71"/>
+    <mergeCell ref="BM69:BN71"/>
+    <mergeCell ref="BO70:BO71"/>
+    <mergeCell ref="BS8:BS12"/>
+    <mergeCell ref="BS14:BS15"/>
+    <mergeCell ref="BQ8:BQ12"/>
+    <mergeCell ref="BQ14:BQ15"/>
+    <mergeCell ref="BQ17:BQ21"/>
+    <mergeCell ref="BQ23:BQ24"/>
+    <mergeCell ref="BO8:BO12"/>
+    <mergeCell ref="BO14:BO15"/>
+    <mergeCell ref="BM8:BM12"/>
+    <mergeCell ref="BM14:BM15"/>
+    <mergeCell ref="BO18:BO19"/>
+    <mergeCell ref="BM22:BN24"/>
+    <mergeCell ref="BO23:BO24"/>
+    <mergeCell ref="BK8:BK12"/>
+    <mergeCell ref="BK14:BK15"/>
+    <mergeCell ref="AE126:AE130"/>
+    <mergeCell ref="AE132:AE133"/>
+    <mergeCell ref="AE107:AE111"/>
+    <mergeCell ref="AE113:AE114"/>
+    <mergeCell ref="AQ44:AQ48"/>
+    <mergeCell ref="AQ50:AQ51"/>
+    <mergeCell ref="AG44:AG48"/>
+    <mergeCell ref="AG50:AG51"/>
+    <mergeCell ref="AG53:AG57"/>
+    <mergeCell ref="AM53:AN55"/>
+    <mergeCell ref="AO54:AO55"/>
+    <mergeCell ref="AM49:AN51"/>
+    <mergeCell ref="AO50:AO51"/>
+    <mergeCell ref="AM44:AN46"/>
+    <mergeCell ref="AO45:AO46"/>
+    <mergeCell ref="AQ68:AQ69"/>
+    <mergeCell ref="AQ53:AQ57"/>
+    <mergeCell ref="BA69:BB71"/>
+    <mergeCell ref="BC70:BC71"/>
+    <mergeCell ref="AG71:AG75"/>
+    <mergeCell ref="AG77:AG78"/>
+    <mergeCell ref="AU58:AU62"/>
     <mergeCell ref="BG23:BG24"/>
     <mergeCell ref="BE17:BF19"/>
     <mergeCell ref="BG18:BG19"/>
@@ -8192,180 +8338,30 @@
     <mergeCell ref="AE59:AE60"/>
     <mergeCell ref="AM58:AN60"/>
     <mergeCell ref="AO59:AO60"/>
-    <mergeCell ref="BK8:BK12"/>
-    <mergeCell ref="BK14:BK15"/>
-    <mergeCell ref="AE126:AE130"/>
-    <mergeCell ref="AE132:AE133"/>
-    <mergeCell ref="AE107:AE111"/>
-    <mergeCell ref="AE113:AE114"/>
-    <mergeCell ref="AQ44:AQ48"/>
-    <mergeCell ref="AQ50:AQ51"/>
-    <mergeCell ref="AG44:AG48"/>
-    <mergeCell ref="AG50:AG51"/>
-    <mergeCell ref="AG53:AG57"/>
-    <mergeCell ref="AM53:AN55"/>
-    <mergeCell ref="AO54:AO55"/>
-    <mergeCell ref="AM49:AN51"/>
-    <mergeCell ref="AO50:AO51"/>
-    <mergeCell ref="AM44:AN46"/>
-    <mergeCell ref="AO45:AO46"/>
-    <mergeCell ref="AQ68:AQ69"/>
-    <mergeCell ref="AQ53:AQ57"/>
-    <mergeCell ref="BA69:BB71"/>
-    <mergeCell ref="BC70:BC71"/>
-    <mergeCell ref="AG71:AG75"/>
-    <mergeCell ref="AG77:AG78"/>
-    <mergeCell ref="AU58:AU62"/>
-    <mergeCell ref="BS8:BS12"/>
-    <mergeCell ref="BS14:BS15"/>
-    <mergeCell ref="BQ8:BQ12"/>
-    <mergeCell ref="BQ14:BQ15"/>
-    <mergeCell ref="BQ17:BQ21"/>
-    <mergeCell ref="BQ23:BQ24"/>
-    <mergeCell ref="BO8:BO12"/>
-    <mergeCell ref="BO14:BO15"/>
-    <mergeCell ref="BM8:BM12"/>
-    <mergeCell ref="BM14:BM15"/>
-    <mergeCell ref="BO18:BO19"/>
-    <mergeCell ref="BM22:BN24"/>
-    <mergeCell ref="BO23:BO24"/>
-    <mergeCell ref="BQ56:BR58"/>
-    <mergeCell ref="BS57:BS58"/>
-    <mergeCell ref="BM56:BN58"/>
-    <mergeCell ref="BO57:BO58"/>
-    <mergeCell ref="BI56:BJ58"/>
-    <mergeCell ref="BK57:BK58"/>
-    <mergeCell ref="BQ69:BR71"/>
-    <mergeCell ref="BS70:BS71"/>
-    <mergeCell ref="BK60:BK64"/>
-    <mergeCell ref="BK66:BK67"/>
-    <mergeCell ref="BM60:BM64"/>
-    <mergeCell ref="BM66:BM67"/>
-    <mergeCell ref="BO60:BO64"/>
+    <mergeCell ref="O147:P149"/>
+    <mergeCell ref="Q148:Q149"/>
+    <mergeCell ref="AC76:AD78"/>
+    <mergeCell ref="AE77:AE78"/>
+    <mergeCell ref="AC71:AD73"/>
+    <mergeCell ref="AE72:AE73"/>
+    <mergeCell ref="AC67:AD69"/>
+    <mergeCell ref="AE68:AE69"/>
+    <mergeCell ref="O127:P129"/>
+    <mergeCell ref="Q128:Q129"/>
+    <mergeCell ref="O132:P134"/>
+    <mergeCell ref="Q133:Q134"/>
+    <mergeCell ref="O137:P139"/>
+    <mergeCell ref="Q138:Q139"/>
+    <mergeCell ref="O112:P114"/>
+    <mergeCell ref="Q113:Q114"/>
+    <mergeCell ref="O107:P109"/>
+    <mergeCell ref="Q108:Q109"/>
+    <mergeCell ref="O117:P119"/>
+    <mergeCell ref="Q118:Q119"/>
+    <mergeCell ref="O122:P124"/>
+    <mergeCell ref="Q123:Q124"/>
     <mergeCell ref="S41:W80"/>
     <mergeCell ref="S107:S111"/>
-    <mergeCell ref="S113:S114"/>
-    <mergeCell ref="S117:S121"/>
-    <mergeCell ref="S147:S151"/>
-    <mergeCell ref="S153:S154"/>
-    <mergeCell ref="AA136:AA140"/>
-    <mergeCell ref="AA142:AA143"/>
-    <mergeCell ref="AA113:AA114"/>
-    <mergeCell ref="S123:S124"/>
-    <mergeCell ref="S127:S131"/>
-    <mergeCell ref="S133:S134"/>
-    <mergeCell ref="S137:S141"/>
-    <mergeCell ref="S143:S144"/>
-    <mergeCell ref="AE166:AE173"/>
-    <mergeCell ref="AC166:AC173"/>
-    <mergeCell ref="AA166:AA173"/>
-    <mergeCell ref="BE56:BF58"/>
-    <mergeCell ref="BE60:BE64"/>
-    <mergeCell ref="BE66:BE67"/>
-    <mergeCell ref="BC60:BC64"/>
-    <mergeCell ref="BC66:BC67"/>
-    <mergeCell ref="BA60:BA64"/>
-    <mergeCell ref="BA66:BA67"/>
-    <mergeCell ref="AQ71:AQ75"/>
-    <mergeCell ref="AQ77:AQ78"/>
-    <mergeCell ref="BA56:BB58"/>
-    <mergeCell ref="BC57:BC58"/>
-    <mergeCell ref="AK71:AK75"/>
-    <mergeCell ref="AA152:AA153"/>
-    <mergeCell ref="AC146:AC150"/>
-    <mergeCell ref="AC152:AC153"/>
-    <mergeCell ref="AC122:AC123"/>
-    <mergeCell ref="AE116:AE120"/>
-    <mergeCell ref="AQ62:AQ66"/>
-    <mergeCell ref="AK77:AK78"/>
-    <mergeCell ref="AC136:AC140"/>
-    <mergeCell ref="AC142:AC143"/>
-    <mergeCell ref="BO66:BO67"/>
-    <mergeCell ref="BQ60:BQ64"/>
-    <mergeCell ref="BQ66:BQ67"/>
-    <mergeCell ref="BS60:BS64"/>
-    <mergeCell ref="BS66:BS67"/>
-    <mergeCell ref="BK70:BK71"/>
-    <mergeCell ref="BM69:BN71"/>
-    <mergeCell ref="BO70:BO71"/>
-    <mergeCell ref="AE136:AE140"/>
-    <mergeCell ref="AQ59:AQ60"/>
-    <mergeCell ref="AK59:AK60"/>
-    <mergeCell ref="AO77:AO78"/>
-    <mergeCell ref="AG59:AG60"/>
-    <mergeCell ref="AG62:AG66"/>
-    <mergeCell ref="AG68:AG69"/>
-    <mergeCell ref="BG57:BG58"/>
-    <mergeCell ref="BI69:BJ71"/>
-    <mergeCell ref="BI60:BI64"/>
-    <mergeCell ref="BI66:BI67"/>
-    <mergeCell ref="BG60:BG64"/>
-    <mergeCell ref="BG66:BG67"/>
-    <mergeCell ref="BG70:BG71"/>
-    <mergeCell ref="AM71:AN73"/>
-    <mergeCell ref="AO72:AO73"/>
-    <mergeCell ref="AO68:AO69"/>
-    <mergeCell ref="AI15:AI16"/>
-    <mergeCell ref="AM14:AN16"/>
-    <mergeCell ref="AO15:AO16"/>
-    <mergeCell ref="BI8:BI12"/>
-    <mergeCell ref="BI14:BI15"/>
-    <mergeCell ref="BG8:BG12"/>
-    <mergeCell ref="BG14:BG15"/>
-    <mergeCell ref="BE8:BE12"/>
-    <mergeCell ref="BE14:BE15"/>
-    <mergeCell ref="BC8:BC12"/>
-    <mergeCell ref="BC14:BC15"/>
-    <mergeCell ref="BA8:BA12"/>
-    <mergeCell ref="BA14:BA15"/>
-    <mergeCell ref="AS14:AT16"/>
-    <mergeCell ref="AU15:AU16"/>
-    <mergeCell ref="AK50:AK51"/>
-    <mergeCell ref="BA17:BB19"/>
-    <mergeCell ref="BC18:BC19"/>
-    <mergeCell ref="BA22:BB24"/>
-    <mergeCell ref="BC23:BC24"/>
-    <mergeCell ref="BE69:BF71"/>
-    <mergeCell ref="AA155:AA159"/>
-    <mergeCell ref="AC155:AC159"/>
-    <mergeCell ref="AE155:AE159"/>
-    <mergeCell ref="AK62:AK66"/>
-    <mergeCell ref="AK68:AK69"/>
-    <mergeCell ref="AE142:AE143"/>
-    <mergeCell ref="AA146:AA150"/>
-    <mergeCell ref="AA126:AA130"/>
-    <mergeCell ref="AA132:AA133"/>
-    <mergeCell ref="AC126:AC130"/>
-    <mergeCell ref="AC132:AC133"/>
-    <mergeCell ref="AA116:AA120"/>
-    <mergeCell ref="AA122:AA123"/>
-    <mergeCell ref="AC116:AC120"/>
-    <mergeCell ref="BE22:BF24"/>
-    <mergeCell ref="AK44:AK48"/>
-    <mergeCell ref="AK53:AK57"/>
-    <mergeCell ref="AC53:AD55"/>
-    <mergeCell ref="AA161:AA162"/>
-    <mergeCell ref="AC161:AC162"/>
-    <mergeCell ref="AE161:AE162"/>
-    <mergeCell ref="AA14:AB16"/>
-    <mergeCell ref="AC15:AC16"/>
-    <mergeCell ref="AG14:AH16"/>
-    <mergeCell ref="AC107:AC111"/>
-    <mergeCell ref="AC113:AC114"/>
-    <mergeCell ref="AE122:AE123"/>
-    <mergeCell ref="AA50:AA51"/>
-    <mergeCell ref="AA77:AA78"/>
-    <mergeCell ref="AA62:AA66"/>
-    <mergeCell ref="AA68:AA69"/>
-    <mergeCell ref="AA53:AA57"/>
-    <mergeCell ref="AA59:AA60"/>
-    <mergeCell ref="AA107:AA111"/>
-    <mergeCell ref="AA71:AA75"/>
-    <mergeCell ref="AE152:AE153"/>
-    <mergeCell ref="AE146:AE150"/>
-    <mergeCell ref="AA44:AA48"/>
-    <mergeCell ref="AC44:AD46"/>
-    <mergeCell ref="AE54:AE55"/>
   </mergeCells>
   <conditionalFormatting sqref="AB116:AB123 AB107:AB114 A1:XFD3 BS8 BL61:BL64 A70:AZ70 BL67 BN60:BN67 A61:AT61 BP60:BP67 BO60 BO65:BO66 BR60:BR67 BQ60 BQ65:BQ66 BT60:XFD67 BS60 BS65:BS66 BJ67 BJ61:BJ64 BI60:BM60 BI65:BM66 BH60:BH67 BG60 BG65:BG66 BF60:BF67 BE60 BE65:BE66 BD60:BD67 BC60 BC65:BC66 BB60:BB67 BA65:BA66 A79:XFD106 A71:Z78 AR72:XFD78 AQ76:AQ77 AK71 AK76:AK77 A62:Z69 AK62 AK67:AK68 AR68:XFD68 AR66:AZ67 AQ62 AQ67:AQ68 AR60:AT60 A53:Z60 AQ53 AK53 AK58:AK59 A52:XFD52 A44:Z51 AK44 AK49:AK50 AR45:XFD51 AQ44:AZ44 AQ49:AQ50 AH44:AJ51 AG44 AG49:AG50 AH53:AJ60 AG53 AG58:AG59 AH62:AJ69 AG62 AG67:AG68 AH71:AJ78 AG71 AG76:AG77 AA71 AA76:AA77 AA62 AA67:AA68 AA53 AA58:AA59 AA44 AA49:AA50 A115:XFD115 AF107:XFD114 A125:Z126 AA107 AA112:AA113 AD107:AD114 AC107 AC112:AC113 AF117:XFD120 AE107 AE112:AE113 A135:Z136 AA124:AE125 A116:AA116 AA121:AA122 AD116:AD123 AC116 AC121:AC122 AE116:XFD116 AE121:AE122 A145:Z146 AA134:AE135 AB126:AB133 AA126 AA131:AA132 AD126:AD133 AC126 AC131:AC132 AE126 AE131:AE132 AA144:AE145 AB136:AB143 AA136 AA141:AA142 AD136:AD143 AC136 AC141:AC142 A165:XFD1048576 A155:Z164 AB146:AB153 AA146 AA151:AA152 AD146:AD153 AC146 AC151:AC152 T107:Z114 S107 S112:S113 T117:Z124 S117 S122:S123 T127:Z134 S127 S132:S133 T137:Z144 S137 S142:S143 T147:Z154 S147 S152:S153 AE136 AE141:AE142 AF159:XFD164 AF121:AJ158 AP121:XFD158 AE146 AE151:AE152 BS13:BS14 BR8:BR15 BQ8 BQ13:BQ14 BR17:BS24 BQ17 BQ22:BQ23 BP8:BP15 BO8 BO13:BO14 BN8:BN15 BM8 BM13:BM14 BL8:BL15 BK8 BK13:BK14 BJ8:BJ15 BI8 BI13:BI14 BG8 BG13:BG14 BF8:BF15 BE8 BE13:BE14 BD8:BD15 BC8 BC13:BC14 BB8:BB15 BA8 BA13:BA14 A107:R114 A117:R124 A127:R134 A137:R144 A147:R154 AR69:AZ69 AQ71:AZ71 AR53:XFD57 BA69:XFD71 AL71:AP78 AB71:AF78 AB62:AF69 AB53:AF60 AL53:AP60 AL44:AP51 AB44:AF51 BA17:BP24 AN23:AZ24 AN28:AZ29 AN6:AN13 BH6:BH15 BA16:BS16 AN4:XFD4 AN5:BH5 A30:AZ43 BI5:XFD7 AN25:XFD27 BT8:XFD24 BT28:XFD44 AL62:AP69 A4:AM13 A17:AM29 AN17:AN22 A14:AO16 AQ58:AT59 AV58:XFD59 AV60:BA60 AR62:AT65 AV61:AZ65 AU63:AU64 AU58">
     <cfRule type="dataBar" priority="3">
@@ -22657,32 +22653,32 @@
     </row>
     <row r="68" spans="8:30" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="69" spans="8:30" x14ac:dyDescent="0.2">
-      <c r="N69" s="92" t="s">
-        <v>0</v>
-      </c>
-      <c r="O69" s="93"/>
-      <c r="P69" s="93"/>
-      <c r="Q69" s="93"/>
-      <c r="R69" s="93"/>
-      <c r="S69" s="93"/>
-      <c r="T69" s="93"/>
-      <c r="U69" s="93"/>
-      <c r="V69" s="93"/>
-      <c r="W69" s="93"/>
-      <c r="X69" s="94"/>
+      <c r="N69" s="90" t="s">
+        <v>0</v>
+      </c>
+      <c r="O69" s="91"/>
+      <c r="P69" s="91"/>
+      <c r="Q69" s="91"/>
+      <c r="R69" s="91"/>
+      <c r="S69" s="91"/>
+      <c r="T69" s="91"/>
+      <c r="U69" s="91"/>
+      <c r="V69" s="91"/>
+      <c r="W69" s="91"/>
+      <c r="X69" s="92"/>
     </row>
     <row r="70" spans="8:30" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="N70" s="95"/>
-      <c r="O70" s="96"/>
-      <c r="P70" s="96"/>
-      <c r="Q70" s="96"/>
-      <c r="R70" s="96"/>
-      <c r="S70" s="96"/>
-      <c r="T70" s="96"/>
-      <c r="U70" s="96"/>
-      <c r="V70" s="96"/>
-      <c r="W70" s="96"/>
-      <c r="X70" s="97"/>
+      <c r="N70" s="93"/>
+      <c r="O70" s="94"/>
+      <c r="P70" s="94"/>
+      <c r="Q70" s="94"/>
+      <c r="R70" s="94"/>
+      <c r="S70" s="94"/>
+      <c r="T70" s="94"/>
+      <c r="U70" s="94"/>
+      <c r="V70" s="94"/>
+      <c r="W70" s="94"/>
+      <c r="X70" s="95"/>
     </row>
     <row r="71" spans="8:30" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="K71" s="3"/>
@@ -22690,300 +22686,311 @@
       <c r="M71" s="3"/>
     </row>
     <row r="72" spans="8:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H72" s="116" t="s">
+      <c r="H72" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="J72" s="98"/>
-      <c r="K72" s="99"/>
-      <c r="L72" s="100"/>
-      <c r="N72" s="98"/>
-      <c r="O72" s="99"/>
-      <c r="P72" s="100"/>
-      <c r="R72" s="107" t="s">
+      <c r="J72" s="101"/>
+      <c r="K72" s="102"/>
+      <c r="L72" s="103"/>
+      <c r="N72" s="101"/>
+      <c r="O72" s="102"/>
+      <c r="P72" s="103"/>
+      <c r="R72" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="S72" s="108"/>
-      <c r="T72" s="109"/>
-      <c r="V72" s="107" t="s">
+      <c r="S72" s="111"/>
+      <c r="T72" s="112"/>
+      <c r="V72" s="110" t="s">
         <v>13</v>
       </c>
-      <c r="W72" s="108"/>
-      <c r="X72" s="109"/>
-      <c r="Z72" s="107" t="s">
+      <c r="W72" s="111"/>
+      <c r="X72" s="112"/>
+      <c r="Z72" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="AA72" s="108"/>
-      <c r="AB72" s="109"/>
-      <c r="AD72" s="116" t="s">
+      <c r="AA72" s="111"/>
+      <c r="AB72" s="112"/>
+      <c r="AD72" s="98" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="73" spans="8:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H73" s="117"/>
-      <c r="J73" s="101"/>
-      <c r="K73" s="102"/>
-      <c r="L73" s="103"/>
-      <c r="N73" s="101"/>
-      <c r="O73" s="102"/>
-      <c r="P73" s="103"/>
-      <c r="R73" s="110"/>
-      <c r="S73" s="111"/>
-      <c r="T73" s="112"/>
-      <c r="V73" s="110"/>
-      <c r="W73" s="111"/>
-      <c r="X73" s="112"/>
-      <c r="Z73" s="110"/>
-      <c r="AA73" s="111"/>
-      <c r="AB73" s="112"/>
-      <c r="AD73" s="117"/>
+      <c r="H73" s="99"/>
+      <c r="J73" s="104"/>
+      <c r="K73" s="105"/>
+      <c r="L73" s="106"/>
+      <c r="N73" s="104"/>
+      <c r="O73" s="105"/>
+      <c r="P73" s="106"/>
+      <c r="R73" s="113"/>
+      <c r="S73" s="114"/>
+      <c r="T73" s="115"/>
+      <c r="V73" s="113"/>
+      <c r="W73" s="114"/>
+      <c r="X73" s="115"/>
+      <c r="Z73" s="113"/>
+      <c r="AA73" s="114"/>
+      <c r="AB73" s="115"/>
+      <c r="AD73" s="99"/>
     </row>
     <row r="74" spans="8:30" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H74" s="117"/>
-      <c r="J74" s="104"/>
-      <c r="K74" s="105"/>
-      <c r="L74" s="106"/>
-      <c r="N74" s="104"/>
-      <c r="O74" s="105"/>
-      <c r="P74" s="106"/>
-      <c r="R74" s="113"/>
-      <c r="S74" s="114"/>
-      <c r="T74" s="115"/>
-      <c r="V74" s="113"/>
-      <c r="W74" s="114"/>
-      <c r="X74" s="115"/>
-      <c r="Z74" s="113"/>
-      <c r="AA74" s="114"/>
-      <c r="AB74" s="115"/>
-      <c r="AD74" s="117"/>
+      <c r="H74" s="99"/>
+      <c r="J74" s="107"/>
+      <c r="K74" s="108"/>
+      <c r="L74" s="109"/>
+      <c r="N74" s="107"/>
+      <c r="O74" s="108"/>
+      <c r="P74" s="109"/>
+      <c r="R74" s="116"/>
+      <c r="S74" s="117"/>
+      <c r="T74" s="118"/>
+      <c r="V74" s="116"/>
+      <c r="W74" s="117"/>
+      <c r="X74" s="118"/>
+      <c r="Z74" s="116"/>
+      <c r="AA74" s="117"/>
+      <c r="AB74" s="118"/>
+      <c r="AD74" s="99"/>
     </row>
     <row r="75" spans="8:30" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H75" s="117"/>
-      <c r="AD75" s="117"/>
+      <c r="H75" s="99"/>
+      <c r="AD75" s="99"/>
     </row>
     <row r="76" spans="8:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H76" s="117"/>
+      <c r="H76" s="99"/>
       <c r="J76" s="119"/>
-      <c r="L76" s="78"/>
-      <c r="N76" s="78"/>
-      <c r="P76" s="78"/>
-      <c r="R76" s="78"/>
-      <c r="T76" s="78"/>
-      <c r="V76" s="78" t="s">
+      <c r="L76" s="87"/>
+      <c r="N76" s="87"/>
+      <c r="P76" s="87"/>
+      <c r="R76" s="87"/>
+      <c r="T76" s="87"/>
+      <c r="V76" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="X76" s="78" t="s">
+      <c r="X76" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="Z76" s="78" t="s">
+      <c r="Z76" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="AB76" s="78" t="s">
+      <c r="AB76" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="AD76" s="117"/>
+      <c r="AD76" s="99"/>
     </row>
     <row r="77" spans="8:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H77" s="117"/>
+      <c r="H77" s="99"/>
       <c r="J77" s="120"/>
-      <c r="L77" s="90"/>
-      <c r="N77" s="90"/>
-      <c r="P77" s="90"/>
-      <c r="R77" s="90"/>
-      <c r="T77" s="90"/>
-      <c r="V77" s="90"/>
-      <c r="X77" s="90"/>
-      <c r="Z77" s="90"/>
-      <c r="AB77" s="90"/>
-      <c r="AD77" s="117"/>
+      <c r="L77" s="96"/>
+      <c r="N77" s="96"/>
+      <c r="P77" s="96"/>
+      <c r="R77" s="96"/>
+      <c r="T77" s="96"/>
+      <c r="V77" s="96"/>
+      <c r="X77" s="96"/>
+      <c r="Z77" s="96"/>
+      <c r="AB77" s="96"/>
+      <c r="AD77" s="99"/>
     </row>
     <row r="78" spans="8:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H78" s="117"/>
+      <c r="H78" s="99"/>
       <c r="J78" s="120"/>
-      <c r="L78" s="90"/>
-      <c r="N78" s="90"/>
-      <c r="P78" s="90"/>
-      <c r="R78" s="90"/>
-      <c r="T78" s="90"/>
-      <c r="V78" s="90"/>
-      <c r="X78" s="90"/>
-      <c r="Z78" s="90"/>
-      <c r="AB78" s="90"/>
-      <c r="AD78" s="117"/>
+      <c r="L78" s="96"/>
+      <c r="N78" s="96"/>
+      <c r="P78" s="96"/>
+      <c r="R78" s="96"/>
+      <c r="T78" s="96"/>
+      <c r="V78" s="96"/>
+      <c r="X78" s="96"/>
+      <c r="Z78" s="96"/>
+      <c r="AB78" s="96"/>
+      <c r="AD78" s="99"/>
     </row>
     <row r="79" spans="8:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H79" s="117"/>
+      <c r="H79" s="99"/>
       <c r="J79" s="120"/>
-      <c r="L79" s="90"/>
-      <c r="N79" s="90"/>
-      <c r="P79" s="90"/>
-      <c r="R79" s="90"/>
-      <c r="T79" s="90"/>
-      <c r="V79" s="90"/>
-      <c r="X79" s="90"/>
-      <c r="Z79" s="90"/>
-      <c r="AB79" s="90"/>
-      <c r="AD79" s="117"/>
+      <c r="L79" s="96"/>
+      <c r="N79" s="96"/>
+      <c r="P79" s="96"/>
+      <c r="R79" s="96"/>
+      <c r="T79" s="96"/>
+      <c r="V79" s="96"/>
+      <c r="X79" s="96"/>
+      <c r="Z79" s="96"/>
+      <c r="AB79" s="96"/>
+      <c r="AD79" s="99"/>
     </row>
     <row r="80" spans="8:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H80" s="117"/>
+      <c r="H80" s="99"/>
       <c r="J80" s="120"/>
-      <c r="L80" s="90"/>
-      <c r="N80" s="90"/>
-      <c r="P80" s="90"/>
-      <c r="R80" s="90"/>
-      <c r="T80" s="90"/>
-      <c r="V80" s="90"/>
-      <c r="X80" s="90"/>
-      <c r="Z80" s="90"/>
-      <c r="AB80" s="90"/>
-      <c r="AD80" s="117"/>
+      <c r="L80" s="96"/>
+      <c r="N80" s="96"/>
+      <c r="P80" s="96"/>
+      <c r="R80" s="96"/>
+      <c r="T80" s="96"/>
+      <c r="V80" s="96"/>
+      <c r="X80" s="96"/>
+      <c r="Z80" s="96"/>
+      <c r="AB80" s="96"/>
+      <c r="AD80" s="99"/>
     </row>
     <row r="81" spans="8:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H81" s="117"/>
+      <c r="H81" s="99"/>
       <c r="J81" s="120"/>
-      <c r="L81" s="90"/>
-      <c r="N81" s="90"/>
-      <c r="P81" s="90"/>
-      <c r="R81" s="90"/>
-      <c r="T81" s="90"/>
-      <c r="V81" s="90"/>
-      <c r="X81" s="90"/>
-      <c r="Z81" s="90"/>
-      <c r="AB81" s="90"/>
-      <c r="AD81" s="117"/>
+      <c r="L81" s="96"/>
+      <c r="N81" s="96"/>
+      <c r="P81" s="96"/>
+      <c r="R81" s="96"/>
+      <c r="T81" s="96"/>
+      <c r="V81" s="96"/>
+      <c r="X81" s="96"/>
+      <c r="Z81" s="96"/>
+      <c r="AB81" s="96"/>
+      <c r="AD81" s="99"/>
     </row>
     <row r="82" spans="8:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H82" s="117"/>
+      <c r="H82" s="99"/>
       <c r="J82" s="120"/>
-      <c r="L82" s="90"/>
-      <c r="N82" s="90"/>
-      <c r="P82" s="90"/>
-      <c r="R82" s="90"/>
-      <c r="T82" s="90"/>
-      <c r="V82" s="90"/>
-      <c r="X82" s="90"/>
-      <c r="Z82" s="90"/>
-      <c r="AB82" s="90"/>
-      <c r="AD82" s="117"/>
+      <c r="L82" s="96"/>
+      <c r="N82" s="96"/>
+      <c r="P82" s="96"/>
+      <c r="R82" s="96"/>
+      <c r="T82" s="96"/>
+      <c r="V82" s="96"/>
+      <c r="X82" s="96"/>
+      <c r="Z82" s="96"/>
+      <c r="AB82" s="96"/>
+      <c r="AD82" s="99"/>
     </row>
     <row r="83" spans="8:30" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H83" s="117"/>
+      <c r="H83" s="99"/>
       <c r="J83" s="121"/>
-      <c r="L83" s="91"/>
-      <c r="N83" s="91"/>
-      <c r="P83" s="91"/>
-      <c r="R83" s="91"/>
-      <c r="T83" s="91"/>
-      <c r="V83" s="91"/>
-      <c r="X83" s="91"/>
-      <c r="Z83" s="91"/>
-      <c r="AB83" s="91"/>
-      <c r="AD83" s="117"/>
+      <c r="L83" s="97"/>
+      <c r="N83" s="97"/>
+      <c r="P83" s="97"/>
+      <c r="R83" s="97"/>
+      <c r="T83" s="97"/>
+      <c r="V83" s="97"/>
+      <c r="X83" s="97"/>
+      <c r="Z83" s="97"/>
+      <c r="AB83" s="97"/>
+      <c r="AD83" s="99"/>
     </row>
     <row r="84" spans="8:30" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H84" s="117"/>
-      <c r="AD84" s="117"/>
+      <c r="H84" s="99"/>
+      <c r="AD84" s="99"/>
     </row>
     <row r="85" spans="8:30" x14ac:dyDescent="0.2">
-      <c r="H85" s="117"/>
-      <c r="J85" s="98"/>
-      <c r="K85" s="99"/>
-      <c r="L85" s="100"/>
-      <c r="N85" s="98"/>
-      <c r="O85" s="99"/>
-      <c r="P85" s="100"/>
-      <c r="R85" s="107" t="s">
+      <c r="H85" s="99"/>
+      <c r="J85" s="101"/>
+      <c r="K85" s="102"/>
+      <c r="L85" s="103"/>
+      <c r="N85" s="101"/>
+      <c r="O85" s="102"/>
+      <c r="P85" s="103"/>
+      <c r="R85" s="110" t="s">
         <v>19</v>
       </c>
-      <c r="S85" s="108"/>
-      <c r="T85" s="109"/>
-      <c r="V85" s="107" t="s">
+      <c r="S85" s="111"/>
+      <c r="T85" s="112"/>
+      <c r="V85" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="W85" s="108"/>
-      <c r="X85" s="109"/>
-      <c r="Z85" s="107" t="s">
+      <c r="W85" s="111"/>
+      <c r="X85" s="112"/>
+      <c r="Z85" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="AA85" s="108"/>
-      <c r="AB85" s="109"/>
-      <c r="AD85" s="117"/>
+      <c r="AA85" s="111"/>
+      <c r="AB85" s="112"/>
+      <c r="AD85" s="99"/>
     </row>
     <row r="86" spans="8:30" x14ac:dyDescent="0.2">
-      <c r="H86" s="117"/>
-      <c r="J86" s="101"/>
-      <c r="K86" s="102"/>
-      <c r="L86" s="103"/>
-      <c r="N86" s="101"/>
-      <c r="O86" s="102"/>
-      <c r="P86" s="103"/>
-      <c r="R86" s="110"/>
-      <c r="S86" s="111"/>
-      <c r="T86" s="112"/>
-      <c r="V86" s="110"/>
-      <c r="W86" s="111"/>
-      <c r="X86" s="112"/>
-      <c r="Z86" s="110"/>
-      <c r="AA86" s="111"/>
-      <c r="AB86" s="112"/>
-      <c r="AD86" s="117"/>
+      <c r="H86" s="99"/>
+      <c r="J86" s="104"/>
+      <c r="K86" s="105"/>
+      <c r="L86" s="106"/>
+      <c r="N86" s="104"/>
+      <c r="O86" s="105"/>
+      <c r="P86" s="106"/>
+      <c r="R86" s="113"/>
+      <c r="S86" s="114"/>
+      <c r="T86" s="115"/>
+      <c r="V86" s="113"/>
+      <c r="W86" s="114"/>
+      <c r="X86" s="115"/>
+      <c r="Z86" s="113"/>
+      <c r="AA86" s="114"/>
+      <c r="AB86" s="115"/>
+      <c r="AD86" s="99"/>
     </row>
     <row r="87" spans="8:30" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H87" s="118"/>
-      <c r="J87" s="104"/>
-      <c r="K87" s="105"/>
-      <c r="L87" s="106"/>
-      <c r="N87" s="104"/>
-      <c r="O87" s="105"/>
-      <c r="P87" s="106"/>
-      <c r="R87" s="113"/>
-      <c r="S87" s="114"/>
-      <c r="T87" s="115"/>
-      <c r="V87" s="113"/>
-      <c r="W87" s="114"/>
-      <c r="X87" s="115"/>
-      <c r="Z87" s="113"/>
-      <c r="AA87" s="114"/>
-      <c r="AB87" s="115"/>
-      <c r="AD87" s="117"/>
+      <c r="H87" s="100"/>
+      <c r="J87" s="107"/>
+      <c r="K87" s="108"/>
+      <c r="L87" s="109"/>
+      <c r="N87" s="107"/>
+      <c r="O87" s="108"/>
+      <c r="P87" s="109"/>
+      <c r="R87" s="116"/>
+      <c r="S87" s="117"/>
+      <c r="T87" s="118"/>
+      <c r="V87" s="116"/>
+      <c r="W87" s="117"/>
+      <c r="X87" s="118"/>
+      <c r="Z87" s="116"/>
+      <c r="AA87" s="117"/>
+      <c r="AB87" s="118"/>
+      <c r="AD87" s="99"/>
     </row>
     <row r="88" spans="8:30" x14ac:dyDescent="0.2">
-      <c r="AD88" s="117"/>
+      <c r="AD88" s="99"/>
     </row>
     <row r="89" spans="8:30" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="AD89" s="118"/>
+      <c r="AD89" s="100"/>
     </row>
     <row r="90" spans="8:30" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="91" spans="8:30" x14ac:dyDescent="0.2">
-      <c r="N91" s="92" t="s">
+      <c r="N91" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="93"/>
-      <c r="P91" s="93"/>
-      <c r="Q91" s="93"/>
-      <c r="R91" s="93"/>
-      <c r="S91" s="93"/>
-      <c r="T91" s="93"/>
-      <c r="U91" s="93"/>
-      <c r="V91" s="93"/>
-      <c r="W91" s="93"/>
-      <c r="X91" s="94"/>
+      <c r="O91" s="91"/>
+      <c r="P91" s="91"/>
+      <c r="Q91" s="91"/>
+      <c r="R91" s="91"/>
+      <c r="S91" s="91"/>
+      <c r="T91" s="91"/>
+      <c r="U91" s="91"/>
+      <c r="V91" s="91"/>
+      <c r="W91" s="91"/>
+      <c r="X91" s="92"/>
     </row>
     <row r="92" spans="8:30" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="N92" s="95"/>
-      <c r="O92" s="96"/>
-      <c r="P92" s="96"/>
-      <c r="Q92" s="96"/>
-      <c r="R92" s="96"/>
-      <c r="S92" s="96"/>
-      <c r="T92" s="96"/>
-      <c r="U92" s="96"/>
-      <c r="V92" s="96"/>
-      <c r="W92" s="96"/>
-      <c r="X92" s="97"/>
+      <c r="N92" s="93"/>
+      <c r="O92" s="94"/>
+      <c r="P92" s="94"/>
+      <c r="Q92" s="94"/>
+      <c r="R92" s="94"/>
+      <c r="S92" s="94"/>
+      <c r="T92" s="94"/>
+      <c r="U92" s="94"/>
+      <c r="V92" s="94"/>
+      <c r="W92" s="94"/>
+      <c r="X92" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="N91:X92"/>
+    <mergeCell ref="N69:X70"/>
+    <mergeCell ref="H72:H87"/>
+    <mergeCell ref="J76:J83"/>
+    <mergeCell ref="L76:L83"/>
+    <mergeCell ref="N76:N83"/>
+    <mergeCell ref="P76:P83"/>
+    <mergeCell ref="R76:R83"/>
+    <mergeCell ref="T76:T83"/>
+    <mergeCell ref="V76:V83"/>
+    <mergeCell ref="X76:X83"/>
     <mergeCell ref="Z76:Z83"/>
     <mergeCell ref="AB76:AB83"/>
     <mergeCell ref="AD72:AD89"/>
@@ -22997,17 +23004,6 @@
     <mergeCell ref="R72:T74"/>
     <mergeCell ref="V72:X74"/>
     <mergeCell ref="Z72:AB74"/>
-    <mergeCell ref="N91:X92"/>
-    <mergeCell ref="N69:X70"/>
-    <mergeCell ref="H72:H87"/>
-    <mergeCell ref="J76:J83"/>
-    <mergeCell ref="L76:L83"/>
-    <mergeCell ref="N76:N83"/>
-    <mergeCell ref="P76:P83"/>
-    <mergeCell ref="R76:R83"/>
-    <mergeCell ref="T76:T83"/>
-    <mergeCell ref="V76:V83"/>
-    <mergeCell ref="X76:X83"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -23052,35 +23048,35 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-      <c r="Q12" s="92" t="s">
+      <c r="Q12" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="R12" s="93"/>
-      <c r="S12" s="93"/>
-      <c r="T12" s="93"/>
-      <c r="U12" s="93"/>
-      <c r="V12" s="93"/>
-      <c r="W12" s="93"/>
-      <c r="X12" s="93"/>
-      <c r="Y12" s="93"/>
-      <c r="Z12" s="93"/>
-      <c r="AA12" s="94"/>
+      <c r="R12" s="91"/>
+      <c r="S12" s="91"/>
+      <c r="T12" s="91"/>
+      <c r="U12" s="91"/>
+      <c r="V12" s="91"/>
+      <c r="W12" s="91"/>
+      <c r="X12" s="91"/>
+      <c r="Y12" s="91"/>
+      <c r="Z12" s="91"/>
+      <c r="AA12" s="92"/>
     </row>
     <row r="13" spans="11:27" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
-      <c r="Q13" s="95"/>
-      <c r="R13" s="96"/>
-      <c r="S13" s="96"/>
-      <c r="T13" s="96"/>
-      <c r="U13" s="96"/>
-      <c r="V13" s="96"/>
-      <c r="W13" s="96"/>
-      <c r="X13" s="96"/>
-      <c r="Y13" s="96"/>
-      <c r="Z13" s="96"/>
-      <c r="AA13" s="97"/>
+      <c r="Q13" s="93"/>
+      <c r="R13" s="94"/>
+      <c r="S13" s="94"/>
+      <c r="T13" s="94"/>
+      <c r="U13" s="94"/>
+      <c r="V13" s="94"/>
+      <c r="W13" s="94"/>
+      <c r="X13" s="94"/>
+      <c r="Y13" s="94"/>
+      <c r="Z13" s="94"/>
+      <c r="AA13" s="95"/>
     </row>
     <row r="14" spans="11:27" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="N14" s="3"/>
@@ -23090,258 +23086,261 @@
       <c r="R14" s="3"/>
     </row>
     <row r="15" spans="11:27" x14ac:dyDescent="0.2">
-      <c r="K15" s="116" t="s">
+      <c r="K15" s="98" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="11:27" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="K16" s="117"/>
+      <c r="K16" s="99"/>
     </row>
     <row r="17" spans="11:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K17" s="117"/>
+      <c r="K17" s="99"/>
       <c r="M17" s="119"/>
-      <c r="O17" s="78" t="s">
+      <c r="O17" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="Q17" s="78" t="s">
+      <c r="Q17" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="S17" s="78" t="s">
+      <c r="S17" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="U17" s="78" t="s">
+      <c r="U17" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="W17" s="78" t="s">
+      <c r="W17" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="Y17" s="78" t="s">
+      <c r="Y17" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="AA17" s="78" t="s">
+      <c r="AA17" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="AC17" s="78" t="s">
+      <c r="AC17" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="AE17" s="78" t="s">
+      <c r="AE17" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="AG17" s="116" t="s">
+      <c r="AG17" s="98" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="11:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K18" s="117"/>
+      <c r="K18" s="99"/>
       <c r="M18" s="120"/>
-      <c r="O18" s="90"/>
-      <c r="Q18" s="90"/>
-      <c r="S18" s="90"/>
-      <c r="U18" s="90"/>
-      <c r="W18" s="90"/>
-      <c r="Y18" s="90"/>
-      <c r="AA18" s="90"/>
-      <c r="AC18" s="90"/>
-      <c r="AE18" s="90"/>
-      <c r="AG18" s="117"/>
+      <c r="O18" s="96"/>
+      <c r="Q18" s="96"/>
+      <c r="S18" s="96"/>
+      <c r="U18" s="96"/>
+      <c r="W18" s="96"/>
+      <c r="Y18" s="96"/>
+      <c r="AA18" s="96"/>
+      <c r="AC18" s="96"/>
+      <c r="AE18" s="96"/>
+      <c r="AG18" s="99"/>
     </row>
     <row r="19" spans="11:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K19" s="117"/>
+      <c r="K19" s="99"/>
       <c r="M19" s="120"/>
-      <c r="O19" s="90"/>
-      <c r="Q19" s="90"/>
-      <c r="S19" s="90"/>
-      <c r="U19" s="90"/>
-      <c r="W19" s="90"/>
-      <c r="Y19" s="90"/>
-      <c r="AA19" s="90"/>
-      <c r="AC19" s="90"/>
-      <c r="AE19" s="90"/>
-      <c r="AG19" s="117"/>
+      <c r="O19" s="96"/>
+      <c r="Q19" s="96"/>
+      <c r="S19" s="96"/>
+      <c r="U19" s="96"/>
+      <c r="W19" s="96"/>
+      <c r="Y19" s="96"/>
+      <c r="AA19" s="96"/>
+      <c r="AC19" s="96"/>
+      <c r="AE19" s="96"/>
+      <c r="AG19" s="99"/>
     </row>
     <row r="20" spans="11:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K20" s="117"/>
+      <c r="K20" s="99"/>
       <c r="M20" s="120"/>
-      <c r="O20" s="90"/>
-      <c r="Q20" s="90"/>
-      <c r="S20" s="90"/>
-      <c r="U20" s="90"/>
-      <c r="W20" s="90"/>
-      <c r="Y20" s="90"/>
-      <c r="AA20" s="90"/>
-      <c r="AC20" s="90"/>
-      <c r="AE20" s="90"/>
-      <c r="AG20" s="117"/>
+      <c r="O20" s="96"/>
+      <c r="Q20" s="96"/>
+      <c r="S20" s="96"/>
+      <c r="U20" s="96"/>
+      <c r="W20" s="96"/>
+      <c r="Y20" s="96"/>
+      <c r="AA20" s="96"/>
+      <c r="AC20" s="96"/>
+      <c r="AE20" s="96"/>
+      <c r="AG20" s="99"/>
     </row>
     <row r="21" spans="11:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K21" s="117"/>
+      <c r="K21" s="99"/>
       <c r="M21" s="120"/>
-      <c r="O21" s="90"/>
-      <c r="Q21" s="90"/>
-      <c r="S21" s="90"/>
-      <c r="U21" s="90"/>
-      <c r="W21" s="90"/>
-      <c r="Y21" s="90"/>
-      <c r="AA21" s="90"/>
-      <c r="AC21" s="90"/>
-      <c r="AE21" s="90"/>
-      <c r="AG21" s="117"/>
+      <c r="O21" s="96"/>
+      <c r="Q21" s="96"/>
+      <c r="S21" s="96"/>
+      <c r="U21" s="96"/>
+      <c r="W21" s="96"/>
+      <c r="Y21" s="96"/>
+      <c r="AA21" s="96"/>
+      <c r="AC21" s="96"/>
+      <c r="AE21" s="96"/>
+      <c r="AG21" s="99"/>
     </row>
     <row r="22" spans="11:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K22" s="117"/>
+      <c r="K22" s="99"/>
       <c r="M22" s="120"/>
-      <c r="O22" s="90"/>
-      <c r="Q22" s="90"/>
-      <c r="S22" s="90"/>
-      <c r="U22" s="90"/>
-      <c r="W22" s="90"/>
-      <c r="Y22" s="90"/>
-      <c r="AA22" s="90"/>
-      <c r="AC22" s="90"/>
-      <c r="AE22" s="90"/>
-      <c r="AG22" s="117"/>
+      <c r="O22" s="96"/>
+      <c r="Q22" s="96"/>
+      <c r="S22" s="96"/>
+      <c r="U22" s="96"/>
+      <c r="W22" s="96"/>
+      <c r="Y22" s="96"/>
+      <c r="AA22" s="96"/>
+      <c r="AC22" s="96"/>
+      <c r="AE22" s="96"/>
+      <c r="AG22" s="99"/>
     </row>
     <row r="23" spans="11:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K23" s="117"/>
+      <c r="K23" s="99"/>
       <c r="M23" s="120"/>
-      <c r="O23" s="90"/>
-      <c r="Q23" s="90"/>
-      <c r="S23" s="90"/>
-      <c r="U23" s="90"/>
-      <c r="W23" s="90"/>
-      <c r="Y23" s="90"/>
-      <c r="AA23" s="90"/>
-      <c r="AC23" s="90"/>
-      <c r="AE23" s="90"/>
-      <c r="AG23" s="117"/>
+      <c r="O23" s="96"/>
+      <c r="Q23" s="96"/>
+      <c r="S23" s="96"/>
+      <c r="U23" s="96"/>
+      <c r="W23" s="96"/>
+      <c r="Y23" s="96"/>
+      <c r="AA23" s="96"/>
+      <c r="AC23" s="96"/>
+      <c r="AE23" s="96"/>
+      <c r="AG23" s="99"/>
     </row>
     <row r="24" spans="11:33" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="K24" s="117"/>
+      <c r="K24" s="99"/>
       <c r="M24" s="121"/>
-      <c r="O24" s="91"/>
-      <c r="Q24" s="91"/>
-      <c r="S24" s="91"/>
-      <c r="U24" s="91"/>
-      <c r="W24" s="91"/>
-      <c r="Y24" s="91"/>
-      <c r="AA24" s="91"/>
-      <c r="AC24" s="91"/>
-      <c r="AE24" s="91"/>
-      <c r="AG24" s="117"/>
+      <c r="O24" s="97"/>
+      <c r="Q24" s="97"/>
+      <c r="S24" s="97"/>
+      <c r="U24" s="97"/>
+      <c r="W24" s="97"/>
+      <c r="Y24" s="97"/>
+      <c r="AA24" s="97"/>
+      <c r="AC24" s="97"/>
+      <c r="AE24" s="97"/>
+      <c r="AG24" s="99"/>
     </row>
     <row r="25" spans="11:33" x14ac:dyDescent="0.2">
-      <c r="K25" s="117"/>
-      <c r="AG25" s="117"/>
+      <c r="K25" s="99"/>
+      <c r="AG25" s="99"/>
     </row>
     <row r="26" spans="11:33" x14ac:dyDescent="0.2">
-      <c r="K26" s="117"/>
-      <c r="AG26" s="117"/>
+      <c r="K26" s="99"/>
+      <c r="AG26" s="99"/>
     </row>
     <row r="27" spans="11:33" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="K27" s="117"/>
-      <c r="AG27" s="117"/>
+      <c r="K27" s="99"/>
+      <c r="AG27" s="99"/>
     </row>
     <row r="28" spans="11:33" x14ac:dyDescent="0.2">
-      <c r="K28" s="117"/>
-      <c r="M28" s="98"/>
-      <c r="N28" s="99"/>
-      <c r="O28" s="100"/>
-      <c r="Q28" s="98"/>
-      <c r="R28" s="99"/>
-      <c r="S28" s="100"/>
-      <c r="U28" s="98"/>
-      <c r="V28" s="99"/>
-      <c r="W28" s="100"/>
-      <c r="Y28" s="98"/>
-      <c r="Z28" s="99"/>
-      <c r="AA28" s="100"/>
-      <c r="AC28" s="107" t="s">
+      <c r="K28" s="99"/>
+      <c r="M28" s="101"/>
+      <c r="N28" s="102"/>
+      <c r="O28" s="103"/>
+      <c r="Q28" s="101"/>
+      <c r="R28" s="102"/>
+      <c r="S28" s="103"/>
+      <c r="U28" s="101"/>
+      <c r="V28" s="102"/>
+      <c r="W28" s="103"/>
+      <c r="Y28" s="101"/>
+      <c r="Z28" s="102"/>
+      <c r="AA28" s="103"/>
+      <c r="AC28" s="110" t="s">
         <v>31</v>
       </c>
-      <c r="AD28" s="108"/>
-      <c r="AE28" s="109"/>
-      <c r="AG28" s="117"/>
+      <c r="AD28" s="111"/>
+      <c r="AE28" s="112"/>
+      <c r="AG28" s="99"/>
     </row>
     <row r="29" spans="11:33" x14ac:dyDescent="0.2">
-      <c r="K29" s="117"/>
-      <c r="M29" s="101"/>
-      <c r="N29" s="102"/>
-      <c r="O29" s="103"/>
-      <c r="Q29" s="101"/>
-      <c r="R29" s="102"/>
-      <c r="S29" s="103"/>
-      <c r="U29" s="101"/>
-      <c r="V29" s="102"/>
-      <c r="W29" s="103"/>
-      <c r="Y29" s="101"/>
-      <c r="Z29" s="102"/>
-      <c r="AA29" s="103"/>
-      <c r="AC29" s="110"/>
-      <c r="AD29" s="111"/>
-      <c r="AE29" s="112"/>
-      <c r="AG29" s="117"/>
+      <c r="K29" s="99"/>
+      <c r="M29" s="104"/>
+      <c r="N29" s="105"/>
+      <c r="O29" s="106"/>
+      <c r="Q29" s="104"/>
+      <c r="R29" s="105"/>
+      <c r="S29" s="106"/>
+      <c r="U29" s="104"/>
+      <c r="V29" s="105"/>
+      <c r="W29" s="106"/>
+      <c r="Y29" s="104"/>
+      <c r="Z29" s="105"/>
+      <c r="AA29" s="106"/>
+      <c r="AC29" s="113"/>
+      <c r="AD29" s="114"/>
+      <c r="AE29" s="115"/>
+      <c r="AG29" s="99"/>
     </row>
     <row r="30" spans="11:33" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="K30" s="117"/>
-      <c r="M30" s="104"/>
-      <c r="N30" s="105"/>
-      <c r="O30" s="106"/>
-      <c r="Q30" s="104"/>
-      <c r="R30" s="105"/>
-      <c r="S30" s="106"/>
-      <c r="U30" s="104"/>
-      <c r="V30" s="105"/>
-      <c r="W30" s="106"/>
-      <c r="Y30" s="104"/>
-      <c r="Z30" s="105"/>
-      <c r="AA30" s="106"/>
-      <c r="AC30" s="113"/>
-      <c r="AD30" s="114"/>
-      <c r="AE30" s="115"/>
-      <c r="AG30" s="117"/>
+      <c r="K30" s="99"/>
+      <c r="M30" s="107"/>
+      <c r="N30" s="108"/>
+      <c r="O30" s="109"/>
+      <c r="Q30" s="107"/>
+      <c r="R30" s="108"/>
+      <c r="S30" s="109"/>
+      <c r="U30" s="107"/>
+      <c r="V30" s="108"/>
+      <c r="W30" s="109"/>
+      <c r="Y30" s="107"/>
+      <c r="Z30" s="108"/>
+      <c r="AA30" s="109"/>
+      <c r="AC30" s="116"/>
+      <c r="AD30" s="117"/>
+      <c r="AE30" s="118"/>
+      <c r="AG30" s="99"/>
     </row>
     <row r="31" spans="11:33" x14ac:dyDescent="0.2">
-      <c r="K31" s="117"/>
-      <c r="AG31" s="117"/>
+      <c r="K31" s="99"/>
+      <c r="AG31" s="99"/>
     </row>
     <row r="32" spans="11:33" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="K32" s="118"/>
-      <c r="AG32" s="117"/>
+      <c r="K32" s="100"/>
+      <c r="AG32" s="99"/>
     </row>
     <row r="33" spans="17:33" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="AG33" s="117"/>
+      <c r="AG33" s="99"/>
     </row>
     <row r="34" spans="17:33" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="Q34" s="92" t="s">
+      <c r="Q34" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="R34" s="93"/>
-      <c r="S34" s="93"/>
-      <c r="T34" s="93"/>
-      <c r="U34" s="93"/>
-      <c r="V34" s="93"/>
-      <c r="W34" s="93"/>
-      <c r="X34" s="93"/>
-      <c r="Y34" s="93"/>
-      <c r="Z34" s="93"/>
-      <c r="AA34" s="94"/>
-      <c r="AG34" s="118"/>
+      <c r="R34" s="91"/>
+      <c r="S34" s="91"/>
+      <c r="T34" s="91"/>
+      <c r="U34" s="91"/>
+      <c r="V34" s="91"/>
+      <c r="W34" s="91"/>
+      <c r="X34" s="91"/>
+      <c r="Y34" s="91"/>
+      <c r="Z34" s="91"/>
+      <c r="AA34" s="92"/>
+      <c r="AG34" s="100"/>
     </row>
     <row r="35" spans="17:33" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="Q35" s="95"/>
-      <c r="R35" s="96"/>
-      <c r="S35" s="96"/>
-      <c r="T35" s="96"/>
-      <c r="U35" s="96"/>
-      <c r="V35" s="96"/>
-      <c r="W35" s="96"/>
-      <c r="X35" s="96"/>
-      <c r="Y35" s="96"/>
-      <c r="Z35" s="96"/>
-      <c r="AA35" s="97"/>
+      <c r="Q35" s="93"/>
+      <c r="R35" s="94"/>
+      <c r="S35" s="94"/>
+      <c r="T35" s="94"/>
+      <c r="U35" s="94"/>
+      <c r="V35" s="94"/>
+      <c r="W35" s="94"/>
+      <c r="X35" s="94"/>
+      <c r="Y35" s="94"/>
+      <c r="Z35" s="94"/>
+      <c r="AA35" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="Q17:Q24"/>
+    <mergeCell ref="O17:O24"/>
+    <mergeCell ref="Q12:AA13"/>
     <mergeCell ref="Q34:AA35"/>
     <mergeCell ref="K15:K32"/>
     <mergeCell ref="AG17:AG34"/>
@@ -23358,9 +23357,6 @@
     <mergeCell ref="W17:W24"/>
     <mergeCell ref="U17:U24"/>
     <mergeCell ref="S17:S24"/>
-    <mergeCell ref="Q17:Q24"/>
-    <mergeCell ref="O17:O24"/>
-    <mergeCell ref="Q12:AA13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -23407,43 +23403,43 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="92" t="s">
+      <c r="H5" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="I5" s="93"/>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="93"/>
-      <c r="M5" s="93"/>
-      <c r="N5" s="93"/>
-      <c r="O5" s="93"/>
-      <c r="P5" s="93"/>
-      <c r="Q5" s="93"/>
-      <c r="R5" s="93"/>
-      <c r="S5" s="93"/>
-      <c r="T5" s="93"/>
-      <c r="U5" s="93"/>
-      <c r="V5" s="94"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="91"/>
+      <c r="M5" s="91"/>
+      <c r="N5" s="91"/>
+      <c r="O5" s="91"/>
+      <c r="P5" s="91"/>
+      <c r="Q5" s="91"/>
+      <c r="R5" s="91"/>
+      <c r="S5" s="91"/>
+      <c r="T5" s="91"/>
+      <c r="U5" s="91"/>
+      <c r="V5" s="92"/>
     </row>
     <row r="6" spans="2:28" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="96"/>
-      <c r="J6" s="96"/>
-      <c r="K6" s="96"/>
-      <c r="L6" s="96"/>
-      <c r="M6" s="96"/>
-      <c r="N6" s="96"/>
-      <c r="O6" s="96"/>
-      <c r="P6" s="96"/>
-      <c r="Q6" s="96"/>
-      <c r="R6" s="96"/>
-      <c r="S6" s="96"/>
-      <c r="T6" s="96"/>
-      <c r="U6" s="96"/>
-      <c r="V6" s="97"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="94"/>
+      <c r="J6" s="94"/>
+      <c r="K6" s="94"/>
+      <c r="L6" s="94"/>
+      <c r="M6" s="94"/>
+      <c r="N6" s="94"/>
+      <c r="O6" s="94"/>
+      <c r="P6" s="94"/>
+      <c r="Q6" s="94"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="94"/>
+      <c r="T6" s="94"/>
+      <c r="U6" s="94"/>
+      <c r="V6" s="95"/>
     </row>
     <row r="7" spans="2:28" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E7" s="3"/>
@@ -23453,45 +23449,45 @@
       <c r="I7" s="3"/>
     </row>
     <row r="8" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="116" t="s">
+      <c r="B8" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="107" t="s">
+      <c r="D8" s="110" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="122"/>
       <c r="F8" s="123"/>
-      <c r="H8" s="107" t="s">
+      <c r="H8" s="110" t="s">
         <v>33</v>
       </c>
       <c r="I8" s="122"/>
       <c r="J8" s="123"/>
-      <c r="L8" s="107" t="s">
+      <c r="L8" s="110" t="s">
         <v>34</v>
       </c>
       <c r="M8" s="122"/>
       <c r="N8" s="123"/>
-      <c r="P8" s="107" t="s">
+      <c r="P8" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="Q8" s="108"/>
-      <c r="R8" s="109"/>
-      <c r="T8" s="107" t="s">
+      <c r="Q8" s="111"/>
+      <c r="R8" s="112"/>
+      <c r="T8" s="110" t="s">
         <v>36</v>
       </c>
-      <c r="U8" s="108"/>
-      <c r="V8" s="109"/>
-      <c r="X8" s="107" t="s">
+      <c r="U8" s="111"/>
+      <c r="V8" s="112"/>
+      <c r="X8" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="Y8" s="108"/>
-      <c r="Z8" s="109"/>
-      <c r="AB8" s="116" t="s">
+      <c r="Y8" s="111"/>
+      <c r="Z8" s="112"/>
+      <c r="AB8" s="98" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="117"/>
+      <c r="B9" s="99"/>
       <c r="D9" s="124"/>
       <c r="E9" s="125"/>
       <c r="F9" s="126"/>
@@ -23501,19 +23497,19 @@
       <c r="L9" s="124"/>
       <c r="M9" s="125"/>
       <c r="N9" s="126"/>
-      <c r="P9" s="110"/>
-      <c r="Q9" s="111"/>
-      <c r="R9" s="112"/>
-      <c r="T9" s="110"/>
-      <c r="U9" s="111"/>
-      <c r="V9" s="112"/>
-      <c r="X9" s="110"/>
-      <c r="Y9" s="111"/>
-      <c r="Z9" s="112"/>
-      <c r="AB9" s="117"/>
+      <c r="P9" s="113"/>
+      <c r="Q9" s="114"/>
+      <c r="R9" s="115"/>
+      <c r="T9" s="113"/>
+      <c r="U9" s="114"/>
+      <c r="V9" s="115"/>
+      <c r="X9" s="113"/>
+      <c r="Y9" s="114"/>
+      <c r="Z9" s="115"/>
+      <c r="AB9" s="99"/>
     </row>
     <row r="10" spans="2:28" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="117"/>
+      <c r="B10" s="99"/>
       <c r="D10" s="127"/>
       <c r="E10" s="128"/>
       <c r="F10" s="129"/>
@@ -23523,19 +23519,19 @@
       <c r="L10" s="127"/>
       <c r="M10" s="128"/>
       <c r="N10" s="129"/>
-      <c r="P10" s="113"/>
-      <c r="Q10" s="114"/>
-      <c r="R10" s="115"/>
-      <c r="T10" s="113"/>
-      <c r="U10" s="114"/>
-      <c r="V10" s="115"/>
-      <c r="X10" s="113"/>
-      <c r="Y10" s="114"/>
-      <c r="Z10" s="115"/>
-      <c r="AB10" s="117"/>
+      <c r="P10" s="116"/>
+      <c r="Q10" s="117"/>
+      <c r="R10" s="118"/>
+      <c r="T10" s="116"/>
+      <c r="U10" s="117"/>
+      <c r="V10" s="118"/>
+      <c r="X10" s="116"/>
+      <c r="Y10" s="117"/>
+      <c r="Z10" s="118"/>
+      <c r="AB10" s="99"/>
     </row>
     <row r="11" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="117"/>
+      <c r="B11" s="99"/>
       <c r="D11" s="11"/>
       <c r="F11" s="6"/>
       <c r="H11" s="6"/>
@@ -23546,10 +23542,10 @@
       <c r="R11" s="6"/>
       <c r="T11" s="6"/>
       <c r="V11" s="6"/>
-      <c r="AB11" s="117"/>
+      <c r="AB11" s="99"/>
     </row>
     <row r="12" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="117"/>
+      <c r="B12" s="99"/>
       <c r="D12" s="11"/>
       <c r="F12" s="6"/>
       <c r="H12" s="6"/>
@@ -23560,10 +23556,10 @@
       <c r="R12" s="6"/>
       <c r="T12" s="6"/>
       <c r="V12" s="6"/>
-      <c r="AB12" s="117"/>
+      <c r="AB12" s="99"/>
     </row>
     <row r="13" spans="2:28" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="117"/>
+      <c r="B13" s="99"/>
       <c r="D13" s="11"/>
       <c r="F13" s="6"/>
       <c r="H13" s="6"/>
@@ -23574,171 +23570,171 @@
       <c r="R13" s="6"/>
       <c r="T13" s="6"/>
       <c r="V13" s="6"/>
-      <c r="AB13" s="117"/>
+      <c r="AB13" s="99"/>
     </row>
     <row r="14" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="117"/>
-      <c r="D14" s="107" t="s">
+      <c r="B14" s="99"/>
+      <c r="D14" s="110" t="s">
         <v>38</v>
       </c>
       <c r="E14" s="122"/>
       <c r="F14" s="123"/>
-      <c r="H14" s="107" t="s">
+      <c r="H14" s="110" t="s">
         <v>39</v>
       </c>
       <c r="I14" s="122"/>
       <c r="J14" s="123"/>
-      <c r="L14" s="107" t="s">
+      <c r="L14" s="110" t="s">
         <v>40</v>
       </c>
-      <c r="M14" s="108"/>
-      <c r="N14" s="109"/>
-      <c r="P14" s="107" t="s">
+      <c r="M14" s="111"/>
+      <c r="N14" s="112"/>
+      <c r="P14" s="110" t="s">
         <v>41</v>
       </c>
       <c r="Q14" s="122"/>
       <c r="R14" s="123"/>
-      <c r="T14" s="107" t="s">
+      <c r="T14" s="110" t="s">
         <v>42</v>
       </c>
       <c r="U14" s="122"/>
       <c r="V14" s="123"/>
-      <c r="X14" s="107" t="s">
+      <c r="X14" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="Y14" s="108"/>
-      <c r="Z14" s="109"/>
-      <c r="AB14" s="117"/>
+      <c r="Y14" s="111"/>
+      <c r="Z14" s="112"/>
+      <c r="AB14" s="99"/>
     </row>
     <row r="15" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="117"/>
+      <c r="B15" s="99"/>
       <c r="D15" s="124"/>
       <c r="E15" s="125"/>
       <c r="F15" s="126"/>
       <c r="H15" s="124"/>
       <c r="I15" s="125"/>
       <c r="J15" s="126"/>
-      <c r="L15" s="110"/>
-      <c r="M15" s="111"/>
-      <c r="N15" s="112"/>
+      <c r="L15" s="113"/>
+      <c r="M15" s="114"/>
+      <c r="N15" s="115"/>
       <c r="P15" s="124"/>
       <c r="Q15" s="125"/>
       <c r="R15" s="126"/>
       <c r="T15" s="124"/>
       <c r="U15" s="125"/>
       <c r="V15" s="126"/>
-      <c r="X15" s="110"/>
-      <c r="Y15" s="111"/>
-      <c r="Z15" s="112"/>
-      <c r="AB15" s="117"/>
+      <c r="X15" s="113"/>
+      <c r="Y15" s="114"/>
+      <c r="Z15" s="115"/>
+      <c r="AB15" s="99"/>
     </row>
     <row r="16" spans="2:28" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="117"/>
+      <c r="B16" s="99"/>
       <c r="D16" s="127"/>
       <c r="E16" s="128"/>
       <c r="F16" s="129"/>
       <c r="H16" s="127"/>
       <c r="I16" s="128"/>
       <c r="J16" s="129"/>
-      <c r="L16" s="113"/>
-      <c r="M16" s="114"/>
-      <c r="N16" s="115"/>
+      <c r="L16" s="116"/>
+      <c r="M16" s="117"/>
+      <c r="N16" s="118"/>
       <c r="P16" s="127"/>
       <c r="Q16" s="128"/>
       <c r="R16" s="129"/>
       <c r="T16" s="127"/>
       <c r="U16" s="128"/>
       <c r="V16" s="129"/>
-      <c r="X16" s="113"/>
-      <c r="Y16" s="114"/>
-      <c r="Z16" s="115"/>
-      <c r="AB16" s="117"/>
+      <c r="X16" s="116"/>
+      <c r="Y16" s="117"/>
+      <c r="Z16" s="118"/>
+      <c r="AB16" s="99"/>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="B17" s="117"/>
-      <c r="AB17" s="117"/>
+      <c r="B17" s="99"/>
+      <c r="AB17" s="99"/>
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="B18" s="117"/>
-      <c r="AB18" s="117"/>
+      <c r="B18" s="99"/>
+      <c r="AB18" s="99"/>
     </row>
     <row r="19" spans="2:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="117"/>
-      <c r="AB19" s="117"/>
+      <c r="B19" s="99"/>
+      <c r="AB19" s="99"/>
     </row>
     <row r="20" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="117"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="99"/>
-      <c r="F20" s="100"/>
-      <c r="H20" s="98"/>
-      <c r="I20" s="99"/>
-      <c r="J20" s="100"/>
-      <c r="L20" s="107" t="s">
+      <c r="B20" s="99"/>
+      <c r="D20" s="101"/>
+      <c r="E20" s="102"/>
+      <c r="F20" s="103"/>
+      <c r="H20" s="101"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="103"/>
+      <c r="L20" s="110" t="s">
         <v>44</v>
       </c>
-      <c r="M20" s="108"/>
-      <c r="N20" s="109"/>
-      <c r="P20" s="107" t="s">
+      <c r="M20" s="111"/>
+      <c r="N20" s="112"/>
+      <c r="P20" s="110" t="s">
         <v>45</v>
       </c>
-      <c r="Q20" s="108"/>
-      <c r="R20" s="109"/>
-      <c r="T20" s="107" t="s">
+      <c r="Q20" s="111"/>
+      <c r="R20" s="112"/>
+      <c r="T20" s="110" t="s">
         <v>46</v>
       </c>
-      <c r="U20" s="108"/>
-      <c r="V20" s="109"/>
-      <c r="X20" s="107" t="s">
+      <c r="U20" s="111"/>
+      <c r="V20" s="112"/>
+      <c r="X20" s="110" t="s">
         <v>47</v>
       </c>
-      <c r="Y20" s="108"/>
-      <c r="Z20" s="109"/>
-      <c r="AB20" s="117"/>
+      <c r="Y20" s="111"/>
+      <c r="Z20" s="112"/>
+      <c r="AB20" s="99"/>
     </row>
     <row r="21" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="117"/>
-      <c r="D21" s="101"/>
-      <c r="E21" s="102"/>
-      <c r="F21" s="103"/>
-      <c r="H21" s="101"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="103"/>
-      <c r="L21" s="110"/>
-      <c r="M21" s="111"/>
-      <c r="N21" s="112"/>
-      <c r="P21" s="110"/>
-      <c r="Q21" s="111"/>
-      <c r="R21" s="112"/>
-      <c r="T21" s="110"/>
-      <c r="U21" s="111"/>
-      <c r="V21" s="112"/>
-      <c r="X21" s="110"/>
-      <c r="Y21" s="111"/>
-      <c r="Z21" s="112"/>
-      <c r="AB21" s="117"/>
+      <c r="B21" s="99"/>
+      <c r="D21" s="104"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="106"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="106"/>
+      <c r="L21" s="113"/>
+      <c r="M21" s="114"/>
+      <c r="N21" s="115"/>
+      <c r="P21" s="113"/>
+      <c r="Q21" s="114"/>
+      <c r="R21" s="115"/>
+      <c r="T21" s="113"/>
+      <c r="U21" s="114"/>
+      <c r="V21" s="115"/>
+      <c r="X21" s="113"/>
+      <c r="Y21" s="114"/>
+      <c r="Z21" s="115"/>
+      <c r="AB21" s="99"/>
     </row>
     <row r="22" spans="2:28" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="118"/>
-      <c r="D22" s="104"/>
-      <c r="E22" s="105"/>
-      <c r="F22" s="106"/>
-      <c r="H22" s="104"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="106"/>
-      <c r="L22" s="113"/>
-      <c r="M22" s="114"/>
-      <c r="N22" s="115"/>
-      <c r="P22" s="113"/>
-      <c r="Q22" s="114"/>
-      <c r="R22" s="115"/>
-      <c r="T22" s="113"/>
-      <c r="U22" s="114"/>
-      <c r="V22" s="115"/>
-      <c r="X22" s="113"/>
-      <c r="Y22" s="114"/>
-      <c r="Z22" s="115"/>
-      <c r="AB22" s="118"/>
+      <c r="B22" s="100"/>
+      <c r="D22" s="107"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="109"/>
+      <c r="H22" s="107"/>
+      <c r="I22" s="108"/>
+      <c r="J22" s="109"/>
+      <c r="L22" s="116"/>
+      <c r="M22" s="117"/>
+      <c r="N22" s="118"/>
+      <c r="P22" s="116"/>
+      <c r="Q22" s="117"/>
+      <c r="R22" s="118"/>
+      <c r="T22" s="116"/>
+      <c r="U22" s="117"/>
+      <c r="V22" s="118"/>
+      <c r="X22" s="116"/>
+      <c r="Y22" s="117"/>
+      <c r="Z22" s="118"/>
+      <c r="AB22" s="100"/>
     </row>
     <row r="23" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="10"/>
@@ -23750,43 +23746,49 @@
     </row>
     <row r="25" spans="2:28" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H26" s="92" t="s">
+      <c r="H26" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="I26" s="93"/>
-      <c r="J26" s="93"/>
-      <c r="K26" s="93"/>
-      <c r="L26" s="93"/>
-      <c r="M26" s="93"/>
-      <c r="N26" s="93"/>
-      <c r="O26" s="93"/>
-      <c r="P26" s="93"/>
-      <c r="Q26" s="93"/>
-      <c r="R26" s="93"/>
-      <c r="S26" s="93"/>
-      <c r="T26" s="93"/>
-      <c r="U26" s="93"/>
-      <c r="V26" s="94"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="91"/>
+      <c r="K26" s="91"/>
+      <c r="L26" s="91"/>
+      <c r="M26" s="91"/>
+      <c r="N26" s="91"/>
+      <c r="O26" s="91"/>
+      <c r="P26" s="91"/>
+      <c r="Q26" s="91"/>
+      <c r="R26" s="91"/>
+      <c r="S26" s="91"/>
+      <c r="T26" s="91"/>
+      <c r="U26" s="91"/>
+      <c r="V26" s="92"/>
     </row>
     <row r="27" spans="2:28" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H27" s="95"/>
-      <c r="I27" s="96"/>
-      <c r="J27" s="96"/>
-      <c r="K27" s="96"/>
-      <c r="L27" s="96"/>
-      <c r="M27" s="96"/>
-      <c r="N27" s="96"/>
-      <c r="O27" s="96"/>
-      <c r="P27" s="96"/>
-      <c r="Q27" s="96"/>
-      <c r="R27" s="96"/>
-      <c r="S27" s="96"/>
-      <c r="T27" s="96"/>
-      <c r="U27" s="96"/>
-      <c r="V27" s="97"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="94"/>
+      <c r="J27" s="94"/>
+      <c r="K27" s="94"/>
+      <c r="L27" s="94"/>
+      <c r="M27" s="94"/>
+      <c r="N27" s="94"/>
+      <c r="O27" s="94"/>
+      <c r="P27" s="94"/>
+      <c r="Q27" s="94"/>
+      <c r="R27" s="94"/>
+      <c r="S27" s="94"/>
+      <c r="T27" s="94"/>
+      <c r="U27" s="94"/>
+      <c r="V27" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="X20:Z22"/>
+    <mergeCell ref="D20:F22"/>
+    <mergeCell ref="H20:J22"/>
+    <mergeCell ref="L20:N22"/>
+    <mergeCell ref="P20:R22"/>
+    <mergeCell ref="T20:V22"/>
     <mergeCell ref="AB8:AB22"/>
     <mergeCell ref="B8:B22"/>
     <mergeCell ref="H5:V6"/>
@@ -23803,12 +23805,6 @@
     <mergeCell ref="P8:R10"/>
     <mergeCell ref="T8:V10"/>
     <mergeCell ref="X8:Z10"/>
-    <mergeCell ref="X20:Z22"/>
-    <mergeCell ref="D20:F22"/>
-    <mergeCell ref="H20:J22"/>
-    <mergeCell ref="L20:N22"/>
-    <mergeCell ref="P20:R22"/>
-    <mergeCell ref="T20:V22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
